--- a/data/MARR.MI.xlsx
+++ b/data/MARR.MI.xlsx
@@ -62886,6 +62886,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2719">
+      <c r="A2719" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2719" t="n">
+        <v>118967</v>
+      </c>
+      <c r="C2719" t="n">
+        <v>5.84999990463257</v>
+      </c>
+      <c r="D2719" t="n">
+        <v>5.71999979019165</v>
+      </c>
+      <c r="E2719" t="n">
+        <v>5.71999979019165</v>
+      </c>
+      <c r="F2719" t="n">
+        <v>5.76000022888184</v>
+      </c>
+      <c r="G2719" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MARR.MI.xlsx
+++ b/data/MARR.MI.xlsx
@@ -62909,6 +62909,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2720">
+      <c r="A2720" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2720" t="n">
+        <v>141892</v>
+      </c>
+      <c r="C2720" t="n">
+        <v>5.78999996185303</v>
+      </c>
+      <c r="D2720" t="n">
+        <v>5.69999980926514</v>
+      </c>
+      <c r="E2720" t="n">
+        <v>5.76000022888184</v>
+      </c>
+      <c r="F2720" t="n">
+        <v>5.71000003814697</v>
+      </c>
+      <c r="G2720" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MARR.MI.xlsx
+++ b/data/MARR.MI.xlsx
@@ -62932,6 +62932,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2721">
+      <c r="A2721" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2721" t="n">
+        <v>201000</v>
+      </c>
+      <c r="C2721" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="D2721" t="n">
+        <v>5.65000009536743</v>
+      </c>
+      <c r="E2721" t="n">
+        <v>5.69999980926514</v>
+      </c>
+      <c r="F2721" t="n">
+        <v>5.67999982833862</v>
+      </c>
+      <c r="G2721" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MARR.MI.xlsx
+++ b/data/MARR.MI.xlsx
@@ -62955,6 +62955,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2722">
+      <c r="A2722" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2722" t="n">
+        <v>250977</v>
+      </c>
+      <c r="C2722" t="n">
+        <v>5.78999996185303</v>
+      </c>
+      <c r="D2722" t="n">
+        <v>5.6100001335144</v>
+      </c>
+      <c r="E2722" t="n">
+        <v>5.71999979019165</v>
+      </c>
+      <c r="F2722" t="n">
+        <v>5.6100001335144</v>
+      </c>
+      <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MARR.MI.xlsx
+++ b/data/MARR.MI.xlsx
@@ -62796,22 +62796,22 @@
     </row>
     <row r="2715">
       <c r="A2715" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2715" t="n">
-        <v>191789</v>
+        <v>277032</v>
       </c>
       <c r="C2715" t="n">
-        <v>5.88000011444092</v>
+        <v>5.96000003814697</v>
       </c>
       <c r="D2715" t="n">
-        <v>5.76000022888184</v>
+        <v>5.76999998092651</v>
       </c>
       <c r="E2715" t="n">
-        <v>5.80000019073486</v>
+        <v>5.96000003814697</v>
       </c>
       <c r="F2715" t="n">
-        <v>5.84999990463257</v>
+        <v>5.76999998092651</v>
       </c>
       <c r="G2715" t="s">
         <v>7</v>
@@ -62819,22 +62819,22 @@
     </row>
     <row r="2716">
       <c r="A2716" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2716" t="n">
-        <v>182879</v>
+        <v>191789</v>
       </c>
       <c r="C2716" t="n">
-        <v>5.8899998664856</v>
+        <v>5.88000011444092</v>
       </c>
       <c r="D2716" t="n">
-        <v>5.73999977111816</v>
+        <v>5.76000022888184</v>
       </c>
       <c r="E2716" t="n">
-        <v>5.84000015258789</v>
+        <v>5.80000019073486</v>
       </c>
       <c r="F2716" t="n">
-        <v>5.75</v>
+        <v>5.84999990463257</v>
       </c>
       <c r="G2716" t="s">
         <v>7</v>
@@ -62842,19 +62842,19 @@
     </row>
     <row r="2717">
       <c r="A2717" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2717" t="n">
-        <v>132357</v>
+        <v>182879</v>
       </c>
       <c r="C2717" t="n">
+        <v>5.8899998664856</v>
+      </c>
+      <c r="D2717" t="n">
+        <v>5.73999977111816</v>
+      </c>
+      <c r="E2717" t="n">
         <v>5.84000015258789</v>
-      </c>
-      <c r="D2717" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="E2717" t="n">
-        <v>5.78999996185303</v>
       </c>
       <c r="F2717" t="n">
         <v>5.75</v>
@@ -62865,22 +62865,22 @@
     </row>
     <row r="2718">
       <c r="A2718" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2718" t="n">
-        <v>164201</v>
+        <v>132357</v>
       </c>
       <c r="C2718" t="n">
-        <v>5.80999994277954</v>
+        <v>5.84000015258789</v>
       </c>
       <c r="D2718" t="n">
-        <v>5.67999982833862</v>
+        <v>5.75</v>
       </c>
       <c r="E2718" t="n">
+        <v>5.78999996185303</v>
+      </c>
+      <c r="F2718" t="n">
         <v>5.75</v>
-      </c>
-      <c r="F2718" t="n">
-        <v>5.71999979019165</v>
       </c>
       <c r="G2718" t="s">
         <v>7</v>
@@ -62888,22 +62888,22 @@
     </row>
     <row r="2719">
       <c r="A2719" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2719" t="n">
-        <v>118967</v>
+        <v>164201</v>
       </c>
       <c r="C2719" t="n">
-        <v>5.84999990463257</v>
+        <v>5.80999994277954</v>
       </c>
       <c r="D2719" t="n">
+        <v>5.67999982833862</v>
+      </c>
+      <c r="E2719" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="F2719" t="n">
         <v>5.71999979019165</v>
-      </c>
-      <c r="E2719" t="n">
-        <v>5.71999979019165</v>
-      </c>
-      <c r="F2719" t="n">
-        <v>5.76000022888184</v>
       </c>
       <c r="G2719" t="s">
         <v>7</v>
@@ -62911,22 +62911,22 @@
     </row>
     <row r="2720">
       <c r="A2720" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2720" t="n">
-        <v>141892</v>
+        <v>118967</v>
       </c>
       <c r="C2720" t="n">
-        <v>5.78999996185303</v>
+        <v>5.84999990463257</v>
       </c>
       <c r="D2720" t="n">
-        <v>5.69999980926514</v>
+        <v>5.71999979019165</v>
       </c>
       <c r="E2720" t="n">
+        <v>5.71999979019165</v>
+      </c>
+      <c r="F2720" t="n">
         <v>5.76000022888184</v>
-      </c>
-      <c r="F2720" t="n">
-        <v>5.71000003814697</v>
       </c>
       <c r="G2720" t="s">
         <v>7</v>
@@ -62934,22 +62934,22 @@
     </row>
     <row r="2721">
       <c r="A2721" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2721" t="n">
-        <v>201000</v>
+        <v>141892</v>
       </c>
       <c r="C2721" t="n">
-        <v>5.75</v>
+        <v>5.78999996185303</v>
       </c>
       <c r="D2721" t="n">
-        <v>5.65000009536743</v>
+        <v>5.69999980926514</v>
       </c>
       <c r="E2721" t="n">
-        <v>5.69999980926514</v>
+        <v>5.76000022888184</v>
       </c>
       <c r="F2721" t="n">
-        <v>5.67999982833862</v>
+        <v>5.71000003814697</v>
       </c>
       <c r="G2721" t="s">
         <v>7</v>
@@ -62957,24 +62957,47 @@
     </row>
     <row r="2722">
       <c r="A2722" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B2722" t="n">
-        <v>250977</v>
+        <v>201000</v>
       </c>
       <c r="C2722" t="n">
-        <v>5.78999996185303</v>
+        <v>5.75</v>
       </c>
       <c r="D2722" t="n">
-        <v>5.6100001335144</v>
+        <v>5.65000009536743</v>
       </c>
       <c r="E2722" t="n">
-        <v>5.71999979019165</v>
+        <v>5.69999980926514</v>
       </c>
       <c r="F2722" t="n">
-        <v>5.6100001335144</v>
+        <v>5.67999982833862</v>
       </c>
       <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2723">
+      <c r="A2723" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2723" t="n">
+        <v>1945796</v>
+      </c>
+      <c r="C2723" t="n">
+        <v>5.65999984741211</v>
+      </c>
+      <c r="D2723" t="n">
+        <v>5.48000001907349</v>
+      </c>
+      <c r="E2723" t="n">
+        <v>5.59999990463257</v>
+      </c>
+      <c r="F2723" t="n">
+        <v>5.48000001907349</v>
+      </c>
+      <c r="G2723" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/MARR.MI.xlsx
+++ b/data/MARR.MI.xlsx
@@ -421,7 +421,7 @@
         <v>18.6599998474121</v>
       </c>
       <c r="G2" t="n">
-        <v>12.678092956543</v>
+        <v>12.6780939102173</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>18.4400005340576</v>
       </c>
       <c r="G3" t="n">
-        <v>12.5286197662354</v>
+        <v>12.528618812561</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>18.2900009155273</v>
       </c>
       <c r="G4" t="n">
-        <v>12.4267044067383</v>
+        <v>12.4267063140869</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>18.0300006866455</v>
       </c>
       <c r="G5" t="n">
-        <v>12.2500562667847</v>
+        <v>12.2500524520874</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>17.9699993133545</v>
       </c>
       <c r="G6" t="n">
-        <v>12.2092876434326</v>
+        <v>12.2092885971069</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>17.5599994659424</v>
       </c>
       <c r="G8" t="n">
-        <v>11.9307222366333</v>
+        <v>11.9307231903076</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>17.6700000762939</v>
       </c>
       <c r="G9" t="n">
-        <v>12.0054597854614</v>
+        <v>12.0054607391357</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>17.2600002288818</v>
       </c>
       <c r="G10" t="n">
-        <v>11.7268972396851</v>
+        <v>11.7268962860107</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>16.6299991607666</v>
       </c>
       <c r="G12" t="n">
-        <v>11.2988567352295</v>
+        <v>11.2988557815552</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>16.7700004577637</v>
       </c>
       <c r="G13" t="n">
-        <v>11.3939781188965</v>
+        <v>11.3939771652222</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>16.1599998474121</v>
       </c>
       <c r="G14" t="n">
-        <v>10.9795265197754</v>
+        <v>10.9795274734497</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>17.8099994659424</v>
       </c>
       <c r="G16" t="n">
-        <v>12.1005783081055</v>
+        <v>12.1005792617798</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G19" t="n">
-        <v>11.8356018066406</v>
+        <v>11.8356056213379</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G21" t="n">
-        <v>11.9918718338013</v>
+        <v>11.9918727874756</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>17.7299995422363</v>
       </c>
       <c r="G23" t="n">
-        <v>12.0462245941162</v>
+        <v>12.0462265014648</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>17.1100006103516</v>
       </c>
       <c r="G24" t="n">
-        <v>11.624981880188</v>
+        <v>11.6249828338623</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>17.3600006103516</v>
       </c>
       <c r="G25" t="n">
-        <v>11.7948408126831</v>
+        <v>11.7948389053345</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>15.8900003433228</v>
       </c>
       <c r="G28" t="n">
-        <v>10.7960834503174</v>
+        <v>10.7960815429688</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>16.0799999237061</v>
       </c>
       <c r="G30" t="n">
-        <v>10.9251737594604</v>
+        <v>10.9251728057861</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>16.1599998474121</v>
       </c>
       <c r="G31" t="n">
-        <v>10.9795265197754</v>
+        <v>10.9795274734497</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>16.7099990844727</v>
       </c>
       <c r="G34" t="n">
-        <v>11.3532104492188</v>
+        <v>11.3532094955444</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>16.9300003051758</v>
       </c>
       <c r="G35" t="n">
-        <v>11.5026845932007</v>
+        <v>11.502685546875</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G36" t="n">
-        <v>11.6861305236816</v>
+        <v>11.686131477356</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>17.7299995422363</v>
       </c>
       <c r="G38" t="n">
-        <v>12.0462245941162</v>
+        <v>12.0462265014648</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>17.4899997711182</v>
       </c>
       <c r="G39" t="n">
-        <v>11.8831615447998</v>
+        <v>11.8831634521484</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G41" t="n">
-        <v>12.1956987380981</v>
+        <v>12.1956996917725</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>18.2600002288818</v>
       </c>
       <c r="G43" t="n">
-        <v>12.4063205718994</v>
+        <v>12.4063196182251</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G44" t="n">
-        <v>12.1956987380981</v>
+        <v>12.1956996917725</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>18.1399993896484</v>
       </c>
       <c r="G46" t="n">
-        <v>12.3247890472412</v>
+        <v>12.3247909545898</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>17.8799991607666</v>
       </c>
       <c r="G47" t="n">
-        <v>12.1481380462646</v>
+        <v>12.1481399536133</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>17.4799995422363</v>
       </c>
       <c r="G48" t="n">
-        <v>11.8763694763184</v>
+        <v>11.876368522644</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>17.4799995422363</v>
       </c>
       <c r="G49" t="n">
-        <v>11.8763694763184</v>
+        <v>11.876368522644</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>16.7600002288818</v>
       </c>
       <c r="G50" t="n">
-        <v>11.3871831893921</v>
+        <v>11.3871812820435</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G51" t="n">
-        <v>11.6521587371826</v>
+        <v>11.652156829834</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>17.5799999237061</v>
       </c>
       <c r="G52" t="n">
-        <v>11.9443120956421</v>
+        <v>11.9443111419678</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>17.7800006866455</v>
       </c>
       <c r="G53" t="n">
-        <v>12.0801963806152</v>
+        <v>12.0801982879639</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>17.6200008392334</v>
       </c>
       <c r="G54" t="n">
-        <v>11.9714918136597</v>
+        <v>11.9714889526367</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>17.8600006103516</v>
       </c>
       <c r="G56" t="n">
-        <v>12.1345510482788</v>
+        <v>12.1345520019531</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>17.5799999237061</v>
       </c>
       <c r="G57" t="n">
-        <v>11.9443120956421</v>
+        <v>11.9443111419678</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G58" t="n">
-        <v>11.7404823303223</v>
+        <v>11.7404842376709</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>17.1299991607666</v>
       </c>
       <c r="G59" t="n">
-        <v>11.6385688781738</v>
+        <v>11.6385698318481</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>17.6200008392334</v>
       </c>
       <c r="G60" t="n">
-        <v>11.9714918136597</v>
+        <v>11.9714889526367</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G61" t="n">
-        <v>11.9579010009766</v>
+        <v>11.9579019546509</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>18.25</v>
       </c>
       <c r="G64" t="n">
-        <v>12.3995275497437</v>
+        <v>12.399528503418</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>18.4099998474121</v>
       </c>
       <c r="G65" t="n">
-        <v>12.5082349777222</v>
+        <v>12.5082359313965</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G67" t="n">
-        <v>12.3315868377686</v>
+        <v>12.3315839767456</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G68" t="n">
-        <v>12.433497428894</v>
+        <v>12.4334983825684</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G70" t="n">
-        <v>12.433497428894</v>
+        <v>12.4334983825684</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>18.2600002288818</v>
       </c>
       <c r="G74" t="n">
-        <v>12.4063205718994</v>
+        <v>12.4063196182251</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>18.5200004577637</v>
       </c>
       <c r="G75" t="n">
-        <v>12.5829744338989</v>
+        <v>12.5829734802246</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G76" t="n">
-        <v>12.3315868377686</v>
+        <v>12.3315839767456</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G77" t="n">
-        <v>12.3315868377686</v>
+        <v>12.3315839767456</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>18.0400009155273</v>
       </c>
       <c r="G78" t="n">
-        <v>12.2568492889404</v>
+        <v>12.2568502426147</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G79" t="n">
-        <v>12.1617259979248</v>
+        <v>12.1617279052734</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>17.75</v>
       </c>
       <c r="G81" t="n">
-        <v>12.0598154067993</v>
+        <v>12.0598134994507</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>18.1200008392334</v>
       </c>
       <c r="G82" t="n">
-        <v>12.3112030029297</v>
+        <v>12.311203956604</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>18.1800003051758</v>
       </c>
       <c r="G83" t="n">
-        <v>12.3519687652588</v>
+        <v>12.3519678115845</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>17.7700004577637</v>
       </c>
       <c r="G84" t="n">
-        <v>12.0734024047852</v>
+        <v>12.0734043121338</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>18.4300003051758</v>
       </c>
       <c r="G85" t="n">
-        <v>12.5218229293823</v>
+        <v>12.5218257904053</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>18.2299995422363</v>
       </c>
       <c r="G86" t="n">
-        <v>12.3859376907349</v>
+        <v>12.3859386444092</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>17.8199996948242</v>
       </c>
       <c r="G87" t="n">
-        <v>12.1073732376099</v>
+        <v>12.1073741912842</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>17.8899993896484</v>
       </c>
       <c r="G88" t="n">
-        <v>12.154935836792</v>
+        <v>12.1549339294434</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>18.0300006866455</v>
       </c>
       <c r="G92" t="n">
-        <v>12.2500562667847</v>
+        <v>12.2500524520874</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>17.75</v>
       </c>
       <c r="G94" t="n">
-        <v>12.0598154067993</v>
+        <v>12.0598134994507</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>17.6700000762939</v>
       </c>
       <c r="G96" t="n">
-        <v>12.0054597854614</v>
+        <v>12.0054607391357</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>17.8099994659424</v>
       </c>
       <c r="G97" t="n">
-        <v>12.1005783081055</v>
+        <v>12.1005792617798</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>17.5300006866455</v>
       </c>
       <c r="G98" t="n">
-        <v>11.9103412628174</v>
+        <v>11.9103403091431</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>17.6900005340576</v>
       </c>
       <c r="G99" t="n">
-        <v>12.0190486907959</v>
+        <v>12.0190477371216</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G100" t="n">
-        <v>12.2801780700684</v>
+        <v>12.280177116394</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>17.3899993896484</v>
       </c>
       <c r="G101" t="n">
-        <v>12.2731227874756</v>
+        <v>12.273120880127</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>17.7099990844727</v>
       </c>
       <c r="G102" t="n">
-        <v>12.4989633560181</v>
+        <v>12.4989624023438</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G103" t="n">
-        <v>12.491907119751</v>
+        <v>12.4919080734253</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>17.9400005340576</v>
       </c>
       <c r="G104" t="n">
-        <v>12.6612882614136</v>
+        <v>12.6612873077393</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>17.7199993133545</v>
       </c>
       <c r="G107" t="n">
-        <v>12.5060234069824</v>
+        <v>12.5060224533081</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>18</v>
       </c>
       <c r="G108" t="n">
-        <v>12.7036333084106</v>
+        <v>12.7036352157593</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>17.8600006103516</v>
       </c>
       <c r="G109" t="n">
-        <v>12.6048269271851</v>
+        <v>12.6048288345337</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>17.8600006103516</v>
       </c>
       <c r="G110" t="n">
-        <v>12.6048269271851</v>
+        <v>12.6048288345337</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>17.9400005340576</v>
       </c>
       <c r="G111" t="n">
-        <v>12.6612882614136</v>
+        <v>12.6612873077393</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>17.75</v>
       </c>
       <c r="G112" t="n">
-        <v>12.5271949768066</v>
+        <v>12.5271940231323</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>17.7299995422363</v>
       </c>
       <c r="G113" t="n">
-        <v>12.5130786895752</v>
+        <v>12.5130796432495</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>17.7399997711182</v>
       </c>
       <c r="G114" t="n">
-        <v>12.5201368331909</v>
+        <v>12.5201377868652</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G115" t="n">
-        <v>12.0684518814087</v>
+        <v>12.068452835083</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>17.2099990844727</v>
       </c>
       <c r="G116" t="n">
-        <v>12.1460847854614</v>
+        <v>12.1460828781128</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G118" t="n">
-        <v>11.6097106933594</v>
+        <v>11.6097097396851</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>17.1100006103516</v>
       </c>
       <c r="G120" t="n">
-        <v>12.0755109786987</v>
+        <v>12.0755100250244</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>17.1100006103516</v>
       </c>
       <c r="G121" t="n">
-        <v>12.0755109786987</v>
+        <v>12.0755100250244</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>17.0900001525879</v>
       </c>
       <c r="G122" t="n">
-        <v>12.0613956451416</v>
+        <v>12.0613946914673</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>17.4699993133545</v>
       </c>
       <c r="G123" t="n">
-        <v>12.3295812606812</v>
+        <v>12.3295822143555</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>16.6200008392334</v>
       </c>
       <c r="G124" t="n">
-        <v>11.7296895980835</v>
+        <v>11.7296886444092</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G125" t="n">
-        <v>11.10862159729</v>
+        <v>11.1086206436157</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>16.4099998474121</v>
       </c>
       <c r="G126" t="n">
-        <v>11.5814800262451</v>
+        <v>11.5814790725708</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>17.0100002288818</v>
       </c>
       <c r="G127" t="n">
-        <v>12.0049343109131</v>
+        <v>12.0049333572388</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>17.0100002288818</v>
       </c>
       <c r="G128" t="n">
-        <v>12.0049343109131</v>
+        <v>12.0049333572388</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>17.9300003051758</v>
       </c>
       <c r="G129" t="n">
-        <v>12.6542301177979</v>
+        <v>12.6542310714722</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>17.9400005340576</v>
       </c>
       <c r="G131" t="n">
-        <v>12.6612882614136</v>
+        <v>12.6612873077393</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>17.8099994659424</v>
       </c>
       <c r="G134" t="n">
-        <v>12.5695371627808</v>
+        <v>12.569540977478</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>17.9300003051758</v>
       </c>
       <c r="G135" t="n">
-        <v>12.6542301177979</v>
+        <v>12.6542310714722</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>18.3799991607666</v>
       </c>
       <c r="G136" t="n">
-        <v>12.9718217849731</v>
+        <v>12.9718227386475</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>18</v>
       </c>
       <c r="G137" t="n">
-        <v>12.7036333084106</v>
+        <v>12.7036352157593</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>18.0799999237061</v>
       </c>
       <c r="G140" t="n">
-        <v>12.7600946426392</v>
+        <v>12.7600936889648</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>18.0200004577637</v>
       </c>
       <c r="G141" t="n">
-        <v>12.7177486419678</v>
+        <v>12.7177495956421</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G142" t="n">
-        <v>12.9506511688232</v>
+        <v>12.9506492614746</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>18.3799991607666</v>
       </c>
       <c r="G143" t="n">
-        <v>12.9718217849731</v>
+        <v>12.9718227386475</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>18.7199993133545</v>
       </c>
       <c r="G144" t="n">
-        <v>13.2117776870728</v>
+        <v>13.2117795944214</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>18.3099994659424</v>
       </c>
       <c r="G145" t="n">
-        <v>12.922417640686</v>
+        <v>12.9224185943604</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G147" t="n">
-        <v>13.3035278320312</v>
+        <v>13.3035268783569</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>18.6700000762939</v>
       </c>
       <c r="G148" t="n">
-        <v>13.1764907836914</v>
+        <v>13.1764917373657</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>18.8099994659424</v>
       </c>
       <c r="G149" t="n">
-        <v>13.275297164917</v>
+        <v>13.2752952575684</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G150" t="n">
-        <v>13.3035278320312</v>
+        <v>13.3035268783569</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>18.3600006103516</v>
       </c>
       <c r="G151" t="n">
-        <v>12.957706451416</v>
+        <v>12.957709312439</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G152" t="n">
-        <v>13.1976633071899</v>
+        <v>13.1976652145386</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>18.0400009155273</v>
       </c>
       <c r="G155" t="n">
-        <v>12.7318639755249</v>
+        <v>12.7318658828735</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>18.2199993133545</v>
       </c>
       <c r="G156" t="n">
-        <v>12.8588981628418</v>
+        <v>12.8588991165161</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>17.8299999237061</v>
       </c>
       <c r="G159" t="n">
-        <v>12.5836544036865</v>
+        <v>12.5836553573608</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>17.9200000762939</v>
       </c>
       <c r="G160" t="n">
-        <v>12.6471738815308</v>
+        <v>12.6471729278564</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>17.6599998474121</v>
       </c>
       <c r="G161" t="n">
-        <v>12.463677406311</v>
+        <v>12.4636764526367</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>17.75</v>
       </c>
       <c r="G162" t="n">
-        <v>12.5271949768066</v>
+        <v>12.5271940231323</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>17.75</v>
       </c>
       <c r="G163" t="n">
-        <v>12.5271949768066</v>
+        <v>12.5271940231323</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G164" t="n">
-        <v>12.2801780700684</v>
+        <v>12.280177116394</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>17.4799995422363</v>
       </c>
       <c r="G165" t="n">
-        <v>12.3366403579712</v>
+        <v>12.3366384506226</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>17.5</v>
       </c>
       <c r="G166" t="n">
-        <v>12.3507566452026</v>
+        <v>12.350754737854</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G167" t="n">
-        <v>12.315468788147</v>
+        <v>12.3154668807983</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>17.6800003051758</v>
       </c>
       <c r="G168" t="n">
-        <v>12.4777927398682</v>
+        <v>12.4777917861938</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>17.75</v>
       </c>
       <c r="G169" t="n">
-        <v>12.5271949768066</v>
+        <v>12.5271940231323</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>17.2700004577637</v>
       </c>
       <c r="G171" t="n">
-        <v>12.1884307861328</v>
+        <v>12.1884326934814</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>17.3899993896484</v>
       </c>
       <c r="G172" t="n">
-        <v>12.2731227874756</v>
+        <v>12.273120880127</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>17.6399993896484</v>
       </c>
       <c r="G173" t="n">
-        <v>12.4495620727539</v>
+        <v>12.4495601654053</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>17.5100002288818</v>
       </c>
       <c r="G174" t="n">
-        <v>12.3578119277954</v>
+        <v>12.357813835144</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>17.6299991607666</v>
       </c>
       <c r="G175" t="n">
-        <v>12.4425020217896</v>
+        <v>12.4425029754639</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>17.9400005340576</v>
       </c>
       <c r="G176" t="n">
-        <v>12.6612882614136</v>
+        <v>12.6612873077393</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>17.8299999237061</v>
       </c>
       <c r="G177" t="n">
-        <v>12.5836544036865</v>
+        <v>12.5836553573608</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>17.5200004577637</v>
       </c>
       <c r="G178" t="n">
-        <v>12.3648700714111</v>
+        <v>12.3648710250854</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>17.25</v>
       </c>
       <c r="G180" t="n">
-        <v>12.17431640625</v>
+        <v>12.1743144989014</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G183" t="n">
-        <v>12.315468788147</v>
+        <v>12.3154668807983</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G184" t="n">
-        <v>12.2801780700684</v>
+        <v>12.280177116394</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>17.2900009155273</v>
       </c>
       <c r="G185" t="n">
-        <v>12.2025480270386</v>
+        <v>12.2025461196899</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>17.6599998474121</v>
       </c>
       <c r="G186" t="n">
-        <v>12.463677406311</v>
+        <v>12.4636764526367</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>17.7399997711182</v>
       </c>
       <c r="G187" t="n">
-        <v>12.5201368331909</v>
+        <v>12.5201377868652</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>17.6599998474121</v>
       </c>
       <c r="G188" t="n">
-        <v>12.463677406311</v>
+        <v>12.4636764526367</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>17.7399997711182</v>
       </c>
       <c r="G189" t="n">
-        <v>12.5201368331909</v>
+        <v>12.5201377868652</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>17.4699993133545</v>
       </c>
       <c r="G190" t="n">
-        <v>12.3295812606812</v>
+        <v>12.3295822143555</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>17.6200008392334</v>
       </c>
       <c r="G191" t="n">
-        <v>12.4354486465454</v>
+        <v>12.4354476928711</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G194" t="n">
-        <v>12.456618309021</v>
+        <v>12.4566202163696</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>17.75</v>
       </c>
       <c r="G195" t="n">
-        <v>12.5271949768066</v>
+        <v>12.5271940231323</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>17.8199996948242</v>
       </c>
       <c r="G196" t="n">
-        <v>12.5765972137451</v>
+        <v>12.5765991210938</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>17.7199993133545</v>
       </c>
       <c r="G197" t="n">
-        <v>12.5060234069824</v>
+        <v>12.5060224533081</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>17.6299991607666</v>
       </c>
       <c r="G198" t="n">
-        <v>12.4425020217896</v>
+        <v>12.4425029754639</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>17.5</v>
       </c>
       <c r="G199" t="n">
-        <v>12.3507566452026</v>
+        <v>12.350754737854</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>17.3199996948242</v>
       </c>
       <c r="G200" t="n">
-        <v>12.2237186431885</v>
+        <v>12.2237167358398</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>17.1399993896484</v>
       </c>
       <c r="G202" t="n">
-        <v>12.0966806411743</v>
+        <v>12.0966815948486</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G203" t="n">
-        <v>12.2378330230713</v>
+        <v>12.2378339767456</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G204" t="n">
-        <v>12.033164024353</v>
+        <v>12.0331630706787</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G206" t="n">
-        <v>12.0684518814087</v>
+        <v>12.068452835083</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>17.0400009155273</v>
       </c>
       <c r="G208" t="n">
-        <v>12.0261087417603</v>
+        <v>12.0261077880859</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>16.9400005340576</v>
       </c>
       <c r="G210" t="n">
-        <v>11.955530166626</v>
+        <v>11.9555320739746</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G211" t="n">
-        <v>11.8567237854004</v>
+        <v>11.8567247390747</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>16.7600002288818</v>
       </c>
       <c r="G212" t="n">
-        <v>11.8284959793091</v>
+        <v>11.8284940719604</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>16.7399997711182</v>
       </c>
       <c r="G213" t="n">
-        <v>11.8143796920776</v>
+        <v>11.8143787384033</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>16.7700004577637</v>
       </c>
       <c r="G215" t="n">
-        <v>11.8355522155762</v>
+        <v>11.8355531692505</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>16.5900001525879</v>
       </c>
       <c r="G216" t="n">
-        <v>11.708517074585</v>
+        <v>11.7085151672363</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G217" t="n">
-        <v>11.5744209289551</v>
+        <v>11.5744218826294</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G219" t="n">
-        <v>11.7579202651978</v>
+        <v>11.7579174041748</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>16.6200008392334</v>
       </c>
       <c r="G220" t="n">
-        <v>11.7296895980835</v>
+        <v>11.7296886444092</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G221" t="n">
-        <v>11.6097106933594</v>
+        <v>11.6097097396851</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>16.5599994659424</v>
       </c>
       <c r="G224" t="n">
-        <v>11.6873435974121</v>
+        <v>11.6873416900635</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>16</v>
       </c>
       <c r="G225" t="n">
-        <v>11.2921180725098</v>
+        <v>11.2921190261841</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>16.5100002288818</v>
       </c>
       <c r="G226" t="n">
-        <v>11.6520566940308</v>
+        <v>11.6520557403564</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G227" t="n">
-        <v>11.8567237854004</v>
+        <v>11.8567247390747</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>16.6900005340576</v>
       </c>
       <c r="G228" t="n">
-        <v>11.7790908813477</v>
+        <v>11.779091835022</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G229" t="n">
-        <v>11.673228263855</v>
+        <v>11.6732292175293</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G231" t="n">
-        <v>11.7579202651978</v>
+        <v>11.7579174041748</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>16.5900001525879</v>
       </c>
       <c r="G232" t="n">
-        <v>11.708517074585</v>
+        <v>11.7085151672363</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>16.5699996948242</v>
       </c>
       <c r="G233" t="n">
-        <v>11.6943998336792</v>
+        <v>11.6944007873535</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>16.25</v>
       </c>
       <c r="G235" t="n">
-        <v>11.4685573577881</v>
+        <v>11.4685583114624</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>16.3700008392334</v>
       </c>
       <c r="G236" t="n">
-        <v>11.5532512664795</v>
+        <v>11.5532493591309</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>16.4799995422363</v>
       </c>
       <c r="G237" t="n">
-        <v>11.6308832168579</v>
+        <v>11.6308813095093</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>16.4599990844727</v>
       </c>
       <c r="G238" t="n">
-        <v>11.6167678833008</v>
+        <v>11.6167669296265</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G239" t="n">
-        <v>11.6097106933594</v>
+        <v>11.6097097396851</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>17</v>
       </c>
       <c r="G240" t="n">
-        <v>11.9978771209717</v>
+        <v>11.9978761672974</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>16.9300003051758</v>
       </c>
       <c r="G242" t="n">
-        <v>11.9484729766846</v>
+        <v>11.9484720230103</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>17.2099990844727</v>
       </c>
       <c r="G243" t="n">
-        <v>12.1460847854614</v>
+        <v>12.1460828781128</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>17</v>
       </c>
       <c r="G244" t="n">
-        <v>11.9978771209717</v>
+        <v>11.9978761672974</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>17.4899997711182</v>
       </c>
       <c r="G246" t="n">
-        <v>12.343695640564</v>
+        <v>12.3436975479126</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>17.3899993896484</v>
       </c>
       <c r="G247" t="n">
-        <v>12.2731227874756</v>
+        <v>12.273120880127</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G249" t="n">
-        <v>12.315468788147</v>
+        <v>12.3154668807983</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>17.5400009155273</v>
       </c>
       <c r="G250" t="n">
-        <v>12.3789863586426</v>
+        <v>12.3789873123169</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G251" t="n">
-        <v>12.2448902130127</v>
+        <v>12.2448921203613</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>17.5100002288818</v>
       </c>
       <c r="G252" t="n">
-        <v>12.3578119277954</v>
+        <v>12.357813835144</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>17.5799999237061</v>
       </c>
       <c r="G254" t="n">
-        <v>12.4072170257568</v>
+        <v>12.4072160720825</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>17.4799995422363</v>
       </c>
       <c r="G256" t="n">
-        <v>12.3366403579712</v>
+        <v>12.3366384506226</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G257" t="n">
-        <v>12.2448902130127</v>
+        <v>12.2448921203613</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>17.3899993896484</v>
       </c>
       <c r="G258" t="n">
-        <v>12.2731227874756</v>
+        <v>12.273120880127</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>17.5400009155273</v>
       </c>
       <c r="G259" t="n">
-        <v>12.3789863586426</v>
+        <v>12.3789873123169</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>17.4799995422363</v>
       </c>
       <c r="G260" t="n">
-        <v>12.3366403579712</v>
+        <v>12.3366384506226</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>17.5900001525879</v>
       </c>
       <c r="G261" t="n">
-        <v>12.4142723083496</v>
+        <v>12.4142732620239</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>17.6700000762939</v>
       </c>
       <c r="G262" t="n">
-        <v>12.4707326889038</v>
+        <v>12.4707336425781</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G263" t="n">
-        <v>12.456618309021</v>
+        <v>12.4566202163696</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>17.6599998474121</v>
       </c>
       <c r="G264" t="n">
-        <v>12.463677406311</v>
+        <v>12.4636764526367</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>17.3199996948242</v>
       </c>
       <c r="G266" t="n">
-        <v>12.2237186431885</v>
+        <v>12.2237167358398</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>17.5</v>
       </c>
       <c r="G267" t="n">
-        <v>12.3507566452026</v>
+        <v>12.350754737854</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>17.75</v>
       </c>
       <c r="G269" t="n">
-        <v>12.5271949768066</v>
+        <v>12.5271940231323</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G270" t="n">
-        <v>12.633056640625</v>
+        <v>12.6330575942993</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>17.8799991607666</v>
       </c>
       <c r="G271" t="n">
-        <v>12.6189403533936</v>
+        <v>12.6189432144165</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>18.3799991607666</v>
       </c>
       <c r="G272" t="n">
-        <v>12.9718217849731</v>
+        <v>12.9718227386475</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>18.5200004577637</v>
       </c>
       <c r="G273" t="n">
-        <v>13.0706300735474</v>
+        <v>13.070629119873</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>18.5900001525879</v>
       </c>
       <c r="G274" t="n">
-        <v>13.1200313568115</v>
+        <v>13.1200323104858</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>17.8500003814697</v>
       </c>
       <c r="G278" t="n">
-        <v>12.597770690918</v>
+        <v>12.5977697372437</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>17.9799995422363</v>
       </c>
       <c r="G279" t="n">
-        <v>12.6895170211792</v>
+        <v>12.6895179748535</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G281" t="n">
-        <v>12.6683444976807</v>
+        <v>12.668345451355</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>18.2199993133545</v>
       </c>
       <c r="G284" t="n">
-        <v>12.8588981628418</v>
+        <v>12.8588991165161</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>18.4099998474121</v>
       </c>
       <c r="G286" t="n">
-        <v>12.9929933547974</v>
+        <v>12.992995262146</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>18.2700004577637</v>
       </c>
       <c r="G291" t="n">
-        <v>12.8941879272461</v>
+        <v>12.8941898345947</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>18.4099998474121</v>
       </c>
       <c r="G292" t="n">
-        <v>12.9929933547974</v>
+        <v>12.992995262146</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>18.5100002288818</v>
       </c>
       <c r="G295" t="n">
-        <v>13.0635690689087</v>
+        <v>13.0635709762573</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>18.3899993896484</v>
       </c>
       <c r="G296" t="n">
-        <v>12.9788770675659</v>
+        <v>12.9788780212402</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>18.1200008392334</v>
       </c>
       <c r="G297" t="n">
-        <v>12.7883243560791</v>
+        <v>12.7883253097534</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>18.5599994659424</v>
       </c>
       <c r="G298" t="n">
-        <v>13.0988569259644</v>
+        <v>13.0988578796387</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>19.4500007629395</v>
       </c>
       <c r="G300" t="n">
-        <v>13.7269821166992</v>
+        <v>13.7269840240479</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>19.3899993896484</v>
       </c>
       <c r="G301" t="n">
-        <v>13.6846370697021</v>
+        <v>13.6846351623535</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>19.6299991607666</v>
       </c>
       <c r="G302" t="n">
-        <v>13.8540182113647</v>
+        <v>13.8540191650391</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>20</v>
       </c>
       <c r="G303" t="n">
-        <v>14.1151494979858</v>
+        <v>14.1151504516602</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>19.9500007629395</v>
       </c>
       <c r="G304" t="n">
-        <v>14.0798597335815</v>
+        <v>14.0798616409302</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>19.9599990844727</v>
       </c>
       <c r="G305" t="n">
-        <v>14.0869169235229</v>
+        <v>14.0869150161743</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G306" t="n">
-        <v>13.9739961624146</v>
+        <v>13.9739952087402</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>19.9500007629395</v>
       </c>
       <c r="G307" t="n">
-        <v>14.0798597335815</v>
+        <v>14.0798616409302</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>20.3099994659424</v>
       </c>
       <c r="G308" t="n">
-        <v>14.3339347839355</v>
+        <v>14.3339338302612</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>20.2199993133545</v>
       </c>
       <c r="G310" t="n">
-        <v>14.2704153060913</v>
+        <v>14.2704133987427</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>20.25</v>
       </c>
       <c r="G311" t="n">
-        <v>14.2915868759155</v>
+        <v>14.2915878295898</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>20.4200000762939</v>
       </c>
       <c r="G312" t="n">
-        <v>14.411563873291</v>
+        <v>14.4115686416626</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>20.3400001525879</v>
       </c>
       <c r="G314" t="n">
-        <v>14.3551054000854</v>
+        <v>14.3551063537598</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>20.5</v>
       </c>
       <c r="G315" t="n">
-        <v>14.4680271148682</v>
+        <v>14.4680280685425</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G316" t="n">
-        <v>14.7856178283691</v>
+        <v>14.7856197357178</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>21</v>
       </c>
       <c r="G317" t="n">
-        <v>14.8209075927734</v>
+        <v>14.8209066390991</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>20.75</v>
       </c>
       <c r="G318" t="n">
-        <v>14.6444654464722</v>
+        <v>14.6444692611694</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>20.3400001525879</v>
       </c>
       <c r="G321" t="n">
-        <v>14.3551054000854</v>
+        <v>14.3551063537598</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G322" t="n">
-        <v>14.3268766403198</v>
+        <v>14.3268728256226</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>20.7700004577637</v>
       </c>
       <c r="G324" t="n">
-        <v>14.6585836410522</v>
+        <v>14.6585826873779</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G325" t="n">
-        <v>14.5386028289795</v>
+        <v>14.5386037826538</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>20.8400001525879</v>
       </c>
       <c r="G327" t="n">
-        <v>14.707986831665</v>
+        <v>14.7079839706421</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G328" t="n">
-        <v>14.7503290176392</v>
+        <v>14.7503299713135</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>21</v>
       </c>
       <c r="G329" t="n">
-        <v>14.8209075927734</v>
+        <v>14.8209066390991</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>21.0200004577637</v>
       </c>
       <c r="G330" t="n">
-        <v>14.8350210189819</v>
+        <v>14.8350219726562</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>20.8199996948242</v>
       </c>
       <c r="G331" t="n">
-        <v>14.693868637085</v>
+        <v>14.6938695907593</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>21.9400005340576</v>
       </c>
       <c r="G333" t="n">
-        <v>15.4843187332153</v>
+        <v>15.4843149185181</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>21.5400009155273</v>
       </c>
       <c r="G334" t="n">
-        <v>15.202018737793</v>
+        <v>15.2020149230957</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>20.9699993133545</v>
       </c>
       <c r="G335" t="n">
-        <v>14.799732208252</v>
+        <v>14.7997312545776</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>21.75</v>
       </c>
       <c r="G336" t="n">
-        <v>15.3502244949341</v>
+        <v>15.3502216339111</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>21.8099994659424</v>
       </c>
       <c r="G337" t="n">
-        <v>15.3925666809082</v>
+        <v>15.3925676345825</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>21.7199993133545</v>
       </c>
       <c r="G338" t="n">
-        <v>15.3290519714355</v>
+        <v>15.3290529251099</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>21.7299995422363</v>
       </c>
       <c r="G339" t="n">
-        <v>15.336109161377</v>
+        <v>15.3361072540283</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>22.1700000762939</v>
       </c>
       <c r="G340" t="n">
-        <v>15.6466407775879</v>
+        <v>15.6466426849365</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>22.4200000762939</v>
       </c>
       <c r="G341" t="n">
-        <v>15.8230819702148</v>
+        <v>15.8230829238892</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>22.2600002288818</v>
       </c>
       <c r="G342" t="n">
-        <v>15.7101593017578</v>
+        <v>15.7101621627808</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>22.0699996948242</v>
       </c>
       <c r="G343" t="n">
-        <v>15.5760669708252</v>
+        <v>15.5760679244995</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>21.9699993133545</v>
       </c>
       <c r="G344" t="n">
-        <v>15.5054912567139</v>
+        <v>15.5054903030396</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>22.2299995422363</v>
       </c>
       <c r="G345" t="n">
-        <v>15.688985824585</v>
+        <v>15.6889886856079</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>22.8099994659424</v>
       </c>
       <c r="G346" t="n">
-        <v>16.0983257293701</v>
+        <v>16.0983276367188</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>22.4400005340576</v>
       </c>
       <c r="G347" t="n">
-        <v>15.8371963500977</v>
+        <v>15.8371982574463</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>22.3700008392334</v>
       </c>
       <c r="G348" t="n">
-        <v>15.7877931594849</v>
+        <v>15.7877941131592</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G351" t="n">
-        <v>16.126558303833</v>
+        <v>16.1265544891357</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G352" t="n">
-        <v>15.4560899734497</v>
+        <v>15.4560880661011</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>21.9699993133545</v>
       </c>
       <c r="G353" t="n">
-        <v>15.5054912567139</v>
+        <v>15.5054903030396</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>22.0499992370605</v>
       </c>
       <c r="G354" t="n">
-        <v>15.5619497299194</v>
+        <v>15.5619525909424</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>21.5799999237061</v>
       </c>
       <c r="G355" t="n">
-        <v>15.7295999526978</v>
+        <v>15.7295980453491</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G357" t="n">
-        <v>16.181510925293</v>
+        <v>16.1815147399902</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>22</v>
       </c>
       <c r="G358" t="n">
-        <v>16.0357341766357</v>
+        <v>16.0357360839844</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>21.6800003051758</v>
       </c>
       <c r="G359" t="n">
-        <v>15.8024883270264</v>
+        <v>15.8024864196777</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>21.5100002288818</v>
       </c>
       <c r="G360" t="n">
-        <v>15.6785774230957</v>
+        <v>15.6785755157471</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>21.6800003051758</v>
       </c>
       <c r="G362" t="n">
-        <v>15.8024883270264</v>
+        <v>15.8024864196777</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>22.0200004577637</v>
       </c>
       <c r="G363" t="n">
-        <v>16.0503120422363</v>
+        <v>16.050313949585</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>21.9099998474121</v>
       </c>
       <c r="G364" t="n">
-        <v>15.9701347351074</v>
+        <v>15.9701328277588</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>21.6900005340576</v>
       </c>
       <c r="G365" t="n">
-        <v>15.8097763061523</v>
+        <v>15.8097743988037</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G368" t="n">
-        <v>16.181510925293</v>
+        <v>16.1815147399902</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>21.6200008392334</v>
       </c>
       <c r="G371" t="n">
-        <v>15.7587556838989</v>
+        <v>15.7587518692017</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>21.6599998474121</v>
       </c>
       <c r="G373" t="n">
-        <v>15.7879095077515</v>
+        <v>15.7879104614258</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>21.6399993896484</v>
       </c>
       <c r="G376" t="n">
-        <v>15.7733297348022</v>
+        <v>15.7733335494995</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>21.4300003051758</v>
       </c>
       <c r="G378" t="n">
-        <v>15.6202611923218</v>
+        <v>15.6202630996704</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>21.6100006103516</v>
       </c>
       <c r="G380" t="n">
-        <v>15.7514677047729</v>
+        <v>15.7514638900757</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>21.5100002288818</v>
       </c>
       <c r="G381" t="n">
-        <v>15.6785774230957</v>
+        <v>15.6785755157471</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>20.8099994659424</v>
       </c>
       <c r="G384" t="n">
-        <v>15.1683464050293</v>
+        <v>15.1683483123779</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G385" t="n">
-        <v>15.161060333252</v>
+        <v>15.1610565185547</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G386" t="n">
-        <v>15.161060333252</v>
+        <v>15.1610565185547</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>21</v>
       </c>
       <c r="G389" t="n">
-        <v>15.3068389892578</v>
+        <v>15.3068370819092</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>20.6900005340576</v>
       </c>
       <c r="G391" t="n">
-        <v>15.0808811187744</v>
+        <v>15.0808792114258</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>21</v>
       </c>
       <c r="G392" t="n">
-        <v>15.3068389892578</v>
+        <v>15.3068370819092</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G393" t="n">
-        <v>15.452615737915</v>
+        <v>15.4526176452637</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>21.3299999237061</v>
       </c>
       <c r="G394" t="n">
-        <v>15.5473747253418</v>
+        <v>15.5473728179932</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>22</v>
       </c>
       <c r="G397" t="n">
-        <v>16.0357341766357</v>
+        <v>16.0357360839844</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G398" t="n">
-        <v>16.2544002532959</v>
+        <v>16.2544040679932</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>22.0599994659424</v>
       </c>
       <c r="G399" t="n">
-        <v>16.0794677734375</v>
+        <v>16.0794696807861</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>22.3700008392334</v>
       </c>
       <c r="G402" t="n">
-        <v>16.3054256439209</v>
+        <v>16.3054275512695</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>21.7700004577637</v>
       </c>
       <c r="G404" t="n">
-        <v>15.8680868148804</v>
+        <v>15.868088722229</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>21.6200008392334</v>
       </c>
       <c r="G405" t="n">
-        <v>15.7587556838989</v>
+        <v>15.7587518692017</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>21.5799999237061</v>
       </c>
       <c r="G406" t="n">
-        <v>15.7295999526978</v>
+        <v>15.7295980453491</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>21.6900005340576</v>
       </c>
       <c r="G407" t="n">
-        <v>15.8097763061523</v>
+        <v>15.8097743988037</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>21.7700004577637</v>
       </c>
       <c r="G411" t="n">
-        <v>15.8680868148804</v>
+        <v>15.868088722229</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>21.4099998474121</v>
       </c>
       <c r="G413" t="n">
-        <v>15.6056852340698</v>
+        <v>15.6056871414185</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>21.3199996948242</v>
       </c>
       <c r="G414" t="n">
-        <v>15.5400829315186</v>
+        <v>15.5400867462158</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G415" t="n">
-        <v>15.817066192627</v>
+        <v>15.8170642852783</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>21.3600006103516</v>
       </c>
       <c r="G417" t="n">
-        <v>15.5692386627197</v>
+        <v>15.5692405700684</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>21.1900005340576</v>
       </c>
       <c r="G418" t="n">
-        <v>15.4453277587891</v>
+        <v>15.4453296661377</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>21.2099990844727</v>
       </c>
       <c r="G419" t="n">
-        <v>15.4599056243896</v>
+        <v>15.459903717041</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>21.3600006103516</v>
       </c>
       <c r="G420" t="n">
-        <v>15.5692386627197</v>
+        <v>15.5692405700684</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>20.9899997711182</v>
       </c>
       <c r="G422" t="n">
-        <v>15.2995471954346</v>
+        <v>15.2995491027832</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>20.7700004577637</v>
       </c>
       <c r="G423" t="n">
-        <v>15.1391925811768</v>
+        <v>15.1391916275024</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>20.6499996185303</v>
       </c>
       <c r="G424" t="n">
-        <v>15.0517225265503</v>
+        <v>15.0517244338989</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>20.6299991607666</v>
       </c>
       <c r="G425" t="n">
-        <v>15.037145614624</v>
+        <v>15.0371437072754</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>21.2299995422363</v>
       </c>
       <c r="G428" t="n">
-        <v>15.4744844436646</v>
+        <v>15.4744815826416</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>21.4799995422363</v>
       </c>
       <c r="G430" t="n">
-        <v>15.6567068099976</v>
+        <v>15.6567087173462</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>21.4599990844727</v>
       </c>
       <c r="G431" t="n">
-        <v>15.6421308517456</v>
+        <v>15.642128944397</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>21.5100002288818</v>
       </c>
       <c r="G432" t="n">
-        <v>15.6785774230957</v>
+        <v>15.6785755157471</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G434" t="n">
-        <v>15.9628467559814</v>
+        <v>15.9628448486328</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>22.0499992370605</v>
       </c>
       <c r="G435" t="n">
-        <v>16.0721778869629</v>
+        <v>16.0721797943115</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>21.9200000762939</v>
       </c>
       <c r="G438" t="n">
-        <v>15.9774227142334</v>
+        <v>15.9774208068848</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>22</v>
       </c>
       <c r="G439" t="n">
-        <v>16.0357341766357</v>
+        <v>16.0357360839844</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>22.0799999237061</v>
       </c>
       <c r="G441" t="n">
-        <v>16.0940475463867</v>
+        <v>16.0940456390381</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>22.0799999237061</v>
       </c>
       <c r="G442" t="n">
-        <v>16.0940475463867</v>
+        <v>16.0940456390381</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G445" t="n">
-        <v>16.181510925293</v>
+        <v>16.1815147399902</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>22.3400001525879</v>
       </c>
       <c r="G446" t="n">
-        <v>16.2835578918457</v>
+        <v>16.2835597991943</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>22.3700008392334</v>
       </c>
       <c r="G447" t="n">
-        <v>16.3054256439209</v>
+        <v>16.3054275512695</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G448" t="n">
-        <v>16.2544002532959</v>
+        <v>16.2544040679932</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>22.4699993133545</v>
       </c>
       <c r="G450" t="n">
-        <v>16.3783168792725</v>
+        <v>16.3783149719238</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>22.7099990844727</v>
       </c>
       <c r="G452" t="n">
-        <v>16.5532493591309</v>
+        <v>16.5532512664795</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>22.5900001525879</v>
       </c>
       <c r="G454" t="n">
-        <v>16.4657802581787</v>
+        <v>16.465784072876</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>22.9200000762939</v>
       </c>
       <c r="G455" t="n">
-        <v>16.70631980896</v>
+        <v>16.7063179016113</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>22.7299995422363</v>
       </c>
       <c r="G456" t="n">
-        <v>16.5678253173828</v>
+        <v>16.5678291320801</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>22.6900005340576</v>
       </c>
       <c r="G457" t="n">
-        <v>16.5386714935303</v>
+        <v>16.5386734008789</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>23.4200000762939</v>
       </c>
       <c r="G459" t="n">
-        <v>17.0707702636719</v>
+        <v>17.0707664489746</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>22.7800006866455</v>
       </c>
       <c r="G461" t="n">
-        <v>16.6042747497559</v>
+        <v>16.6042728424072</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>22.6599998474121</v>
       </c>
       <c r="G464" t="n">
-        <v>16.5168037414551</v>
+        <v>16.5168075561523</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>22.3899993896484</v>
       </c>
       <c r="G465" t="n">
-        <v>16.3200054168701</v>
+        <v>16.3200035095215</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>22.1299991607666</v>
       </c>
       <c r="G466" t="n">
-        <v>16.1304893493652</v>
+        <v>16.1304912567139</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>22.1700000762939</v>
       </c>
       <c r="G469" t="n">
-        <v>16.1596450805664</v>
+        <v>16.159646987915</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>22</v>
       </c>
       <c r="G472" t="n">
-        <v>16.0357341766357</v>
+        <v>16.0357360839844</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G473" t="n">
-        <v>16.1086235046387</v>
+        <v>16.1086254119873</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>21.6399993896484</v>
       </c>
       <c r="G475" t="n">
-        <v>15.7733297348022</v>
+        <v>15.7733335494995</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>21.4899997711182</v>
       </c>
       <c r="G476" t="n">
-        <v>15.6639976501465</v>
+        <v>15.6639966964722</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>21.3799991607666</v>
       </c>
       <c r="G477" t="n">
-        <v>15.5838165283203</v>
+        <v>15.5838184356689</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G478" t="n">
-        <v>15.4161701202393</v>
+        <v>15.4161720275879</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>20.75</v>
       </c>
       <c r="G479" t="n">
-        <v>15.1246118545532</v>
+        <v>15.1246156692505</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>20.4699993133545</v>
       </c>
       <c r="G480" t="n">
-        <v>14.9205207824707</v>
+        <v>14.9205236434937</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G481" t="n">
-        <v>15.0152778625488</v>
+        <v>15.0152788162231</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>21.3199996948242</v>
       </c>
       <c r="G482" t="n">
-        <v>15.5400829315186</v>
+        <v>15.5400867462158</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G483" t="n">
-        <v>15.2703924179077</v>
+        <v>15.270393371582</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>21.7700004577637</v>
       </c>
       <c r="G485" t="n">
-        <v>15.8680868148804</v>
+        <v>15.868088722229</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>21.5100002288818</v>
       </c>
       <c r="G488" t="n">
-        <v>15.6785774230957</v>
+        <v>15.6785755157471</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>21.4099998474121</v>
       </c>
       <c r="G489" t="n">
-        <v>15.6056852340698</v>
+        <v>15.6056871414185</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>21.8199996948242</v>
       </c>
       <c r="G490" t="n">
-        <v>15.9045343399048</v>
+        <v>15.9045324325562</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>21.5799999237061</v>
       </c>
       <c r="G491" t="n">
-        <v>15.7295999526978</v>
+        <v>15.7295980453491</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G494" t="n">
-        <v>15.9628467559814</v>
+        <v>15.9628448486328</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>21.9400005340576</v>
       </c>
       <c r="G495" t="n">
-        <v>15.9920015335083</v>
+        <v>15.9919967651367</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>21.8899993896484</v>
       </c>
       <c r="G497" t="n">
-        <v>15.9555549621582</v>
+        <v>15.9555568695068</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>21.6599998474121</v>
       </c>
       <c r="G498" t="n">
-        <v>15.7879095077515</v>
+        <v>15.7879104614258</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>21.3799991607666</v>
       </c>
       <c r="G501" t="n">
-        <v>15.5838165283203</v>
+        <v>15.5838184356689</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G502" t="n">
-        <v>15.4161701202393</v>
+        <v>15.4161720275879</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>21</v>
       </c>
       <c r="G504" t="n">
-        <v>15.3068389892578</v>
+        <v>15.3068370819092</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>20.7600002288818</v>
       </c>
       <c r="G505" t="n">
-        <v>15.1319036483765</v>
+        <v>15.1318998336792</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>21.2900009155273</v>
       </c>
       <c r="G506" t="n">
-        <v>15.5182199478149</v>
+        <v>15.5182180404663</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>21.3600006103516</v>
       </c>
       <c r="G507" t="n">
-        <v>15.5692386627197</v>
+        <v>15.5692405700684</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>21.2800006866455</v>
       </c>
       <c r="G508" t="n">
-        <v>15.5109281539917</v>
+        <v>15.5109300613403</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>21.6599998474121</v>
       </c>
       <c r="G509" t="n">
-        <v>15.7879095077515</v>
+        <v>15.7879104614258</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>21.6700000762939</v>
       </c>
       <c r="G510" t="n">
-        <v>15.7951955795288</v>
+        <v>15.7951974868774</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>21.9200000762939</v>
       </c>
       <c r="G515" t="n">
-        <v>15.9774227142334</v>
+        <v>15.9774208068848</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>21.9200000762939</v>
       </c>
       <c r="G516" t="n">
-        <v>15.9774227142334</v>
+        <v>15.9774208068848</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>21.3600006103516</v>
       </c>
       <c r="G519" t="n">
-        <v>15.5692386627197</v>
+        <v>15.5692405700684</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>22.0200004577637</v>
       </c>
       <c r="G521" t="n">
-        <v>16.0503120422363</v>
+        <v>16.050313949585</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G522" t="n">
-        <v>16.181510925293</v>
+        <v>16.1815147399902</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>22.3400001525879</v>
       </c>
       <c r="G523" t="n">
-        <v>16.2835578918457</v>
+        <v>16.2835597991943</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>22.4200000762939</v>
       </c>
       <c r="G524" t="n">
-        <v>16.3418712615967</v>
+        <v>16.3418731689453</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>22.6200008392334</v>
       </c>
       <c r="G526" t="n">
-        <v>16.4876518249512</v>
+        <v>16.4876499176025</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>22.8799991607666</v>
       </c>
       <c r="G528" t="n">
-        <v>16.6771640777588</v>
+        <v>16.6771621704102</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>22.4200000762939</v>
       </c>
       <c r="G531" t="n">
-        <v>16.3418712615967</v>
+        <v>16.3418731689453</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>22.3199996948242</v>
       </c>
       <c r="G532" t="n">
-        <v>16.2689838409424</v>
+        <v>16.2689819335938</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>22.6399993896484</v>
       </c>
       <c r="G534" t="n">
-        <v>16.5022296905518</v>
+        <v>16.5022277832031</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>22.0599994659424</v>
       </c>
       <c r="G535" t="n">
-        <v>16.0794677734375</v>
+        <v>16.0794696807861</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>21.6599998474121</v>
       </c>
       <c r="G536" t="n">
-        <v>15.7879095077515</v>
+        <v>15.7879104614258</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>21.9599990844727</v>
       </c>
       <c r="G538" t="n">
-        <v>16.0065784454346</v>
+        <v>16.0065803527832</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>21.1399993896484</v>
       </c>
       <c r="G539" t="n">
-        <v>15.408881187439</v>
+        <v>15.4088821411133</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>21</v>
       </c>
       <c r="G540" t="n">
-        <v>15.3068389892578</v>
+        <v>15.3068370819092</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>20.7600002288818</v>
       </c>
       <c r="G541" t="n">
-        <v>15.1319036483765</v>
+        <v>15.1318998336792</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>21</v>
       </c>
       <c r="G542" t="n">
-        <v>15.3068389892578</v>
+        <v>15.3068370819092</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>21.0799999237061</v>
       </c>
       <c r="G543" t="n">
-        <v>15.3651494979858</v>
+        <v>15.3651475906372</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>21</v>
       </c>
       <c r="G544" t="n">
-        <v>15.3068389892578</v>
+        <v>15.3068370819092</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>21.6800003051758</v>
       </c>
       <c r="G547" t="n">
-        <v>15.8024883270264</v>
+        <v>15.8024864196777</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>21.4799995422363</v>
       </c>
       <c r="G548" t="n">
-        <v>15.6567068099976</v>
+        <v>15.6567087173462</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>21.4599990844727</v>
       </c>
       <c r="G549" t="n">
-        <v>15.6421308517456</v>
+        <v>15.642128944397</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>21.5799999237061</v>
       </c>
       <c r="G550" t="n">
-        <v>15.7295999526978</v>
+        <v>15.7295980453491</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>22.0200004577637</v>
       </c>
       <c r="G552" t="n">
-        <v>16.0503120422363</v>
+        <v>16.050313949585</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>21.8600006103516</v>
       </c>
       <c r="G553" t="n">
-        <v>15.9336891174316</v>
+        <v>15.933687210083</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>21.5400009155273</v>
       </c>
       <c r="G554" t="n">
-        <v>15.7004451751709</v>
+        <v>15.7004413604736</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>21.1399993896484</v>
       </c>
       <c r="G555" t="n">
-        <v>15.408881187439</v>
+        <v>15.4088821411133</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>21</v>
       </c>
       <c r="G556" t="n">
-        <v>15.3068389892578</v>
+        <v>15.3068370819092</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G558" t="n">
-        <v>15.3797273635864</v>
+        <v>15.3797254562378</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G559" t="n">
-        <v>15.9628467559814</v>
+        <v>15.9628448486328</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>22.5400009155273</v>
       </c>
       <c r="G561" t="n">
-        <v>16.4293384552002</v>
+        <v>16.4293403625488</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>23.8600006103516</v>
       </c>
       <c r="G564" t="n">
-        <v>17.3914833068848</v>
+        <v>17.3914852142334</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>23.7800006866455</v>
       </c>
       <c r="G565" t="n">
-        <v>17.3331737518311</v>
+        <v>17.3331718444824</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>24.7600002288818</v>
       </c>
       <c r="G567" t="n">
-        <v>18.0474910736084</v>
+        <v>18.0474891662598</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>24.5799999237061</v>
       </c>
       <c r="G568" t="n">
-        <v>17.9162902832031</v>
+        <v>17.9162883758545</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>24.1800003051758</v>
       </c>
       <c r="G570" t="n">
-        <v>17.6247291564941</v>
+        <v>17.6247310638428</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>24.1599998474121</v>
       </c>
       <c r="G571" t="n">
-        <v>17.6101493835449</v>
+        <v>17.6101531982422</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>24.1599998474121</v>
       </c>
       <c r="G572" t="n">
-        <v>17.6101493835449</v>
+        <v>17.6101531982422</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>24.2399997711182</v>
       </c>
       <c r="G573" t="n">
-        <v>17.6684627532959</v>
+        <v>17.6684646606445</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>24.1399993896484</v>
       </c>
       <c r="G574" t="n">
-        <v>17.5955715179443</v>
+        <v>17.595573425293</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G575" t="n">
-        <v>17.7121963500977</v>
+        <v>17.7121982574463</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G576" t="n">
-        <v>18.1495342254639</v>
+        <v>18.1495361328125</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>25.0200004577637</v>
       </c>
       <c r="G578" t="n">
-        <v>18.2370052337646</v>
+        <v>18.237003326416</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G580" t="n">
-        <v>18.4410934448242</v>
+        <v>18.4410953521729</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>24.7600002288818</v>
       </c>
       <c r="G581" t="n">
-        <v>18.0474910736084</v>
+        <v>18.0474891662598</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>25</v>
       </c>
       <c r="G582" t="n">
-        <v>18.2224254608154</v>
+        <v>18.2224273681641</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>24.7199993133545</v>
       </c>
       <c r="G585" t="n">
-        <v>18.0183353424072</v>
+        <v>18.0183334350586</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G586" t="n">
-        <v>18.1495342254639</v>
+        <v>18.1495361328125</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>24.8799991607666</v>
       </c>
       <c r="G589" t="n">
-        <v>18.1349582672119</v>
+        <v>18.1349544525146</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>24.8400001525879</v>
       </c>
       <c r="G590" t="n">
-        <v>18.1058025360107</v>
+        <v>18.1057987213135</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>24.8799991607666</v>
       </c>
       <c r="G591" t="n">
-        <v>18.1349582672119</v>
+        <v>18.1349544525146</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>24.8799991607666</v>
       </c>
       <c r="G593" t="n">
-        <v>18.1349582672119</v>
+        <v>18.1349544525146</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>25.0200004577637</v>
       </c>
       <c r="G594" t="n">
-        <v>18.2370052337646</v>
+        <v>18.237003326416</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>25.3400001525879</v>
       </c>
       <c r="G597" t="n">
-        <v>18.470251083374</v>
+        <v>18.4702529907227</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>24.7600002288818</v>
       </c>
       <c r="G604" t="n">
-        <v>18.0474910736084</v>
+        <v>18.0474891662598</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>24.1399993896484</v>
       </c>
       <c r="G605" t="n">
-        <v>17.5955715179443</v>
+        <v>17.595573425293</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>24.1399993896484</v>
       </c>
       <c r="G606" t="n">
-        <v>17.5955715179443</v>
+        <v>17.595573425293</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>23.4599990844727</v>
       </c>
       <c r="G607" t="n">
-        <v>17.0999221801758</v>
+        <v>17.0999240875244</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>23.7399997711182</v>
       </c>
       <c r="G608" t="n">
-        <v>17.3040180206299</v>
+        <v>17.3040142059326</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>23.4200000762939</v>
       </c>
       <c r="G609" t="n">
-        <v>17.0707702636719</v>
+        <v>17.0707664489746</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>23.4200000762939</v>
       </c>
       <c r="G610" t="n">
-        <v>17.0707702636719</v>
+        <v>17.0707664489746</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>23.3799991607666</v>
       </c>
       <c r="G611" t="n">
-        <v>17.0416145324707</v>
+        <v>17.0416126251221</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>23.3199996948242</v>
       </c>
       <c r="G612" t="n">
-        <v>16.9978790283203</v>
+        <v>16.9978771209717</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>22.7600002288818</v>
       </c>
       <c r="G613" t="n">
-        <v>17.1333789825439</v>
+        <v>17.1333808898926</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>23</v>
       </c>
       <c r="G615" t="n">
-        <v>17.3140468597412</v>
+        <v>17.3140487670898</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>23.3199996948242</v>
       </c>
       <c r="G617" t="n">
-        <v>17.5549392700195</v>
+        <v>17.5549373626709</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>23.1800003051758</v>
       </c>
       <c r="G618" t="n">
-        <v>17.4495487213135</v>
+        <v>17.4495506286621</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>23.1599998474121</v>
       </c>
       <c r="G621" t="n">
-        <v>17.4344959259033</v>
+        <v>17.4344940185547</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>22.7399997711182</v>
       </c>
       <c r="G622" t="n">
-        <v>17.1183242797852</v>
+        <v>17.1183261871338</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>23.0799999237061</v>
       </c>
       <c r="G623" t="n">
-        <v>17.3742733001709</v>
+        <v>17.3742713928223</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G624" t="n">
-        <v>17.615161895752</v>
+        <v>17.6151599884033</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G625" t="n">
-        <v>17.615161895752</v>
+        <v>17.6151599884033</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>23.0799999237061</v>
       </c>
       <c r="G629" t="n">
-        <v>17.3742733001709</v>
+        <v>17.3742713928223</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>22.7600002288818</v>
       </c>
       <c r="G632" t="n">
-        <v>17.1333789825439</v>
+        <v>17.1333808898926</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>22.4400005340576</v>
       </c>
       <c r="G635" t="n">
-        <v>16.8924884796143</v>
+        <v>16.8924903869629</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G638" t="n">
-        <v>16.862377166748</v>
+        <v>16.8623790740967</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>22.5400009155273</v>
       </c>
       <c r="G640" t="n">
-        <v>16.9677677154541</v>
+        <v>16.9677696228027</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>23.9799995422363</v>
       </c>
       <c r="G646" t="n">
-        <v>18.0517768859863</v>
+        <v>18.051778793335</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>24</v>
       </c>
       <c r="G647" t="n">
-        <v>18.0668315887451</v>
+        <v>18.0668334960938</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>23.8199996948242</v>
       </c>
       <c r="G648" t="n">
-        <v>17.9313316345215</v>
+        <v>17.9313335418701</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>23.6200008392334</v>
       </c>
       <c r="G649" t="n">
-        <v>17.7807750701904</v>
+        <v>17.7807769775391</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>23.2600002288818</v>
       </c>
       <c r="G651" t="n">
-        <v>17.5097732543945</v>
+        <v>17.5097713470459</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>23.8799991607666</v>
       </c>
       <c r="G652" t="n">
-        <v>17.9764976501465</v>
+        <v>17.9764995574951</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>23.1399993896484</v>
       </c>
       <c r="G656" t="n">
-        <v>17.4194355010986</v>
+        <v>17.4194393157959</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>23.3199996948242</v>
       </c>
       <c r="G657" t="n">
-        <v>17.5549392700195</v>
+        <v>17.5549373626709</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>23.2600002288818</v>
       </c>
       <c r="G662" t="n">
-        <v>17.5097732543945</v>
+        <v>17.5097713470459</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>24.1000003814697</v>
       </c>
       <c r="G663" t="n">
-        <v>18.142110824585</v>
+        <v>18.1421089172363</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>24.1000003814697</v>
       </c>
       <c r="G664" t="n">
-        <v>18.142110824585</v>
+        <v>18.1421089172363</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>24</v>
       </c>
       <c r="G668" t="n">
-        <v>18.0668315887451</v>
+        <v>18.0668334960938</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>23.9599990844727</v>
       </c>
       <c r="G669" t="n">
-        <v>18.0367202758789</v>
+        <v>18.0367221832275</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>23.8199996948242</v>
       </c>
       <c r="G670" t="n">
-        <v>17.9313316345215</v>
+        <v>17.9313335418701</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G671" t="n">
-        <v>17.9162731170654</v>
+        <v>17.9162769317627</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>23.9400005340576</v>
       </c>
       <c r="G672" t="n">
-        <v>18.0216674804688</v>
+        <v>18.0216655731201</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>23.8400001525879</v>
       </c>
       <c r="G673" t="n">
-        <v>17.9463882446289</v>
+        <v>17.9463901519775</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G675" t="n">
-        <v>18.2173881530762</v>
+        <v>18.2173900604248</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>23.8799991607666</v>
       </c>
       <c r="G676" t="n">
-        <v>17.9764976501465</v>
+        <v>17.9764995574951</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>24.3799991607666</v>
       </c>
       <c r="G680" t="n">
-        <v>18.3528900146484</v>
+        <v>18.3528919219971</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G681" t="n">
-        <v>18.2173881530762</v>
+        <v>18.2173900604248</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G682" t="n">
-        <v>18.2173881530762</v>
+        <v>18.2173900604248</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>24.2800006866455</v>
       </c>
       <c r="G683" t="n">
-        <v>18.2776145935059</v>
+        <v>18.2776126861572</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G691" t="n">
-        <v>19.2712898254395</v>
+        <v>19.2712879180908</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>25.3799991607666</v>
       </c>
       <c r="G692" t="n">
-        <v>19.105676651001</v>
+        <v>19.1056747436523</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>26.4200000762939</v>
       </c>
       <c r="G694" t="n">
-        <v>19.8885707855225</v>
+        <v>19.8885726928711</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>25.3600006103516</v>
       </c>
       <c r="G696" t="n">
-        <v>19.0906181335449</v>
+        <v>19.0906219482422</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>25.3799991607666</v>
       </c>
       <c r="G697" t="n">
-        <v>19.105676651001</v>
+        <v>19.1056747436523</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>25.6399993896484</v>
       </c>
       <c r="G698" t="n">
-        <v>19.301399230957</v>
+        <v>19.3014030456543</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>25.2399997711182</v>
       </c>
       <c r="G699" t="n">
-        <v>19.0002841949463</v>
+        <v>19.0002861022949</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>25.2399997711182</v>
       </c>
       <c r="G700" t="n">
-        <v>19.0002841949463</v>
+        <v>19.0002861022949</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>24.7399997711182</v>
       </c>
       <c r="G703" t="n">
-        <v>18.6238956451416</v>
+        <v>18.6238918304443</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>24.4599990844727</v>
       </c>
       <c r="G704" t="n">
-        <v>18.4131126403809</v>
+        <v>18.4131164550781</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G705" t="n">
-        <v>18.292667388916</v>
+        <v>18.2926692962646</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>23.5599994659424</v>
       </c>
       <c r="G706" t="n">
-        <v>17.7356090545654</v>
+        <v>17.7356052398682</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>23.4599990844727</v>
       </c>
       <c r="G707" t="n">
-        <v>17.660327911377</v>
+        <v>17.6603298187256</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>23.0200004577637</v>
       </c>
       <c r="G708" t="n">
-        <v>17.3291053771973</v>
+        <v>17.3291034698486</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>23</v>
       </c>
       <c r="G711" t="n">
-        <v>17.3140468597412</v>
+        <v>17.3140487670898</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>23.4799995422363</v>
       </c>
       <c r="G714" t="n">
-        <v>17.675386428833</v>
+        <v>17.6753845214844</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>23.0200004577637</v>
       </c>
       <c r="G715" t="n">
-        <v>17.3291053771973</v>
+        <v>17.3291034698486</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>22.2800006866455</v>
       </c>
       <c r="G717" t="n">
-        <v>16.772045135498</v>
+        <v>16.7720432281494</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>21.8400001525879</v>
       </c>
       <c r="G718" t="n">
-        <v>16.4408187866211</v>
+        <v>16.4408168792725</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>21.4599990844727</v>
       </c>
       <c r="G719" t="n">
-        <v>16.1547603607178</v>
+        <v>16.1547584533691</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>21.9799995422363</v>
       </c>
       <c r="G722" t="n">
-        <v>16.5462074279785</v>
+        <v>16.5462093353271</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>21.4599990844727</v>
       </c>
       <c r="G726" t="n">
-        <v>16.1547603607178</v>
+        <v>16.1547584533691</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>21.4599990844727</v>
       </c>
       <c r="G731" t="n">
-        <v>16.1547603607178</v>
+        <v>16.1547584533691</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>21.8600006103516</v>
       </c>
       <c r="G733" t="n">
-        <v>16.4558753967285</v>
+        <v>16.4558734893799</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>20.4799995422363</v>
       </c>
       <c r="G735" t="n">
-        <v>15.4170303344727</v>
+        <v>15.4170331954956</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>20.1599998474121</v>
       </c>
       <c r="G737" t="n">
-        <v>15.1761379241943</v>
+        <v>15.176139831543</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>20.1800003051758</v>
       </c>
       <c r="G738" t="n">
-        <v>15.1911954879761</v>
+        <v>15.1911973953247</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>19.3199996948242</v>
       </c>
       <c r="G739" t="n">
-        <v>14.5438003540039</v>
+        <v>14.5438013076782</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G740" t="n">
-        <v>14.4534673690796</v>
+        <v>14.4534664154053</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G741" t="n">
-        <v>14.7545795440674</v>
+        <v>14.7545804977417</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>19.3799991607666</v>
       </c>
       <c r="G742" t="n">
-        <v>14.5889654159546</v>
+        <v>14.5889682769775</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>19.8400001525879</v>
       </c>
       <c r="G745" t="n">
-        <v>14.9352474212646</v>
+        <v>14.9352502822876</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>20.2399997711182</v>
       </c>
       <c r="G749" t="n">
-        <v>15.2363634109497</v>
+        <v>15.2363615036011</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>20.6399993896484</v>
       </c>
       <c r="G751" t="n">
-        <v>15.5374755859375</v>
+        <v>15.5374774932861</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>20.8199996948242</v>
       </c>
       <c r="G752" t="n">
-        <v>15.6729764938354</v>
+        <v>15.6729784011841</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>21.6399993896484</v>
       </c>
       <c r="G756" t="n">
-        <v>16.2902603149414</v>
+        <v>16.29026222229</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>21.2199993133545</v>
       </c>
       <c r="G757" t="n">
-        <v>15.9740886688232</v>
+        <v>15.9740924835205</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G760" t="n">
-        <v>16.0343170166016</v>
+        <v>16.0343151092529</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>20.8400001525879</v>
       </c>
       <c r="G761" t="n">
-        <v>15.6880359649658</v>
+        <v>15.6880340576172</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>20.3400001525879</v>
       </c>
       <c r="G762" t="n">
-        <v>15.3116397857666</v>
+        <v>15.3116416931152</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G766" t="n">
-        <v>15.8837585449219</v>
+        <v>15.8837566375732</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>21.7600002288818</v>
       </c>
       <c r="G767" t="n">
-        <v>16.3805980682373</v>
+        <v>16.38059425354</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>21.4599990844727</v>
       </c>
       <c r="G768" t="n">
-        <v>16.1547603607178</v>
+        <v>16.1547584533691</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>21.1399993896484</v>
       </c>
       <c r="G773" t="n">
-        <v>15.9138698577881</v>
+        <v>15.9138679504395</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>20.9400005340576</v>
       </c>
       <c r="G777" t="n">
-        <v>15.7633104324341</v>
+        <v>15.7633142471313</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>20.9400005340576</v>
       </c>
       <c r="G778" t="n">
-        <v>15.7633104324341</v>
+        <v>15.7633142471313</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>21.2199993133545</v>
       </c>
       <c r="G780" t="n">
-        <v>15.9740886688232</v>
+        <v>15.9740924835205</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>20.6399993896484</v>
       </c>
       <c r="G782" t="n">
-        <v>15.5374755859375</v>
+        <v>15.5374774932861</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>20.8199996948242</v>
       </c>
       <c r="G783" t="n">
-        <v>15.6729764938354</v>
+        <v>15.6729784011841</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>20.8199996948242</v>
       </c>
       <c r="G784" t="n">
-        <v>15.6729764938354</v>
+        <v>15.6729784011841</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G786" t="n">
-        <v>15.6579236984253</v>
+        <v>15.657919883728</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>20.9599990844727</v>
       </c>
       <c r="G787" t="n">
-        <v>15.7783679962158</v>
+        <v>15.7783660888672</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>20.4200000762939</v>
       </c>
       <c r="G790" t="n">
-        <v>15.371862411499</v>
+        <v>15.3718643188477</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>19.9099998474121</v>
       </c>
       <c r="G791" t="n">
-        <v>14.987943649292</v>
+        <v>14.9879417419434</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>20.2800006866455</v>
       </c>
       <c r="G792" t="n">
-        <v>15.2664756774902</v>
+        <v>15.2664737701416</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G793" t="n">
-        <v>15.2815294265747</v>
+        <v>15.2815284729004</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>20.4799995422363</v>
       </c>
       <c r="G795" t="n">
-        <v>15.4170303344727</v>
+        <v>15.4170331954956</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G796" t="n">
-        <v>15.3568096160889</v>
+        <v>15.3568077087402</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>20.3600006103516</v>
       </c>
       <c r="G798" t="n">
-        <v>15.326696395874</v>
+        <v>15.3266973495483</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>20.3199996948242</v>
       </c>
       <c r="G799" t="n">
-        <v>15.2965860366821</v>
+        <v>15.2965841293335</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>19.9300003051758</v>
       </c>
       <c r="G800" t="n">
-        <v>15.0029993057251</v>
+        <v>15.0030002593994</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>21.1399993896484</v>
       </c>
       <c r="G803" t="n">
-        <v>15.9138698577881</v>
+        <v>15.9138679504395</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>20.4200000762939</v>
       </c>
       <c r="G804" t="n">
-        <v>15.371862411499</v>
+        <v>15.3718643188477</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>20.8400001525879</v>
       </c>
       <c r="G807" t="n">
-        <v>15.6880359649658</v>
+        <v>15.6880340576172</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>21.0200004577637</v>
       </c>
       <c r="G808" t="n">
-        <v>15.8235340118408</v>
+        <v>15.8235359191895</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>20.6399993896484</v>
       </c>
       <c r="G809" t="n">
-        <v>15.5374755859375</v>
+        <v>15.5374774932861</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>20.9400005340576</v>
       </c>
       <c r="G810" t="n">
-        <v>15.7633104324341</v>
+        <v>15.7633142471313</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>20.4200000762939</v>
       </c>
       <c r="G814" t="n">
-        <v>15.371862411499</v>
+        <v>15.3718643188477</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>20.6399993896484</v>
       </c>
       <c r="G815" t="n">
-        <v>15.5374755859375</v>
+        <v>15.5374774932861</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>20.7600002288818</v>
       </c>
       <c r="G817" t="n">
-        <v>15.6278104782104</v>
+        <v>15.6278085708618</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G818" t="n">
-        <v>15.8837585449219</v>
+        <v>15.8837566375732</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>20.7600002288818</v>
       </c>
       <c r="G819" t="n">
-        <v>15.6278104782104</v>
+        <v>15.6278085708618</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G820" t="n">
-        <v>15.6579236984253</v>
+        <v>15.657919883728</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>20.3600006103516</v>
       </c>
       <c r="G822" t="n">
-        <v>15.326696395874</v>
+        <v>15.3266973495483</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>20.2800006866455</v>
       </c>
       <c r="G824" t="n">
-        <v>15.2664756774902</v>
+        <v>15.2664737701416</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>20.3199996948242</v>
       </c>
       <c r="G825" t="n">
-        <v>15.2965860366821</v>
+        <v>15.2965841293335</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>20.2800006866455</v>
       </c>
       <c r="G826" t="n">
-        <v>15.2664756774902</v>
+        <v>15.2664737701416</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>20.6499996185303</v>
       </c>
       <c r="G828" t="n">
-        <v>15.5450029373169</v>
+        <v>15.5450048446655</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G837" t="n">
-        <v>15.2815294265747</v>
+        <v>15.2815284729004</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G839" t="n">
-        <v>15.1309757232666</v>
+        <v>15.1309719085693</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>20.75</v>
       </c>
       <c r="G841" t="n">
-        <v>15.6202812194824</v>
+        <v>15.6202850341797</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>20.75</v>
       </c>
       <c r="G842" t="n">
-        <v>15.6202812194824</v>
+        <v>15.6202850341797</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>20.8500003814697</v>
       </c>
       <c r="G843" t="n">
-        <v>15.6955633163452</v>
+        <v>15.6955614089966</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>21.6499996185303</v>
       </c>
       <c r="G846" t="n">
-        <v>16.2977886199951</v>
+        <v>16.2977867126465</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G848" t="n">
-        <v>15.8837585449219</v>
+        <v>15.8837566375732</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G849" t="n">
-        <v>15.8837585449219</v>
+        <v>15.8837566375732</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>21.3500003814697</v>
       </c>
       <c r="G851" t="n">
-        <v>16.0719547271729</v>
+        <v>16.0719528198242</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>21.3500003814697</v>
       </c>
       <c r="G853" t="n">
-        <v>16.0719547271729</v>
+        <v>16.0719528198242</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G855" t="n">
-        <v>15.7708425521851</v>
+        <v>15.7708406448364</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>20.3500003814697</v>
       </c>
       <c r="G864" t="n">
-        <v>15.9130516052246</v>
+        <v>15.9130535125732</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G866" t="n">
-        <v>15.9521532058716</v>
+        <v>15.9521512985229</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G869" t="n">
-        <v>15.9521532058716</v>
+        <v>15.9521512985229</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>20.75</v>
       </c>
       <c r="G870" t="n">
-        <v>16.2258396148682</v>
+        <v>16.2258415222168</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>20.75</v>
       </c>
       <c r="G874" t="n">
-        <v>16.2258396148682</v>
+        <v>16.2258415222168</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>21</v>
       </c>
       <c r="G875" t="n">
-        <v>16.4213333129883</v>
+        <v>16.4213314056396</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>20.4500007629395</v>
       </c>
       <c r="G880" t="n">
-        <v>15.9912519454956</v>
+        <v>15.991250038147</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G881" t="n">
-        <v>15.7957563400269</v>
+        <v>15.7957582473755</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G882" t="n">
-        <v>15.9521532058716</v>
+        <v>15.9521512985229</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G883" t="n">
-        <v>15.9521532058716</v>
+        <v>15.9521512985229</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G885" t="n">
-        <v>15.4047718048096</v>
+        <v>15.4047737121582</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>19.9400005340576</v>
       </c>
       <c r="G887" t="n">
-        <v>15.5924472808838</v>
+        <v>15.5924453735352</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G889" t="n">
-        <v>15.7957563400269</v>
+        <v>15.7957582473755</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>20.4500007629395</v>
       </c>
       <c r="G890" t="n">
-        <v>15.9912519454956</v>
+        <v>15.991250038147</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>21</v>
       </c>
       <c r="G892" t="n">
-        <v>16.4213333129883</v>
+        <v>16.4213314056396</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G895" t="n">
-        <v>16.4995307922363</v>
+        <v>16.4995288848877</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G896" t="n">
-        <v>16.4995307922363</v>
+        <v>16.4995288848877</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>21</v>
       </c>
       <c r="G899" t="n">
-        <v>16.4213333129883</v>
+        <v>16.4213314056396</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G901" t="n">
-        <v>16.2649383544922</v>
+        <v>16.2649364471436</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G902" t="n">
-        <v>15.7566576004028</v>
+        <v>15.7566585540771</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G904" t="n">
-        <v>15.4829702377319</v>
+        <v>15.4829683303833</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>19.7399997711182</v>
       </c>
       <c r="G905" t="n">
-        <v>15.4360513687134</v>
+        <v>15.4360523223877</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G908" t="n">
-        <v>15.4829702377319</v>
+        <v>15.4829683303833</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>19.6200008392334</v>
       </c>
       <c r="G909" t="n">
-        <v>15.3422174453735</v>
+        <v>15.3422155380249</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>19.1200008392334</v>
       </c>
       <c r="G913" t="n">
-        <v>14.9512329101562</v>
+        <v>14.9512319564819</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>19.0400009155273</v>
       </c>
       <c r="G916" t="n">
-        <v>14.8886737823486</v>
+        <v>14.8886747360229</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>19.3799991607666</v>
       </c>
       <c r="G917" t="n">
-        <v>15.1545419692993</v>
+        <v>15.1545438766479</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>18.7199993133545</v>
       </c>
       <c r="G918" t="n">
-        <v>14.6384439468384</v>
+        <v>14.6384449005127</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G919" t="n">
-        <v>14.5446100234985</v>
+        <v>14.5446090698242</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>18.8799991607666</v>
       </c>
       <c r="G920" t="n">
-        <v>14.763560295105</v>
+        <v>14.7635583877563</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>18.9200000762939</v>
       </c>
       <c r="G923" t="n">
-        <v>14.7948398590088</v>
+        <v>14.7948389053345</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>18.8199996948242</v>
       </c>
       <c r="G924" t="n">
-        <v>14.7166414260864</v>
+        <v>14.7166433334351</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>18.6399993896484</v>
       </c>
       <c r="G925" t="n">
-        <v>14.5758848190308</v>
+        <v>14.5758857727051</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>18.5400009155273</v>
       </c>
       <c r="G927" t="n">
-        <v>14.4976902008057</v>
+        <v>14.4976921081543</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>18.4400005340576</v>
       </c>
       <c r="G928" t="n">
-        <v>14.4194927215576</v>
+        <v>14.4194936752319</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>19.6399993896484</v>
       </c>
       <c r="G930" t="n">
-        <v>15.357855796814</v>
+        <v>15.357852935791</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G931" t="n">
-        <v>15.4047718048096</v>
+        <v>15.4047737121582</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>19.7600002288818</v>
       </c>
       <c r="G932" t="n">
-        <v>15.4516916275024</v>
+        <v>15.4516935348511</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>19.8199996948242</v>
       </c>
       <c r="G933" t="n">
-        <v>15.4986124038696</v>
+        <v>15.498610496521</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G934" t="n">
-        <v>15.7175617218018</v>
+        <v>15.7175598144531</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G935" t="n">
-        <v>15.7175617218018</v>
+        <v>15.7175598144531</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G936" t="n">
-        <v>15.7175617218018</v>
+        <v>15.7175598144531</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G937" t="n">
-        <v>15.4047718048096</v>
+        <v>15.4047737121582</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G938" t="n">
-        <v>15.7175617218018</v>
+        <v>15.7175598144531</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G939" t="n">
-        <v>15.7566576004028</v>
+        <v>15.7566585540771</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G940" t="n">
-        <v>15.9521532058716</v>
+        <v>15.9521512985229</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G941" t="n">
-        <v>15.9521532058716</v>
+        <v>15.9521512985229</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>21.6499996185303</v>
       </c>
       <c r="G942" t="n">
-        <v>16.9296112060547</v>
+        <v>16.9296092987061</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>21</v>
       </c>
       <c r="G946" t="n">
-        <v>16.4213333129883</v>
+        <v>16.4213314056396</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G947" t="n">
-        <v>16.3431339263916</v>
+        <v>16.3431358337402</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>20.3500003814697</v>
       </c>
       <c r="G949" t="n">
-        <v>15.9130516052246</v>
+        <v>15.9130535125732</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>20</v>
       </c>
       <c r="G952" t="n">
-        <v>15.6393632888794</v>
+        <v>15.639365196228</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G953" t="n">
-        <v>15.7175617218018</v>
+        <v>15.7175598144531</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G954" t="n">
-        <v>15.7566576004028</v>
+        <v>15.7566585540771</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G955" t="n">
-        <v>15.3265752792358</v>
+        <v>15.3265771865845</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>19.1399993896484</v>
       </c>
       <c r="G956" t="n">
-        <v>14.966869354248</v>
+        <v>14.966872215271</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>19.1800003051758</v>
       </c>
       <c r="G957" t="n">
-        <v>14.9981498718262</v>
+        <v>14.9981508255005</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>19.4799995422363</v>
       </c>
       <c r="G958" t="n">
-        <v>15.2327404022217</v>
+        <v>15.2327423095703</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25303,7 +25303,7 @@
         <v>19.3799991607666</v>
       </c>
       <c r="G959" t="n">
-        <v>15.1545419692993</v>
+        <v>15.1545438766479</v>
       </c>
       <c r="H959" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>19.6200008392334</v>
       </c>
       <c r="G961" t="n">
-        <v>15.3422174453735</v>
+        <v>15.3422155380249</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G964" t="n">
-        <v>15.7566576004028</v>
+        <v>15.7566585540771</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>19.3799991607666</v>
       </c>
       <c r="G965" t="n">
-        <v>15.1545419692993</v>
+        <v>15.1545438766479</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>19.1200008392334</v>
       </c>
       <c r="G967" t="n">
-        <v>14.9512329101562</v>
+        <v>14.9512319564819</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>19</v>
       </c>
       <c r="G968" t="n">
-        <v>14.8573942184448</v>
+        <v>14.8573951721191</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G969" t="n">
-        <v>14.7791976928711</v>
+        <v>14.7791986465454</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G970" t="n">
-        <v>14.7010021209717</v>
+        <v>14.7010011672974</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>18.6599998474121</v>
       </c>
       <c r="G971" t="n">
-        <v>14.5915269851685</v>
+        <v>14.5915279388428</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>18.9799995422363</v>
       </c>
       <c r="G972" t="n">
-        <v>14.8417568206787</v>
+        <v>14.8417549133301</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>18.8199996948242</v>
       </c>
       <c r="G974" t="n">
-        <v>14.7166414260864</v>
+        <v>14.7166433334351</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>18.8199996948242</v>
       </c>
       <c r="G975" t="n">
-        <v>14.7166414260864</v>
+        <v>14.7166433334351</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>18.8199996948242</v>
       </c>
       <c r="G976" t="n">
-        <v>14.7166414260864</v>
+        <v>14.7166433334351</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G977" t="n">
-        <v>14.7010021209717</v>
+        <v>14.7010011672974</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>18.8799991607666</v>
       </c>
       <c r="G978" t="n">
-        <v>14.763560295105</v>
+        <v>14.7635583877563</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25823,7 +25823,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G979" t="n">
-        <v>14.9355907440186</v>
+        <v>14.9355916976929</v>
       </c>
       <c r="H979" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>19.1800003051758</v>
       </c>
       <c r="G981" t="n">
-        <v>14.9981498718262</v>
+        <v>14.9981508255005</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>19.7199993133545</v>
       </c>
       <c r="G982" t="n">
-        <v>15.4204120635986</v>
+        <v>15.42041015625</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>19.6399993896484</v>
       </c>
       <c r="G983" t="n">
-        <v>15.357855796814</v>
+        <v>15.357852935791</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>19.6800003051758</v>
       </c>
       <c r="G985" t="n">
-        <v>15.3891334533691</v>
+        <v>15.3891353607178</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G986" t="n">
-        <v>15.3265752792358</v>
+        <v>15.3265771865845</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>19.2600002288818</v>
       </c>
       <c r="G989" t="n">
-        <v>15.0607089996338</v>
+        <v>15.0607070922852</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>19.1399993896484</v>
       </c>
       <c r="G990" t="n">
-        <v>14.966869354248</v>
+        <v>14.966872215271</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>19.1200008392334</v>
       </c>
       <c r="G991" t="n">
-        <v>14.9512329101562</v>
+        <v>14.9512319564819</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26161,7 +26161,7 @@
         <v>19.1399993896484</v>
       </c>
       <c r="G992" t="n">
-        <v>14.966869354248</v>
+        <v>14.966872215271</v>
       </c>
       <c r="H992" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G995" t="n">
-        <v>15.9521532058716</v>
+        <v>15.9521512985229</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G997" t="n">
-        <v>16.3431339263916</v>
+        <v>16.3431358337402</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G999" t="n">
-        <v>15.7957563400269</v>
+        <v>15.7957582473755</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>20.4500007629395</v>
       </c>
       <c r="G1004" t="n">
-        <v>15.9912519454956</v>
+        <v>15.991250038147</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>20.75</v>
       </c>
       <c r="G1007" t="n">
-        <v>16.2258396148682</v>
+        <v>16.2258415222168</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>20.4500007629395</v>
       </c>
       <c r="G1009" t="n">
-        <v>15.9912519454956</v>
+        <v>15.991250038147</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>20.3500003814697</v>
       </c>
       <c r="G1010" t="n">
-        <v>15.9130516052246</v>
+        <v>15.9130535125732</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G1012" t="n">
-        <v>15.9521532058716</v>
+        <v>15.9521512985229</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>20.3500003814697</v>
       </c>
       <c r="G1015" t="n">
-        <v>15.9130516052246</v>
+        <v>15.9130535125732</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>20.4500007629395</v>
       </c>
       <c r="G1017" t="n">
-        <v>15.9912519454956</v>
+        <v>15.991250038147</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G1018" t="n">
-        <v>15.7566576004028</v>
+        <v>15.7566585540771</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G1019" t="n">
-        <v>15.7957563400269</v>
+        <v>15.7957582473755</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>20.4500007629395</v>
       </c>
       <c r="G1020" t="n">
-        <v>15.9912519454956</v>
+        <v>15.991250038147</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G1023" t="n">
-        <v>15.9521532058716</v>
+        <v>15.9521512985229</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G1024" t="n">
-        <v>15.7957563400269</v>
+        <v>15.7957582473755</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>20.3500003814697</v>
       </c>
       <c r="G1026" t="n">
-        <v>15.9130516052246</v>
+        <v>15.9130535125732</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1027" t="n">
-        <v>16.2649383544922</v>
+        <v>16.2649364471436</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G1029" t="n">
-        <v>15.7957563400269</v>
+        <v>15.7957582473755</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27149,7 +27149,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G1030" t="n">
-        <v>15.9521532058716</v>
+        <v>15.9521512985229</v>
       </c>
       <c r="H1030" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>20</v>
       </c>
       <c r="G1031" t="n">
-        <v>15.6393632888794</v>
+        <v>15.639365196228</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G1033" t="n">
-        <v>15.3265752792358</v>
+        <v>15.3265771865845</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>19.5599994659424</v>
       </c>
       <c r="G1034" t="n">
-        <v>15.2952966690063</v>
+        <v>15.295298576355</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>19.6200008392334</v>
       </c>
       <c r="G1035" t="n">
-        <v>15.3422174453735</v>
+        <v>15.3422155380249</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>19.6200008392334</v>
       </c>
       <c r="G1036" t="n">
-        <v>15.3422174453735</v>
+        <v>15.3422155380249</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>19.3799991607666</v>
       </c>
       <c r="G1038" t="n">
-        <v>15.1545419692993</v>
+        <v>15.1545438766479</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>19.5200004577637</v>
       </c>
       <c r="G1039" t="n">
-        <v>15.2640209197998</v>
+        <v>15.2640190124512</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G1040" t="n">
-        <v>15.4829702377319</v>
+        <v>15.4829683303833</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>20</v>
       </c>
       <c r="G1041" t="n">
-        <v>15.6393632888794</v>
+        <v>15.639365196228</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G1043" t="n">
-        <v>15.3265752792358</v>
+        <v>15.3265771865845</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>19.9599990844727</v>
       </c>
       <c r="G1044" t="n">
-        <v>15.6080865859985</v>
+        <v>15.6080827713013</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G1045" t="n">
-        <v>15.7566576004028</v>
+        <v>15.7566585540771</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>20</v>
       </c>
       <c r="G1046" t="n">
-        <v>15.6393632888794</v>
+        <v>15.639365196228</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>20</v>
       </c>
       <c r="G1047" t="n">
-        <v>15.6393632888794</v>
+        <v>15.639365196228</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>20</v>
       </c>
       <c r="G1048" t="n">
-        <v>15.6393632888794</v>
+        <v>15.639365196228</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G1049" t="n">
-        <v>15.4829702377319</v>
+        <v>15.4829683303833</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>19.7399997711182</v>
       </c>
       <c r="G1050" t="n">
-        <v>15.4360513687134</v>
+        <v>15.4360523223877</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27695,7 +27695,7 @@
         <v>19.2600002288818</v>
       </c>
       <c r="G1051" t="n">
-        <v>15.0607089996338</v>
+        <v>15.0607070922852</v>
       </c>
       <c r="H1051" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>19</v>
       </c>
       <c r="G1052" t="n">
-        <v>14.8573942184448</v>
+        <v>14.8573951721191</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>17.5200004577637</v>
       </c>
       <c r="G1053" t="n">
-        <v>13.7000827789307</v>
+        <v>13.700083732605</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>17.5200004577637</v>
       </c>
       <c r="G1054" t="n">
-        <v>13.7000827789307</v>
+        <v>13.700083732605</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27799,7 +27799,7 @@
         <v>17.8400001525879</v>
       </c>
       <c r="G1055" t="n">
-        <v>13.9503116607666</v>
+        <v>13.9503126144409</v>
       </c>
       <c r="H1055" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>16.4400005340576</v>
       </c>
       <c r="G1058" t="n">
-        <v>12.8555583953857</v>
+        <v>12.8555564880371</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1059" t="n">
-        <v>12.6678848266602</v>
+        <v>12.6678857803345</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27955,7 +27955,7 @@
         <v>16.1399993896484</v>
       </c>
       <c r="G1061" t="n">
-        <v>12.6209659576416</v>
+        <v>12.6209669113159</v>
       </c>
       <c r="H1061" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1062" t="n">
-        <v>12.6678848266602</v>
+        <v>12.6678857803345</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>14.1800003051758</v>
       </c>
       <c r="G1063" t="n">
-        <v>11.0883073806763</v>
+        <v>11.0883083343506</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>14.9799995422363</v>
       </c>
       <c r="G1065" t="n">
-        <v>11.7138824462891</v>
+        <v>11.7138833999634</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>12.2600002288818</v>
       </c>
       <c r="G1068" t="n">
-        <v>9.58693027496338</v>
+        <v>9.58692932128906</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>12</v>
       </c>
       <c r="G1070" t="n">
-        <v>9.38361835479736</v>
+        <v>9.38361930847168</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>12.4399995803833</v>
       </c>
       <c r="G1071" t="n">
-        <v>9.72768497467041</v>
+        <v>9.72768306732178</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>15</v>
       </c>
       <c r="G1073" t="n">
-        <v>11.7295227050781</v>
+        <v>11.7295217514038</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>15.5</v>
       </c>
       <c r="G1074" t="n">
-        <v>12.1205081939697</v>
+        <v>12.1205072402954</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28319,7 +28319,7 @@
         <v>14.6800003051758</v>
       </c>
       <c r="G1075" t="n">
-        <v>11.4792928695679</v>
+        <v>11.4792938232422</v>
       </c>
       <c r="H1075" t="s">
         <v>8</v>
@@ -28371,7 +28371,7 @@
         <v>13.5200004577637</v>
       </c>
       <c r="G1077" t="n">
-        <v>10.5722103118896</v>
+        <v>10.572211265564</v>
       </c>
       <c r="H1077" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>12.8599996566772</v>
       </c>
       <c r="G1079" t="n">
-        <v>10.0561103820801</v>
+        <v>10.0561113357544</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28449,7 +28449,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G1080" t="n">
-        <v>9.61820888519287</v>
+        <v>9.61820793151855</v>
       </c>
       <c r="H1080" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1081" t="n">
-        <v>9.8528003692627</v>
+        <v>9.85279846191406</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>12.4399995803833</v>
       </c>
       <c r="G1082" t="n">
-        <v>9.72768497467041</v>
+        <v>9.72768306732178</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>12.6800003051758</v>
       </c>
       <c r="G1083" t="n">
-        <v>9.91535568237305</v>
+        <v>9.91535758972168</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1084" t="n">
-        <v>9.93099498748779</v>
+        <v>9.93099594116211</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G1087" t="n">
-        <v>9.47745418548584</v>
+        <v>9.47745513916016</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>12.4200000762939</v>
       </c>
       <c r="G1091" t="n">
-        <v>9.71204566955566</v>
+        <v>9.71204471588135</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G1092" t="n">
-        <v>9.4930944442749</v>
+        <v>9.49309349060059</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G1094" t="n">
-        <v>9.43053722381592</v>
+        <v>9.4305362701416</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1095" t="n">
-        <v>9.46181488037109</v>
+        <v>9.46181583404541</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>12.4200000762939</v>
       </c>
       <c r="G1096" t="n">
-        <v>9.71204566955566</v>
+        <v>9.71204471588135</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -28995,7 +28995,7 @@
         <v>11.460000038147</v>
       </c>
       <c r="G1101" t="n">
-        <v>8.9613561630249</v>
+        <v>8.96135520935059</v>
       </c>
       <c r="H1101" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>11.0200004577637</v>
       </c>
       <c r="G1103" t="n">
-        <v>8.61728954315186</v>
+        <v>8.61729049682617</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29125,7 +29125,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G1106" t="n">
-        <v>9.5556526184082</v>
+        <v>9.55565071105957</v>
       </c>
       <c r="H1106" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G1107" t="n">
-        <v>9.61820888519287</v>
+        <v>9.61820793151855</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G1108" t="n">
-        <v>9.14902782440186</v>
+        <v>9.14902687072754</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29255,7 +29255,7 @@
         <v>12</v>
       </c>
       <c r="G1111" t="n">
-        <v>9.38361835479736</v>
+        <v>9.38361930847168</v>
       </c>
       <c r="H1111" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1112" t="n">
-        <v>9.46181488037109</v>
+        <v>9.46181583404541</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G1113" t="n">
-        <v>9.43053722381592</v>
+        <v>9.4305362701416</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G1114" t="n">
-        <v>9.83715915679932</v>
+        <v>9.83716011047363</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29359,7 +29359,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1115" t="n">
-        <v>9.8528003692627</v>
+        <v>9.85279846191406</v>
       </c>
       <c r="H1115" t="s">
         <v>8</v>
@@ -29463,7 +29463,7 @@
         <v>13.1400003433228</v>
       </c>
       <c r="G1119" t="n">
-        <v>10.2750616073608</v>
+        <v>10.2750625610352</v>
       </c>
       <c r="H1119" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>13.1199998855591</v>
       </c>
       <c r="G1122" t="n">
-        <v>10.2594232559204</v>
+        <v>10.2594213485718</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29567,7 +29567,7 @@
         <v>13.1199998855591</v>
       </c>
       <c r="G1123" t="n">
-        <v>10.2594232559204</v>
+        <v>10.2594213485718</v>
       </c>
       <c r="H1123" t="s">
         <v>8</v>
@@ -29593,7 +29593,7 @@
         <v>14.2399997711182</v>
       </c>
       <c r="G1124" t="n">
-        <v>11.1352281570435</v>
+        <v>11.1352272033691</v>
       </c>
       <c r="H1124" t="s">
         <v>8</v>
@@ -29619,7 +29619,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1125" t="n">
-        <v>11.103949546814</v>
+        <v>11.1039476394653</v>
       </c>
       <c r="H1125" t="s">
         <v>8</v>
@@ -29723,7 +29723,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1129" t="n">
-        <v>10.3219804763794</v>
+        <v>10.3219795227051</v>
       </c>
       <c r="H1129" t="s">
         <v>8</v>
@@ -29775,7 +29775,7 @@
         <v>13.5799999237061</v>
       </c>
       <c r="G1131" t="n">
-        <v>10.6191272735596</v>
+        <v>10.6191291809082</v>
       </c>
       <c r="H1131" t="s">
         <v>8</v>
@@ -29853,7 +29853,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1134" t="n">
-        <v>10.6347665786743</v>
+        <v>10.6347684860229</v>
       </c>
       <c r="H1134" t="s">
         <v>8</v>
@@ -29879,7 +29879,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G1135" t="n">
-        <v>10.5409317016602</v>
+        <v>10.5409326553345</v>
       </c>
       <c r="H1135" t="s">
         <v>8</v>
@@ -29931,7 +29931,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G1137" t="n">
-        <v>10.5409317016602</v>
+        <v>10.5409326553345</v>
       </c>
       <c r="H1137" t="s">
         <v>8</v>
@@ -29983,7 +29983,7 @@
         <v>13.3599996566772</v>
       </c>
       <c r="G1139" t="n">
-        <v>10.4470958709717</v>
+        <v>10.4470949172974</v>
       </c>
       <c r="H1139" t="s">
         <v>8</v>
@@ -30035,7 +30035,7 @@
         <v>13.3400001525879</v>
       </c>
       <c r="G1141" t="n">
-        <v>10.4314556121826</v>
+        <v>10.4314546585083</v>
       </c>
       <c r="H1141" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>13.0600004196167</v>
       </c>
       <c r="G1142" t="n">
-        <v>10.2125053405762</v>
+        <v>10.2125062942505</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>13.0799999237061</v>
       </c>
       <c r="G1143" t="n">
-        <v>10.2281446456909</v>
+        <v>10.2281436920166</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30139,7 +30139,7 @@
         <v>12.7600002288818</v>
       </c>
       <c r="G1145" t="n">
-        <v>9.97791385650635</v>
+        <v>9.97791481018066</v>
       </c>
       <c r="H1145" t="s">
         <v>8</v>
@@ -30191,7 +30191,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G1147" t="n">
-        <v>9.83715915679932</v>
+        <v>9.83716011047363</v>
       </c>
       <c r="H1147" t="s">
         <v>8</v>
@@ -30269,7 +30269,7 @@
         <v>12.8400001525879</v>
       </c>
       <c r="G1150" t="n">
-        <v>10.0404720306396</v>
+        <v>10.040472984314</v>
       </c>
       <c r="H1150" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>12.4399995803833</v>
       </c>
       <c r="G1152" t="n">
-        <v>9.72768497467041</v>
+        <v>9.72768306732178</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>12.3400001525879</v>
       </c>
       <c r="G1153" t="n">
-        <v>9.64948844909668</v>
+        <v>9.64948749542236</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30425,7 +30425,7 @@
         <v>13.1800003051758</v>
       </c>
       <c r="G1156" t="n">
-        <v>10.306342124939</v>
+        <v>10.3063411712646</v>
       </c>
       <c r="H1156" t="s">
         <v>8</v>
@@ -30529,7 +30529,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G1160" t="n">
-        <v>9.89971733093262</v>
+        <v>9.89971923828125</v>
       </c>
       <c r="H1160" t="s">
         <v>8</v>
@@ -30581,7 +30581,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1162" t="n">
-        <v>10.0091934204102</v>
+        <v>10.0091924667358</v>
       </c>
       <c r="H1162" t="s">
         <v>8</v>
@@ -30607,7 +30607,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1163" t="n">
-        <v>10.0091934204102</v>
+        <v>10.0091924667358</v>
       </c>
       <c r="H1163" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1165" t="n">
-        <v>9.8528003692627</v>
+        <v>9.85279846191406</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30711,7 +30711,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1167" t="n">
-        <v>9.8528003692627</v>
+        <v>9.85279846191406</v>
       </c>
       <c r="H1167" t="s">
         <v>8</v>
@@ -30841,7 +30841,7 @@
         <v>12.7600002288818</v>
       </c>
       <c r="G1172" t="n">
-        <v>9.97791385650635</v>
+        <v>9.97791481018066</v>
       </c>
       <c r="H1172" t="s">
         <v>8</v>
@@ -30867,7 +30867,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G1173" t="n">
-        <v>9.89971733093262</v>
+        <v>9.89971923828125</v>
       </c>
       <c r="H1173" t="s">
         <v>8</v>
@@ -30919,7 +30919,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G1175" t="n">
-        <v>9.74332332611084</v>
+        <v>9.74332427978516</v>
       </c>
       <c r="H1175" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1180" t="n">
-        <v>9.93099498748779</v>
+        <v>9.93099594116211</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>13</v>
       </c>
       <c r="G1181" t="n">
-        <v>10.1655855178833</v>
+        <v>10.1655864715576</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31127,7 +31127,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1183" t="n">
-        <v>10.3219804763794</v>
+        <v>10.3219795227051</v>
       </c>
       <c r="H1183" t="s">
         <v>8</v>
@@ -31179,7 +31179,7 @@
         <v>12.8599996566772</v>
       </c>
       <c r="G1185" t="n">
-        <v>10.0561103820801</v>
+        <v>10.0561113357544</v>
       </c>
       <c r="H1185" t="s">
         <v>8</v>
@@ -31205,7 +31205,7 @@
         <v>13.1800003051758</v>
       </c>
       <c r="G1186" t="n">
-        <v>10.306342124939</v>
+        <v>10.3063411712646</v>
       </c>
       <c r="H1186" t="s">
         <v>8</v>
@@ -31231,7 +31231,7 @@
         <v>13.1400003433228</v>
       </c>
       <c r="G1187" t="n">
-        <v>10.2750616073608</v>
+        <v>10.2750625610352</v>
       </c>
       <c r="H1187" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>13.5200004577637</v>
       </c>
       <c r="G1188" t="n">
-        <v>10.5722103118896</v>
+        <v>10.572211265564</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31283,7 +31283,7 @@
         <v>13.3599996566772</v>
       </c>
       <c r="G1189" t="n">
-        <v>10.4470958709717</v>
+        <v>10.4470949172974</v>
       </c>
       <c r="H1189" t="s">
         <v>8</v>
@@ -31309,7 +31309,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G1190" t="n">
-        <v>10.4940137863159</v>
+        <v>10.4940128326416</v>
       </c>
       <c r="H1190" t="s">
         <v>8</v>
@@ -31335,7 +31335,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1191" t="n">
-        <v>10.6347665786743</v>
+        <v>10.6347684860229</v>
       </c>
       <c r="H1191" t="s">
         <v>8</v>
@@ -31387,7 +31387,7 @@
         <v>13.3400001525879</v>
       </c>
       <c r="G1193" t="n">
-        <v>10.4314556121826</v>
+        <v>10.4314546585083</v>
       </c>
       <c r="H1193" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>13.5200004577637</v>
       </c>
       <c r="G1194" t="n">
-        <v>10.5722103118896</v>
+        <v>10.572211265564</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31491,7 +31491,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1197" t="n">
-        <v>10.6347665786743</v>
+        <v>10.6347684860229</v>
       </c>
       <c r="H1197" t="s">
         <v>8</v>
@@ -31595,7 +31595,7 @@
         <v>13.3599996566772</v>
       </c>
       <c r="G1201" t="n">
-        <v>10.4470958709717</v>
+        <v>10.4470949172974</v>
       </c>
       <c r="H1201" t="s">
         <v>8</v>
@@ -31777,7 +31777,7 @@
         <v>13.8800001144409</v>
       </c>
       <c r="G1208" t="n">
-        <v>10.8537178039551</v>
+        <v>10.8537187576294</v>
       </c>
       <c r="H1208" t="s">
         <v>8</v>
@@ -31907,7 +31907,7 @@
         <v>14.539999961853</v>
       </c>
       <c r="G1213" t="n">
-        <v>11.369818687439</v>
+        <v>11.3698177337646</v>
       </c>
       <c r="H1213" t="s">
         <v>8</v>
@@ -31959,7 +31959,7 @@
         <v>14.2399997711182</v>
       </c>
       <c r="G1215" t="n">
-        <v>11.1352281570435</v>
+        <v>11.1352272033691</v>
       </c>
       <c r="H1215" t="s">
         <v>8</v>
@@ -31985,7 +31985,7 @@
         <v>13.7200002670288</v>
       </c>
       <c r="G1216" t="n">
-        <v>10.7286043167114</v>
+        <v>10.7286033630371</v>
       </c>
       <c r="H1216" t="s">
         <v>8</v>
@@ -32011,7 +32011,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G1217" t="n">
-        <v>10.4783735275269</v>
+        <v>10.4783744812012</v>
       </c>
       <c r="H1217" t="s">
         <v>8</v>
@@ -32167,7 +32167,7 @@
         <v>12.4399995803833</v>
       </c>
       <c r="G1223" t="n">
-        <v>9.72768497467041</v>
+        <v>9.72768306732178</v>
       </c>
       <c r="H1223" t="s">
         <v>8</v>
@@ -32193,7 +32193,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1224" t="n">
-        <v>9.93099498748779</v>
+        <v>9.93099594116211</v>
       </c>
       <c r="H1224" t="s">
         <v>8</v>
@@ -32219,7 +32219,7 @@
         <v>12.2600002288818</v>
       </c>
       <c r="G1225" t="n">
-        <v>9.58693027496338</v>
+        <v>9.58692932128906</v>
       </c>
       <c r="H1225" t="s">
         <v>8</v>
@@ -32297,7 +32297,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1228" t="n">
-        <v>9.07083129882812</v>
+        <v>9.07083225250244</v>
       </c>
       <c r="H1228" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>11.6400003433228</v>
       </c>
       <c r="G1229" t="n">
-        <v>9.10211086273193</v>
+        <v>9.10210990905762</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32401,7 +32401,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G1232" t="n">
-        <v>9.14902782440186</v>
+        <v>9.14902687072754</v>
       </c>
       <c r="H1232" t="s">
         <v>8</v>
@@ -32609,7 +32609,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G1240" t="n">
-        <v>12.1048669815063</v>
+        <v>12.1048679351807</v>
       </c>
       <c r="H1240" t="s">
         <v>8</v>
@@ -32635,7 +32635,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G1241" t="n">
-        <v>12.5584077835083</v>
+        <v>12.5584096908569</v>
       </c>
       <c r="H1241" t="s">
         <v>8</v>
@@ -32713,7 +32713,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1244" t="n">
-        <v>11.573130607605</v>
+        <v>11.5731287002563</v>
       </c>
       <c r="H1244" t="s">
         <v>8</v>
@@ -32765,7 +32765,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G1246" t="n">
-        <v>12.1674251556396</v>
+        <v>12.167426109314</v>
       </c>
       <c r="H1246" t="s">
         <v>8</v>
@@ -32817,7 +32817,7 @@
         <v>15.6599998474121</v>
       </c>
       <c r="G1248" t="n">
-        <v>12.2456226348877</v>
+        <v>12.2456216812134</v>
       </c>
       <c r="H1248" t="s">
         <v>8</v>
@@ -32869,7 +32869,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1250" t="n">
-        <v>12.2769012451172</v>
+        <v>12.2768993377686</v>
       </c>
       <c r="H1250" t="s">
         <v>8</v>
@@ -32895,7 +32895,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G1251" t="n">
-        <v>12.1674251556396</v>
+        <v>12.167426109314</v>
       </c>
       <c r="H1251" t="s">
         <v>8</v>
@@ -32921,7 +32921,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G1252" t="n">
-        <v>12.1048669815063</v>
+        <v>12.1048679351807</v>
       </c>
       <c r="H1252" t="s">
         <v>8</v>
@@ -33025,7 +33025,7 @@
         <v>15.0200004577637</v>
       </c>
       <c r="G1256" t="n">
-        <v>11.7451620101929</v>
+        <v>11.7451610565186</v>
       </c>
       <c r="H1256" t="s">
         <v>8</v>
@@ -33051,7 +33051,7 @@
         <v>15.0799999237061</v>
       </c>
       <c r="G1257" t="n">
-        <v>11.7920799255371</v>
+        <v>11.7920808792114</v>
       </c>
       <c r="H1257" t="s">
         <v>8</v>
@@ -33077,7 +33077,7 @@
         <v>15.3599996566772</v>
       </c>
       <c r="G1258" t="n">
-        <v>12.0110321044922</v>
+        <v>12.0110311508179</v>
       </c>
       <c r="H1258" t="s">
         <v>8</v>
@@ -33103,7 +33103,7 @@
         <v>14.9200000762939</v>
       </c>
       <c r="G1259" t="n">
-        <v>11.6669664382935</v>
+        <v>11.6669645309448</v>
       </c>
       <c r="H1259" t="s">
         <v>8</v>
@@ -33155,7 +33155,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G1261" t="n">
-        <v>11.9328346252441</v>
+        <v>11.9328355789185</v>
       </c>
       <c r="H1261" t="s">
         <v>8</v>
@@ -33181,7 +33181,7 @@
         <v>15.5</v>
       </c>
       <c r="G1262" t="n">
-        <v>12.1205081939697</v>
+        <v>12.1205072402954</v>
       </c>
       <c r="H1262" t="s">
         <v>8</v>
@@ -33207,7 +33207,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G1263" t="n">
-        <v>12.2143430709839</v>
+        <v>12.2143421173096</v>
       </c>
       <c r="H1263" t="s">
         <v>8</v>
@@ -33233,7 +33233,7 @@
         <v>15.5799999237061</v>
       </c>
       <c r="G1264" t="n">
-        <v>12.1830644607544</v>
+        <v>12.1830635070801</v>
       </c>
       <c r="H1264" t="s">
         <v>8</v>
@@ -33259,7 +33259,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1265" t="n">
-        <v>12.2769012451172</v>
+        <v>12.2768993377686</v>
       </c>
       <c r="H1265" t="s">
         <v>8</v>
@@ -33337,7 +33337,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1268" t="n">
-        <v>12.6678848266602</v>
+        <v>12.6678857803345</v>
       </c>
       <c r="H1268" t="s">
         <v>8</v>
@@ -33441,7 +33441,7 @@
         <v>17.3199996948242</v>
       </c>
       <c r="G1272" t="n">
-        <v>13.5436887741089</v>
+        <v>13.5436878204346</v>
       </c>
       <c r="H1272" t="s">
         <v>8</v>
@@ -33467,7 +33467,7 @@
         <v>17.5799999237061</v>
       </c>
       <c r="G1273" t="n">
-        <v>13.7470006942749</v>
+        <v>13.7470016479492</v>
       </c>
       <c r="H1273" t="s">
         <v>8</v>
@@ -33493,7 +33493,7 @@
         <v>17.7199993133545</v>
       </c>
       <c r="G1274" t="n">
-        <v>13.8564777374268</v>
+        <v>13.8564767837524</v>
       </c>
       <c r="H1274" t="s">
         <v>8</v>
@@ -33519,7 +33519,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1275" t="n">
-        <v>13.9190330505371</v>
+        <v>13.9190340042114</v>
       </c>
       <c r="H1275" t="s">
         <v>8</v>
@@ -33545,7 +33545,7 @@
         <v>17.6399993896484</v>
       </c>
       <c r="G1276" t="n">
-        <v>13.7939186096191</v>
+        <v>13.7939176559448</v>
       </c>
       <c r="H1276" t="s">
         <v>8</v>
@@ -33571,7 +33571,7 @@
         <v>17</v>
       </c>
       <c r="G1277" t="n">
-        <v>13.2934579849243</v>
+        <v>13.2934589385986</v>
       </c>
       <c r="H1277" t="s">
         <v>8</v>
@@ -33597,7 +33597,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1278" t="n">
-        <v>13.6062479019165</v>
+        <v>13.6062450408936</v>
       </c>
       <c r="H1278" t="s">
         <v>8</v>
@@ -33649,7 +33649,7 @@
         <v>17.7800006866455</v>
       </c>
       <c r="G1280" t="n">
-        <v>13.903395652771</v>
+        <v>13.9033946990967</v>
       </c>
       <c r="H1280" t="s">
         <v>8</v>
@@ -33675,7 +33675,7 @@
         <v>17.4799995422363</v>
       </c>
       <c r="G1281" t="n">
-        <v>13.6688041687012</v>
+        <v>13.6688032150269</v>
       </c>
       <c r="H1281" t="s">
         <v>8</v>
@@ -33779,7 +33779,7 @@
         <v>16.6200008392334</v>
       </c>
       <c r="G1285" t="n">
-        <v>12.9963130950928</v>
+        <v>12.9963121414185</v>
       </c>
       <c r="H1285" t="s">
         <v>8</v>
@@ -33805,7 +33805,7 @@
         <v>16.6200008392334</v>
       </c>
       <c r="G1286" t="n">
-        <v>12.9963130950928</v>
+        <v>12.9963121414185</v>
       </c>
       <c r="H1286" t="s">
         <v>8</v>
@@ -33935,7 +33935,7 @@
         <v>17.2199993133545</v>
       </c>
       <c r="G1291" t="n">
-        <v>13.4654922485352</v>
+        <v>13.4654912948608</v>
       </c>
       <c r="H1291" t="s">
         <v>8</v>
@@ -33961,7 +33961,7 @@
         <v>17.3199996948242</v>
       </c>
       <c r="G1292" t="n">
-        <v>13.5436887741089</v>
+        <v>13.5436878204346</v>
       </c>
       <c r="H1292" t="s">
         <v>8</v>
@@ -33987,7 +33987,7 @@
         <v>18.1399993896484</v>
       </c>
       <c r="G1293" t="n">
-        <v>14.1849021911621</v>
+        <v>14.1849012374878</v>
       </c>
       <c r="H1293" t="s">
         <v>8</v>
@@ -34039,7 +34039,7 @@
         <v>18.5599994659424</v>
       </c>
       <c r="G1295" t="n">
-        <v>14.5133304595947</v>
+        <v>14.5133295059204</v>
       </c>
       <c r="H1295" t="s">
         <v>8</v>
@@ -34091,7 +34091,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1297" t="n">
-        <v>14.7791976928711</v>
+        <v>14.7791986465454</v>
       </c>
       <c r="H1297" t="s">
         <v>8</v>
@@ -34117,7 +34117,7 @@
         <v>19.2800006866455</v>
       </c>
       <c r="G1298" t="n">
-        <v>15.0763483047485</v>
+        <v>15.0763454437256</v>
       </c>
       <c r="H1298" t="s">
         <v>8</v>
@@ -34195,7 +34195,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1301" t="n">
-        <v>14.5446100234985</v>
+        <v>14.5446090698242</v>
       </c>
       <c r="H1301" t="s">
         <v>8</v>
@@ -34221,7 +34221,7 @@
         <v>18.6399993896484</v>
       </c>
       <c r="G1302" t="n">
-        <v>14.5758848190308</v>
+        <v>14.5758857727051</v>
       </c>
       <c r="H1302" t="s">
         <v>8</v>
@@ -34247,7 +34247,7 @@
         <v>18.0599994659424</v>
       </c>
       <c r="G1303" t="n">
-        <v>14.1223459243774</v>
+        <v>14.1223449707031</v>
       </c>
       <c r="H1303" t="s">
         <v>8</v>
@@ -34299,7 +34299,7 @@
         <v>18.6599998474121</v>
       </c>
       <c r="G1305" t="n">
-        <v>14.5915269851685</v>
+        <v>14.5915279388428</v>
       </c>
       <c r="H1305" t="s">
         <v>8</v>
@@ -34325,7 +34325,7 @@
         <v>18.1399993896484</v>
       </c>
       <c r="G1306" t="n">
-        <v>14.1849021911621</v>
+        <v>14.1849012374878</v>
       </c>
       <c r="H1306" t="s">
         <v>8</v>
@@ -34351,7 +34351,7 @@
         <v>18.0799999237061</v>
       </c>
       <c r="G1307" t="n">
-        <v>14.1379842758179</v>
+        <v>14.1379852294922</v>
       </c>
       <c r="H1307" t="s">
         <v>8</v>
@@ -34377,7 +34377,7 @@
         <v>18.4400005340576</v>
       </c>
       <c r="G1308" t="n">
-        <v>14.4194927215576</v>
+        <v>14.4194936752319</v>
       </c>
       <c r="H1308" t="s">
         <v>8</v>
@@ -34429,7 +34429,7 @@
         <v>18.8600006103516</v>
       </c>
       <c r="G1310" t="n">
-        <v>14.7479209899902</v>
+        <v>14.7479200363159</v>
       </c>
       <c r="H1310" t="s">
         <v>8</v>
@@ -34481,7 +34481,7 @@
         <v>19.1800003051758</v>
       </c>
       <c r="G1312" t="n">
-        <v>14.9981498718262</v>
+        <v>14.9981508255005</v>
       </c>
       <c r="H1312" t="s">
         <v>8</v>
@@ -34507,7 +34507,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G1313" t="n">
-        <v>15.1701822280884</v>
+        <v>15.170184135437</v>
       </c>
       <c r="H1313" t="s">
         <v>8</v>
@@ -34533,7 +34533,7 @@
         <v>19.3600006103516</v>
       </c>
       <c r="G1314" t="n">
-        <v>15.1389074325562</v>
+        <v>15.1389036178589</v>
       </c>
       <c r="H1314" t="s">
         <v>8</v>
@@ -34559,7 +34559,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G1315" t="n">
-        <v>14.9355907440186</v>
+        <v>14.9355916976929</v>
       </c>
       <c r="H1315" t="s">
         <v>8</v>
@@ -34585,7 +34585,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G1316" t="n">
-        <v>15.7957563400269</v>
+        <v>15.7957582473755</v>
       </c>
       <c r="H1316" t="s">
         <v>8</v>
@@ -34611,7 +34611,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G1317" t="n">
-        <v>15.7566576004028</v>
+        <v>15.7566585540771</v>
       </c>
       <c r="H1317" t="s">
         <v>8</v>
@@ -34637,7 +34637,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G1318" t="n">
-        <v>15.4829702377319</v>
+        <v>15.4829683303833</v>
       </c>
       <c r="H1318" t="s">
         <v>8</v>
@@ -34663,7 +34663,7 @@
         <v>19.9599990844727</v>
       </c>
       <c r="G1319" t="n">
-        <v>15.6080865859985</v>
+        <v>15.6080827713013</v>
       </c>
       <c r="H1319" t="s">
         <v>8</v>
@@ -34689,7 +34689,7 @@
         <v>19.9599990844727</v>
       </c>
       <c r="G1320" t="n">
-        <v>15.6080865859985</v>
+        <v>15.6080827713013</v>
       </c>
       <c r="H1320" t="s">
         <v>8</v>
@@ -34715,7 +34715,7 @@
         <v>19.3799991607666</v>
       </c>
       <c r="G1321" t="n">
-        <v>15.1545419692993</v>
+        <v>15.1545438766479</v>
       </c>
       <c r="H1321" t="s">
         <v>8</v>
@@ -34767,7 +34767,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1323" t="n">
-        <v>14.1536254882812</v>
+        <v>14.1536235809326</v>
       </c>
       <c r="H1323" t="s">
         <v>8</v>
@@ -34793,7 +34793,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1324" t="n">
-        <v>14.3882141113281</v>
+        <v>14.3882150650024</v>
       </c>
       <c r="H1324" t="s">
         <v>8</v>
@@ -34819,7 +34819,7 @@
         <v>18.3600006103516</v>
       </c>
       <c r="G1325" t="n">
-        <v>14.3569364547729</v>
+        <v>14.3569383621216</v>
       </c>
       <c r="H1325" t="s">
         <v>8</v>
@@ -34845,7 +34845,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1326" t="n">
-        <v>14.3882141113281</v>
+        <v>14.3882150650024</v>
       </c>
       <c r="H1326" t="s">
         <v>8</v>
@@ -34871,7 +34871,7 @@
         <v>18.2600002288818</v>
       </c>
       <c r="G1327" t="n">
-        <v>14.2787399291992</v>
+        <v>14.2787380218506</v>
       </c>
       <c r="H1327" t="s">
         <v>8</v>
@@ -34897,7 +34897,7 @@
         <v>18.5400009155273</v>
       </c>
       <c r="G1328" t="n">
-        <v>14.4976902008057</v>
+        <v>14.4976921081543</v>
       </c>
       <c r="H1328" t="s">
         <v>8</v>
@@ -34975,7 +34975,7 @@
         <v>18.5599994659424</v>
       </c>
       <c r="G1331" t="n">
-        <v>14.5133304595947</v>
+        <v>14.5133295059204</v>
       </c>
       <c r="H1331" t="s">
         <v>8</v>
@@ -35001,7 +35001,7 @@
         <v>18.8400001525879</v>
       </c>
       <c r="G1332" t="n">
-        <v>14.7322807312012</v>
+        <v>14.7322816848755</v>
       </c>
       <c r="H1332" t="s">
         <v>8</v>
@@ -35079,7 +35079,7 @@
         <v>18.6900005340576</v>
       </c>
       <c r="G1335" t="n">
-        <v>14.6149845123291</v>
+        <v>14.6149854660034</v>
       </c>
       <c r="H1335" t="s">
         <v>8</v>
@@ -35157,7 +35157,7 @@
         <v>18.3600006103516</v>
       </c>
       <c r="G1338" t="n">
-        <v>14.3569364547729</v>
+        <v>14.3569383621216</v>
       </c>
       <c r="H1338" t="s">
         <v>8</v>
@@ -35183,7 +35183,7 @@
         <v>18.6900005340576</v>
       </c>
       <c r="G1339" t="n">
-        <v>14.6149845123291</v>
+        <v>14.6149854660034</v>
       </c>
       <c r="H1339" t="s">
         <v>8</v>
@@ -35235,7 +35235,7 @@
         <v>18.7399997711182</v>
       </c>
       <c r="G1341" t="n">
-        <v>14.6540832519531</v>
+        <v>14.6540851593018</v>
       </c>
       <c r="H1341" t="s">
         <v>8</v>
@@ -35261,7 +35261,7 @@
         <v>18.7800006866455</v>
       </c>
       <c r="G1342" t="n">
-        <v>14.6853628158569</v>
+        <v>14.6853618621826</v>
       </c>
       <c r="H1342" t="s">
         <v>8</v>
@@ -35365,7 +35365,7 @@
         <v>18.4400005340576</v>
       </c>
       <c r="G1346" t="n">
-        <v>14.4194927215576</v>
+        <v>14.4194936752319</v>
       </c>
       <c r="H1346" t="s">
         <v>8</v>
@@ -35391,7 +35391,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G1347" t="n">
-        <v>14.8182973861694</v>
+        <v>14.8182983398438</v>
       </c>
       <c r="H1347" t="s">
         <v>8</v>
@@ -35469,7 +35469,7 @@
         <v>19.2600002288818</v>
       </c>
       <c r="G1350" t="n">
-        <v>15.0607089996338</v>
+        <v>15.0607070922852</v>
       </c>
       <c r="H1350" t="s">
         <v>8</v>
@@ -35495,7 +35495,7 @@
         <v>18.9899997711182</v>
       </c>
       <c r="G1351" t="n">
-        <v>14.8495740890503</v>
+        <v>14.8495750427246</v>
       </c>
       <c r="H1351" t="s">
         <v>8</v>
@@ -35573,7 +35573,7 @@
         <v>19.1200008392334</v>
       </c>
       <c r="G1354" t="n">
-        <v>14.9512329101562</v>
+        <v>14.9512319564819</v>
       </c>
       <c r="H1354" t="s">
         <v>8</v>
@@ -35599,7 +35599,7 @@
         <v>19.1800003051758</v>
       </c>
       <c r="G1355" t="n">
-        <v>14.9981498718262</v>
+        <v>14.9981508255005</v>
       </c>
       <c r="H1355" t="s">
         <v>8</v>
@@ -35677,7 +35677,7 @@
         <v>19.9899997711182</v>
       </c>
       <c r="G1358" t="n">
-        <v>15.6315431594849</v>
+        <v>15.6315450668335</v>
       </c>
       <c r="H1358" t="s">
         <v>8</v>
@@ -35729,7 +35729,7 @@
         <v>19.1299991607666</v>
       </c>
       <c r="G1360" t="n">
-        <v>14.9590511322021</v>
+        <v>14.9590520858765</v>
       </c>
       <c r="H1360" t="s">
         <v>8</v>
@@ -35755,7 +35755,7 @@
         <v>19</v>
       </c>
       <c r="G1361" t="n">
-        <v>14.8573942184448</v>
+        <v>14.8573951721191</v>
       </c>
       <c r="H1361" t="s">
         <v>8</v>
@@ -35833,7 +35833,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G1364" t="n">
-        <v>15.1701822280884</v>
+        <v>15.170184135437</v>
       </c>
       <c r="H1364" t="s">
         <v>8</v>
@@ -35859,7 +35859,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G1365" t="n">
-        <v>15.3265752792358</v>
+        <v>15.3265771865845</v>
       </c>
       <c r="H1365" t="s">
         <v>8</v>
@@ -35911,7 +35911,7 @@
         <v>20</v>
       </c>
       <c r="G1367" t="n">
-        <v>15.6393632888794</v>
+        <v>15.639365196228</v>
       </c>
       <c r="H1367" t="s">
         <v>8</v>
@@ -35937,7 +35937,7 @@
         <v>19.9400005340576</v>
       </c>
       <c r="G1368" t="n">
-        <v>15.5924472808838</v>
+        <v>15.5924453735352</v>
       </c>
       <c r="H1368" t="s">
         <v>8</v>
@@ -35989,7 +35989,7 @@
         <v>20.0400009155273</v>
       </c>
       <c r="G1370" t="n">
-        <v>15.6706438064575</v>
+        <v>15.6706418991089</v>
       </c>
       <c r="H1370" t="s">
         <v>8</v>
@@ -36171,7 +36171,7 @@
         <v>20.8600006103516</v>
       </c>
       <c r="G1377" t="n">
-        <v>16.3118572235107</v>
+        <v>16.3118591308594</v>
       </c>
       <c r="H1377" t="s">
         <v>8</v>
@@ -36223,7 +36223,7 @@
         <v>21.0400009155273</v>
       </c>
       <c r="G1379" t="n">
-        <v>16.4526100158691</v>
+        <v>16.4526119232178</v>
       </c>
       <c r="H1379" t="s">
         <v>8</v>
@@ -36275,7 +36275,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1381" t="n">
-        <v>15.7175617218018</v>
+        <v>15.7175598144531</v>
       </c>
       <c r="H1381" t="s">
         <v>8</v>
@@ -36301,7 +36301,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1382" t="n">
-        <v>15.7175617218018</v>
+        <v>15.7175598144531</v>
       </c>
       <c r="H1382" t="s">
         <v>8</v>
@@ -36327,7 +36327,7 @@
         <v>20.1599998474121</v>
       </c>
       <c r="G1383" t="n">
-        <v>15.7644777297974</v>
+        <v>15.7644786834717</v>
       </c>
       <c r="H1383" t="s">
         <v>8</v>
@@ -36353,7 +36353,7 @@
         <v>20.6800003051758</v>
       </c>
       <c r="G1384" t="n">
-        <v>16.1711025238037</v>
+        <v>16.1711044311523</v>
       </c>
       <c r="H1384" t="s">
         <v>8</v>
@@ -36405,7 +36405,7 @@
         <v>20.5400009155273</v>
       </c>
       <c r="G1386" t="n">
-        <v>16.0616283416748</v>
+        <v>16.0616302490234</v>
       </c>
       <c r="H1386" t="s">
         <v>8</v>
@@ -36457,7 +36457,7 @@
         <v>20.3600006103516</v>
       </c>
       <c r="G1388" t="n">
-        <v>15.9208717346191</v>
+        <v>15.9208736419678</v>
       </c>
       <c r="H1388" t="s">
         <v>8</v>
@@ -36509,7 +36509,7 @@
         <v>20.2199993133545</v>
       </c>
       <c r="G1390" t="n">
-        <v>15.8113965988159</v>
+        <v>15.8113946914673</v>
       </c>
       <c r="H1390" t="s">
         <v>8</v>
@@ -36561,7 +36561,7 @@
         <v>20.1599998474121</v>
       </c>
       <c r="G1392" t="n">
-        <v>15.7644777297974</v>
+        <v>15.7644786834717</v>
       </c>
       <c r="H1392" t="s">
         <v>8</v>
@@ -36613,7 +36613,7 @@
         <v>20.6200008392334</v>
       </c>
       <c r="G1394" t="n">
-        <v>16.1241836547852</v>
+        <v>16.1241855621338</v>
       </c>
       <c r="H1394" t="s">
         <v>8</v>
@@ -36665,7 +36665,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1396" t="n">
-        <v>15.7175617218018</v>
+        <v>15.7175598144531</v>
       </c>
       <c r="H1396" t="s">
         <v>8</v>
@@ -36691,7 +36691,7 @@
         <v>20.1800003051758</v>
       </c>
       <c r="G1397" t="n">
-        <v>15.7801179885864</v>
+        <v>15.7801198959351</v>
       </c>
       <c r="H1397" t="s">
         <v>8</v>
@@ -36717,7 +36717,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G1398" t="n">
-        <v>15.7957563400269</v>
+        <v>15.7957582473755</v>
       </c>
       <c r="H1398" t="s">
         <v>8</v>
@@ -36743,7 +36743,7 @@
         <v>20.6800003051758</v>
       </c>
       <c r="G1399" t="n">
-        <v>16.1711025238037</v>
+        <v>16.1711044311523</v>
       </c>
       <c r="H1399" t="s">
         <v>8</v>
@@ -36795,7 +36795,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G1401" t="n">
-        <v>15.9521532058716</v>
+        <v>15.9521512985229</v>
       </c>
       <c r="H1401" t="s">
         <v>8</v>
@@ -36847,7 +36847,7 @@
         <v>20.6800003051758</v>
       </c>
       <c r="G1403" t="n">
-        <v>16.1711025238037</v>
+        <v>16.1711044311523</v>
       </c>
       <c r="H1403" t="s">
         <v>8</v>
@@ -36873,7 +36873,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1404" t="n">
-        <v>16.2649383544922</v>
+        <v>16.2649364471436</v>
       </c>
       <c r="H1404" t="s">
         <v>8</v>
@@ -36925,7 +36925,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1406" t="n">
-        <v>16.2649383544922</v>
+        <v>16.2649364471436</v>
       </c>
       <c r="H1406" t="s">
         <v>8</v>
@@ -36977,7 +36977,7 @@
         <v>20.3400001525879</v>
       </c>
       <c r="G1408" t="n">
-        <v>15.9052314758301</v>
+        <v>15.9052333831787</v>
       </c>
       <c r="H1408" t="s">
         <v>8</v>
@@ -37003,7 +37003,7 @@
         <v>19.1900005340576</v>
       </c>
       <c r="G1409" t="n">
-        <v>15.0059690475464</v>
+        <v>15.005970954895</v>
       </c>
       <c r="H1409" t="s">
         <v>8</v>
@@ -37029,7 +37029,7 @@
         <v>19.1200008392334</v>
       </c>
       <c r="G1410" t="n">
-        <v>14.9512329101562</v>
+        <v>14.9512319564819</v>
       </c>
       <c r="H1410" t="s">
         <v>8</v>
@@ -37133,7 +37133,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1414" t="n">
-        <v>15.7175617218018</v>
+        <v>15.7175598144531</v>
       </c>
       <c r="H1414" t="s">
         <v>8</v>
@@ -37159,7 +37159,7 @@
         <v>19.8199996948242</v>
       </c>
       <c r="G1415" t="n">
-        <v>15.4986124038696</v>
+        <v>15.498610496521</v>
       </c>
       <c r="H1415" t="s">
         <v>8</v>
@@ -37289,7 +37289,7 @@
         <v>19.8199996948242</v>
       </c>
       <c r="G1420" t="n">
-        <v>15.4986124038696</v>
+        <v>15.498610496521</v>
       </c>
       <c r="H1420" t="s">
         <v>8</v>
@@ -37315,7 +37315,7 @@
         <v>22.5400009155273</v>
       </c>
       <c r="G1421" t="n">
-        <v>17.6255626678467</v>
+        <v>17.6255645751953</v>
       </c>
       <c r="H1421" t="s">
         <v>8</v>
@@ -37341,7 +37341,7 @@
         <v>21.9400005340576</v>
       </c>
       <c r="G1422" t="n">
-        <v>17.1563816070557</v>
+        <v>17.156379699707</v>
       </c>
       <c r="H1422" t="s">
         <v>8</v>
@@ -37367,7 +37367,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G1423" t="n">
-        <v>17.1251049041748</v>
+        <v>17.1251029968262</v>
       </c>
       <c r="H1423" t="s">
         <v>8</v>
@@ -37419,7 +37419,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G1425" t="n">
-        <v>17.0469055175781</v>
+        <v>17.0469074249268</v>
       </c>
       <c r="H1425" t="s">
         <v>8</v>
@@ -37575,7 +37575,7 @@
         <v>20.8799991607666</v>
       </c>
       <c r="G1431" t="n">
-        <v>16.3274955749512</v>
+        <v>16.3274974822998</v>
       </c>
       <c r="H1431" t="s">
         <v>8</v>
@@ -37627,7 +37627,7 @@
         <v>20.2199993133545</v>
       </c>
       <c r="G1433" t="n">
-        <v>15.8113965988159</v>
+        <v>15.8113946914673</v>
       </c>
       <c r="H1433" t="s">
         <v>8</v>
@@ -37653,7 +37653,7 @@
         <v>20.3600006103516</v>
       </c>
       <c r="G1434" t="n">
-        <v>15.9208717346191</v>
+        <v>15.9208736419678</v>
       </c>
       <c r="H1434" t="s">
         <v>8</v>
@@ -37679,7 +37679,7 @@
         <v>20.2399997711182</v>
       </c>
       <c r="G1435" t="n">
-        <v>15.827036857605</v>
+        <v>15.8270349502563</v>
       </c>
       <c r="H1435" t="s">
         <v>8</v>
@@ -37835,7 +37835,7 @@
         <v>20.3600006103516</v>
       </c>
       <c r="G1441" t="n">
-        <v>15.9208717346191</v>
+        <v>15.9208736419678</v>
       </c>
       <c r="H1441" t="s">
         <v>8</v>
@@ -37887,7 +37887,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G1443" t="n">
-        <v>15.9521532058716</v>
+        <v>15.9521512985229</v>
       </c>
       <c r="H1443" t="s">
         <v>8</v>
@@ -37939,7 +37939,7 @@
         <v>20.1599998474121</v>
       </c>
       <c r="G1445" t="n">
-        <v>15.7644777297974</v>
+        <v>15.7644786834717</v>
       </c>
       <c r="H1445" t="s">
         <v>8</v>
@@ -37965,7 +37965,7 @@
         <v>20</v>
       </c>
       <c r="G1446" t="n">
-        <v>15.6393632888794</v>
+        <v>15.639365196228</v>
       </c>
       <c r="H1446" t="s">
         <v>8</v>
@@ -38017,7 +38017,7 @@
         <v>19.7199993133545</v>
       </c>
       <c r="G1448" t="n">
-        <v>15.4204120635986</v>
+        <v>15.42041015625</v>
       </c>
       <c r="H1448" t="s">
         <v>8</v>
@@ -38043,7 +38043,7 @@
         <v>19.7800006866455</v>
       </c>
       <c r="G1449" t="n">
-        <v>15.4673299789429</v>
+        <v>15.4673318862915</v>
       </c>
       <c r="H1449" t="s">
         <v>8</v>
@@ -38147,7 +38147,7 @@
         <v>19.4899997711182</v>
       </c>
       <c r="G1453" t="n">
-        <v>15.2405605316162</v>
+        <v>15.2405586242676</v>
       </c>
       <c r="H1453" t="s">
         <v>8</v>
@@ -38277,7 +38277,7 @@
         <v>19.6399993896484</v>
       </c>
       <c r="G1458" t="n">
-        <v>15.357855796814</v>
+        <v>15.357852935791</v>
       </c>
       <c r="H1458" t="s">
         <v>8</v>
@@ -38459,7 +38459,7 @@
         <v>21.3199996948242</v>
       </c>
       <c r="G1465" t="n">
-        <v>16.6715621948242</v>
+        <v>16.6715641021729</v>
       </c>
       <c r="H1465" t="s">
         <v>8</v>
@@ -38485,7 +38485,7 @@
         <v>21.0799999237061</v>
       </c>
       <c r="G1466" t="n">
-        <v>16.4838905334473</v>
+        <v>16.4838886260986</v>
       </c>
       <c r="H1466" t="s">
         <v>8</v>
@@ -38589,7 +38589,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1470" t="n">
-        <v>16.2649383544922</v>
+        <v>16.2649364471436</v>
       </c>
       <c r="H1470" t="s">
         <v>8</v>
@@ -38641,7 +38641,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G1472" t="n">
-        <v>16.4995307922363</v>
+        <v>16.4995288848877</v>
       </c>
       <c r="H1472" t="s">
         <v>8</v>
@@ -38693,7 +38693,7 @@
         <v>20.4799995422363</v>
       </c>
       <c r="G1474" t="n">
-        <v>16.2872009277344</v>
+        <v>16.287202835083</v>
       </c>
       <c r="H1474" t="s">
         <v>8</v>
@@ -38719,7 +38719,7 @@
         <v>20.4400005340576</v>
       </c>
       <c r="G1475" t="n">
-        <v>16.2553901672363</v>
+        <v>16.2553882598877</v>
       </c>
       <c r="H1475" t="s">
         <v>8</v>
@@ -38771,7 +38771,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1477" t="n">
-        <v>16.5416889190674</v>
+        <v>16.5416870117188</v>
       </c>
       <c r="H1477" t="s">
         <v>8</v>
@@ -38797,7 +38797,7 @@
         <v>20.6399993896484</v>
       </c>
       <c r="G1478" t="n">
-        <v>16.4144439697266</v>
+        <v>16.4144458770752</v>
       </c>
       <c r="H1478" t="s">
         <v>8</v>
@@ -38901,7 +38901,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G1482" t="n">
-        <v>16.4621601104736</v>
+        <v>16.4621620178223</v>
       </c>
       <c r="H1482" t="s">
         <v>8</v>
@@ -39031,7 +39031,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1487" t="n">
-        <v>15.9849977493286</v>
+        <v>15.98499584198</v>
       </c>
       <c r="H1487" t="s">
         <v>8</v>
@@ -39213,7 +39213,7 @@
         <v>20</v>
       </c>
       <c r="G1494" t="n">
-        <v>15.9054689407349</v>
+        <v>15.9054708480835</v>
       </c>
       <c r="H1494" t="s">
         <v>8</v>
@@ -39239,7 +39239,7 @@
         <v>19.8600006103516</v>
       </c>
       <c r="G1495" t="n">
-        <v>15.7941293716431</v>
+        <v>15.794132232666</v>
       </c>
       <c r="H1495" t="s">
         <v>8</v>
@@ -39291,7 +39291,7 @@
         <v>19.2099990844727</v>
       </c>
       <c r="G1497" t="n">
-        <v>15.2772016525269</v>
+        <v>15.2772035598755</v>
       </c>
       <c r="H1497" t="s">
         <v>8</v>
@@ -39369,7 +39369,7 @@
         <v>18.7199993133545</v>
       </c>
       <c r="G1500" t="n">
-        <v>14.8875198364258</v>
+        <v>14.8875188827515</v>
       </c>
       <c r="H1500" t="s">
         <v>8</v>
@@ -39395,7 +39395,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1501" t="n">
-        <v>14.792085647583</v>
+        <v>14.7920866012573</v>
       </c>
       <c r="H1501" t="s">
         <v>8</v>
@@ -39421,7 +39421,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1502" t="n">
-        <v>14.9511413574219</v>
+        <v>14.9511394500732</v>
       </c>
       <c r="H1502" t="s">
         <v>8</v>
@@ -39447,7 +39447,7 @@
         <v>18.2700004577637</v>
       </c>
       <c r="G1503" t="n">
-        <v>14.5296468734741</v>
+        <v>14.5296478271484</v>
       </c>
       <c r="H1503" t="s">
         <v>8</v>
@@ -39499,7 +39499,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1505" t="n">
-        <v>14.2353935241699</v>
+        <v>14.2353944778442</v>
       </c>
       <c r="H1505" t="s">
         <v>8</v>
@@ -39551,7 +39551,7 @@
         <v>18.5</v>
       </c>
       <c r="G1507" t="n">
-        <v>14.7125606536865</v>
+        <v>14.7125587463379</v>
       </c>
       <c r="H1507" t="s">
         <v>8</v>
@@ -39577,7 +39577,7 @@
         <v>18.4699993133545</v>
       </c>
       <c r="G1508" t="n">
-        <v>14.6887016296387</v>
+        <v>14.68869972229</v>
       </c>
       <c r="H1508" t="s">
         <v>8</v>
@@ -39603,7 +39603,7 @@
         <v>18.7700004577637</v>
       </c>
       <c r="G1509" t="n">
-        <v>14.9272813796997</v>
+        <v>14.9272842407227</v>
       </c>
       <c r="H1509" t="s">
         <v>8</v>
@@ -39629,7 +39629,7 @@
         <v>19.0200004577637</v>
       </c>
       <c r="G1510" t="n">
-        <v>15.1261005401611</v>
+        <v>15.1261024475098</v>
       </c>
       <c r="H1510" t="s">
         <v>8</v>
@@ -39655,7 +39655,7 @@
         <v>18.8199996948242</v>
       </c>
       <c r="G1511" t="n">
-        <v>14.9670457839966</v>
+        <v>14.9670476913452</v>
       </c>
       <c r="H1511" t="s">
         <v>8</v>
@@ -39681,7 +39681,7 @@
         <v>18.8400001525879</v>
       </c>
       <c r="G1512" t="n">
-        <v>14.9829511642456</v>
+        <v>14.9829530715942</v>
       </c>
       <c r="H1512" t="s">
         <v>8</v>
@@ -39733,7 +39733,7 @@
         <v>18.8899993896484</v>
       </c>
       <c r="G1514" t="n">
-        <v>15.0227155685425</v>
+        <v>15.0227136611938</v>
       </c>
       <c r="H1514" t="s">
         <v>8</v>
@@ -39759,7 +39759,7 @@
         <v>18.6900005340576</v>
       </c>
       <c r="G1515" t="n">
-        <v>14.8636627197266</v>
+        <v>14.8636608123779</v>
       </c>
       <c r="H1515" t="s">
         <v>8</v>
@@ -39785,7 +39785,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1516" t="n">
-        <v>14.8716144561768</v>
+        <v>14.8716154098511</v>
       </c>
       <c r="H1516" t="s">
         <v>8</v>
@@ -39811,7 +39811,7 @@
         <v>18.3899993896484</v>
       </c>
       <c r="G1517" t="n">
-        <v>14.6250782012939</v>
+        <v>14.6250772476196</v>
       </c>
       <c r="H1517" t="s">
         <v>8</v>
@@ -39837,7 +39837,7 @@
         <v>18.3600006103516</v>
       </c>
       <c r="G1518" t="n">
-        <v>14.6012210845947</v>
+        <v>14.6012229919434</v>
       </c>
       <c r="H1518" t="s">
         <v>8</v>
@@ -39863,7 +39863,7 @@
         <v>18</v>
       </c>
       <c r="G1519" t="n">
-        <v>14.3149213790894</v>
+        <v>14.314923286438</v>
       </c>
       <c r="H1519" t="s">
         <v>8</v>
@@ -39889,7 +39889,7 @@
         <v>18.0599994659424</v>
       </c>
       <c r="G1520" t="n">
-        <v>14.3626394271851</v>
+        <v>14.3626384735107</v>
       </c>
       <c r="H1520" t="s">
         <v>8</v>
@@ -39915,7 +39915,7 @@
         <v>18</v>
       </c>
       <c r="G1521" t="n">
-        <v>14.3149213790894</v>
+        <v>14.314923286438</v>
       </c>
       <c r="H1521" t="s">
         <v>8</v>
@@ -39941,7 +39941,7 @@
         <v>18.25</v>
       </c>
       <c r="G1522" t="n">
-        <v>14.5137405395508</v>
+        <v>14.5137414932251</v>
       </c>
       <c r="H1522" t="s">
         <v>8</v>
@@ -39967,7 +39967,7 @@
         <v>18.8400001525879</v>
       </c>
       <c r="G1523" t="n">
-        <v>14.9829511642456</v>
+        <v>14.9829530715942</v>
       </c>
       <c r="H1523" t="s">
         <v>8</v>
@@ -39993,7 +39993,7 @@
         <v>18.8899993896484</v>
       </c>
       <c r="G1524" t="n">
-        <v>15.0227155685425</v>
+        <v>15.0227136611938</v>
       </c>
       <c r="H1524" t="s">
         <v>8</v>
@@ -40123,7 +40123,7 @@
         <v>19.5</v>
       </c>
       <c r="G1529" t="n">
-        <v>15.5078315734863</v>
+        <v>15.507833480835</v>
       </c>
       <c r="H1529" t="s">
         <v>8</v>
@@ -40175,7 +40175,7 @@
         <v>18.8199996948242</v>
       </c>
       <c r="G1531" t="n">
-        <v>14.9670457839966</v>
+        <v>14.9670476913452</v>
       </c>
       <c r="H1531" t="s">
         <v>8</v>
@@ -40227,7 +40227,7 @@
         <v>18.6100006103516</v>
       </c>
       <c r="G1533" t="n">
-        <v>14.8000392913818</v>
+        <v>14.8000402450562</v>
       </c>
       <c r="H1533" t="s">
         <v>8</v>
@@ -40305,7 +40305,7 @@
         <v>18.9300003051758</v>
       </c>
       <c r="G1536" t="n">
-        <v>15.0545272827148</v>
+        <v>15.0545282363892</v>
       </c>
       <c r="H1536" t="s">
         <v>8</v>
@@ -40331,7 +40331,7 @@
         <v>19.3400001525879</v>
       </c>
       <c r="G1537" t="n">
-        <v>15.3805904388428</v>
+        <v>15.3805885314941</v>
       </c>
       <c r="H1537" t="s">
         <v>8</v>
@@ -40383,7 +40383,7 @@
         <v>18.8700008392334</v>
       </c>
       <c r="G1539" t="n">
-        <v>15.0068120956421</v>
+        <v>15.0068101882935</v>
       </c>
       <c r="H1539" t="s">
         <v>8</v>
@@ -40409,7 +40409,7 @@
         <v>18.9899997711182</v>
       </c>
       <c r="G1540" t="n">
-        <v>15.102240562439</v>
+        <v>15.1022424697876</v>
       </c>
       <c r="H1540" t="s">
         <v>8</v>
@@ -40435,7 +40435,7 @@
         <v>18.4200000762939</v>
       </c>
       <c r="G1541" t="n">
-        <v>14.6489372253418</v>
+        <v>14.6489362716675</v>
       </c>
       <c r="H1541" t="s">
         <v>8</v>
@@ -40513,7 +40513,7 @@
         <v>18.4099998474121</v>
       </c>
       <c r="G1544" t="n">
-        <v>14.6409845352173</v>
+        <v>14.6409854888916</v>
       </c>
       <c r="H1544" t="s">
         <v>8</v>
@@ -40539,7 +40539,7 @@
         <v>18.75</v>
       </c>
       <c r="G1545" t="n">
-        <v>14.911376953125</v>
+        <v>14.9113798141479</v>
       </c>
       <c r="H1545" t="s">
         <v>8</v>
@@ -40643,7 +40643,7 @@
         <v>18.8099994659424</v>
       </c>
       <c r="G1549" t="n">
-        <v>14.9590930938721</v>
+        <v>14.9590921401978</v>
       </c>
       <c r="H1549" t="s">
         <v>8</v>
@@ -40669,7 +40669,7 @@
         <v>18.3199996948242</v>
       </c>
       <c r="G1550" t="n">
-        <v>14.569408416748</v>
+        <v>14.5694093704224</v>
       </c>
       <c r="H1550" t="s">
         <v>8</v>
@@ -40695,7 +40695,7 @@
         <v>18.2700004577637</v>
       </c>
       <c r="G1551" t="n">
-        <v>14.5296468734741</v>
+        <v>14.5296478271484</v>
       </c>
       <c r="H1551" t="s">
         <v>8</v>
@@ -40721,7 +40721,7 @@
         <v>17.75</v>
       </c>
       <c r="G1552" t="n">
-        <v>14.1161050796509</v>
+        <v>14.1161041259766</v>
       </c>
       <c r="H1552" t="s">
         <v>8</v>
@@ -40773,7 +40773,7 @@
         <v>17.75</v>
       </c>
       <c r="G1554" t="n">
-        <v>14.1161050796509</v>
+        <v>14.1161041259766</v>
       </c>
       <c r="H1554" t="s">
         <v>8</v>
@@ -40799,7 +40799,7 @@
         <v>18.0599994659424</v>
       </c>
       <c r="G1555" t="n">
-        <v>14.3626394271851</v>
+        <v>14.3626384735107</v>
       </c>
       <c r="H1555" t="s">
         <v>8</v>
@@ -40825,7 +40825,7 @@
         <v>18</v>
       </c>
       <c r="G1556" t="n">
-        <v>14.3149213790894</v>
+        <v>14.314923286438</v>
       </c>
       <c r="H1556" t="s">
         <v>8</v>
@@ -40851,7 +40851,7 @@
         <v>17.9799995422363</v>
       </c>
       <c r="G1557" t="n">
-        <v>14.2990169525146</v>
+        <v>14.2990159988403</v>
       </c>
       <c r="H1557" t="s">
         <v>8</v>
@@ -40877,7 +40877,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1558" t="n">
-        <v>14.5535039901733</v>
+        <v>14.553503036499</v>
       </c>
       <c r="H1558" t="s">
         <v>8</v>
@@ -40903,7 +40903,7 @@
         <v>18.8400001525879</v>
       </c>
       <c r="G1559" t="n">
-        <v>14.9829511642456</v>
+        <v>14.9829530715942</v>
       </c>
       <c r="H1559" t="s">
         <v>8</v>
@@ -40955,7 +40955,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G1561" t="n">
-        <v>14.5932664871216</v>
+        <v>14.5932683944702</v>
       </c>
       <c r="H1561" t="s">
         <v>8</v>
@@ -40981,7 +40981,7 @@
         <v>17.9699993133545</v>
       </c>
       <c r="G1562" t="n">
-        <v>14.2910633087158</v>
+        <v>14.2910642623901</v>
       </c>
       <c r="H1562" t="s">
         <v>8</v>
@@ -41033,7 +41033,7 @@
         <v>17.0799999237061</v>
       </c>
       <c r="G1564" t="n">
-        <v>13.5832710266113</v>
+        <v>13.583270072937</v>
       </c>
       <c r="H1564" t="s">
         <v>8</v>
@@ -41059,7 +41059,7 @@
         <v>16.2900009155273</v>
       </c>
       <c r="G1565" t="n">
-        <v>12.9550046920776</v>
+        <v>12.955005645752</v>
       </c>
       <c r="H1565" t="s">
         <v>8</v>
@@ -41111,7 +41111,7 @@
         <v>16.7399997711182</v>
       </c>
       <c r="G1567" t="n">
-        <v>13.3128786087036</v>
+        <v>13.3128776550293</v>
       </c>
       <c r="H1567" t="s">
         <v>8</v>
@@ -41189,7 +41189,7 @@
         <v>15.5799999237061</v>
       </c>
       <c r="G1570" t="n">
-        <v>12.3903608322144</v>
+        <v>12.39035987854</v>
       </c>
       <c r="H1570" t="s">
         <v>8</v>
@@ -41267,7 +41267,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1573" t="n">
-        <v>12.1676836013794</v>
+        <v>12.1676845550537</v>
       </c>
       <c r="H1573" t="s">
         <v>8</v>
@@ -41345,7 +41345,7 @@
         <v>16.0200004577637</v>
       </c>
       <c r="G1576" t="n">
-        <v>12.7402820587158</v>
+        <v>12.7402811050415</v>
       </c>
       <c r="H1576" t="s">
         <v>8</v>
@@ -41371,7 +41371,7 @@
         <v>16.5</v>
       </c>
       <c r="G1577" t="n">
-        <v>13.1220111846924</v>
+        <v>13.1220121383667</v>
       </c>
       <c r="H1577" t="s">
         <v>8</v>
@@ -41397,7 +41397,7 @@
         <v>15.789999961853</v>
       </c>
       <c r="G1578" t="n">
-        <v>12.5573692321777</v>
+        <v>12.5573682785034</v>
       </c>
       <c r="H1578" t="s">
         <v>8</v>
@@ -41423,7 +41423,7 @@
         <v>16.0400009155273</v>
       </c>
       <c r="G1579" t="n">
-        <v>12.7561874389648</v>
+        <v>12.7561864852905</v>
       </c>
       <c r="H1579" t="s">
         <v>8</v>
@@ -41475,7 +41475,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1581" t="n">
-        <v>12.1676836013794</v>
+        <v>12.1676845550537</v>
       </c>
       <c r="H1581" t="s">
         <v>8</v>
@@ -41501,7 +41501,7 @@
         <v>15.3299999237061</v>
       </c>
       <c r="G1582" t="n">
-        <v>12.1915416717529</v>
+        <v>12.1915426254272</v>
       </c>
       <c r="H1582" t="s">
         <v>8</v>
@@ -41527,7 +41527,7 @@
         <v>15.5799999237061</v>
       </c>
       <c r="G1583" t="n">
-        <v>12.3903608322144</v>
+        <v>12.39035987854</v>
       </c>
       <c r="H1583" t="s">
         <v>8</v>
@@ -41553,7 +41553,7 @@
         <v>15.1300001144409</v>
       </c>
       <c r="G1584" t="n">
-        <v>12.0324869155884</v>
+        <v>12.0324878692627</v>
       </c>
       <c r="H1584" t="s">
         <v>8</v>
@@ -41579,7 +41579,7 @@
         <v>14.9799995422363</v>
       </c>
       <c r="G1585" t="n">
-        <v>11.9131956100464</v>
+        <v>11.9131965637207</v>
       </c>
       <c r="H1585" t="s">
         <v>8</v>
@@ -41605,7 +41605,7 @@
         <v>14.7200002670288</v>
       </c>
       <c r="G1586" t="n">
-        <v>11.7064266204834</v>
+        <v>11.7064256668091</v>
       </c>
       <c r="H1586" t="s">
         <v>8</v>
@@ -41631,7 +41631,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1587" t="n">
-        <v>11.7700481414795</v>
+        <v>11.7700471878052</v>
       </c>
       <c r="H1587" t="s">
         <v>8</v>
@@ -41657,7 +41657,7 @@
         <v>15.039999961853</v>
       </c>
       <c r="G1588" t="n">
-        <v>11.9609136581421</v>
+        <v>11.9609127044678</v>
       </c>
       <c r="H1588" t="s">
         <v>8</v>
@@ -41683,7 +41683,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1589" t="n">
-        <v>12.1676836013794</v>
+        <v>12.1676845550537</v>
       </c>
       <c r="H1589" t="s">
         <v>8</v>
@@ -41735,7 +41735,7 @@
         <v>15.039999961853</v>
       </c>
       <c r="G1591" t="n">
-        <v>11.9609136581421</v>
+        <v>11.9609127044678</v>
       </c>
       <c r="H1591" t="s">
         <v>8</v>
@@ -41839,7 +41839,7 @@
         <v>14.5600004196167</v>
       </c>
       <c r="G1595" t="n">
-        <v>11.5791816711426</v>
+        <v>11.5791826248169</v>
       </c>
       <c r="H1595" t="s">
         <v>8</v>
@@ -41891,7 +41891,7 @@
         <v>14.6400003433228</v>
       </c>
       <c r="G1597" t="n">
-        <v>11.6428031921387</v>
+        <v>11.642804145813</v>
       </c>
       <c r="H1597" t="s">
         <v>8</v>
@@ -42021,7 +42021,7 @@
         <v>16.0200004577637</v>
       </c>
       <c r="G1602" t="n">
-        <v>12.7402820587158</v>
+        <v>12.7402811050415</v>
       </c>
       <c r="H1602" t="s">
         <v>8</v>
@@ -42073,7 +42073,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G1604" t="n">
-        <v>12.6766595840454</v>
+        <v>12.6766576766968</v>
       </c>
       <c r="H1604" t="s">
         <v>8</v>
@@ -42099,7 +42099,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G1605" t="n">
-        <v>12.9947681427002</v>
+        <v>12.9947690963745</v>
       </c>
       <c r="H1605" t="s">
         <v>8</v>
@@ -42255,7 +42255,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G1611" t="n">
-        <v>12.0404415130615</v>
+        <v>12.0404405593872</v>
       </c>
       <c r="H1611" t="s">
         <v>8</v>
@@ -42307,7 +42307,7 @@
         <v>14.4799995422363</v>
       </c>
       <c r="G1613" t="n">
-        <v>11.5155591964722</v>
+        <v>11.5155601501465</v>
       </c>
       <c r="H1613" t="s">
         <v>8</v>
@@ -42333,7 +42333,7 @@
         <v>14.2799997329712</v>
       </c>
       <c r="G1614" t="n">
-        <v>11.3565053939819</v>
+        <v>11.3565044403076</v>
       </c>
       <c r="H1614" t="s">
         <v>8</v>
@@ -42411,7 +42411,7 @@
         <v>14.4200000762939</v>
       </c>
       <c r="G1617" t="n">
-        <v>11.4678440093994</v>
+        <v>11.4678430557251</v>
       </c>
       <c r="H1617" t="s">
         <v>8</v>
@@ -42437,7 +42437,7 @@
         <v>14.5</v>
       </c>
       <c r="G1618" t="n">
-        <v>11.5314645767212</v>
+        <v>11.5314655303955</v>
       </c>
       <c r="H1618" t="s">
         <v>8</v>
@@ -42489,7 +42489,7 @@
         <v>14.6800003051758</v>
       </c>
       <c r="G1620" t="n">
-        <v>11.6746139526367</v>
+        <v>11.674614906311</v>
       </c>
       <c r="H1620" t="s">
         <v>8</v>
@@ -42541,7 +42541,7 @@
         <v>14.5</v>
       </c>
       <c r="G1622" t="n">
-        <v>11.5314645767212</v>
+        <v>11.5314655303955</v>
       </c>
       <c r="H1622" t="s">
         <v>8</v>
@@ -71222,6 +71222,32 @@
         <v>5.61999988555908</v>
       </c>
       <c r="H2725" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2726">
+      <c r="A2726" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B2726" t="n">
+        <v>169511</v>
+      </c>
+      <c r="C2726" t="n">
+        <v>5.67000007629395</v>
+      </c>
+      <c r="D2726" t="n">
+        <v>5.55999994277954</v>
+      </c>
+      <c r="E2726" t="n">
+        <v>5.55999994277954</v>
+      </c>
+      <c r="F2726" t="n">
+        <v>5.59000015258789</v>
+      </c>
+      <c r="G2726" t="n">
+        <v>5.59000015258789</v>
+      </c>
+      <c r="H2726" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/MARR.MI.xlsx
+++ b/data/MARR.MI.xlsx
@@ -473,7 +473,7 @@
         <v>18.2900009155273</v>
       </c>
       <c r="G4" t="n">
-        <v>12.4267063140869</v>
+        <v>12.4267044067383</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>18.0300006866455</v>
       </c>
       <c r="G5" t="n">
-        <v>12.2500524520874</v>
+        <v>12.250054359436</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>17.4699993133545</v>
       </c>
       <c r="G7" t="n">
-        <v>11.8695735931396</v>
+        <v>11.8695755004883</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>17.5599994659424</v>
       </c>
       <c r="G8" t="n">
-        <v>11.9307231903076</v>
+        <v>11.9307241439819</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>17.2600002288818</v>
       </c>
       <c r="G10" t="n">
-        <v>11.7268962860107</v>
+        <v>11.7268953323364</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>17.2700004577637</v>
       </c>
       <c r="G11" t="n">
-        <v>11.7336902618408</v>
+        <v>11.7336893081665</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>17.5900001525879</v>
       </c>
       <c r="G17" t="n">
-        <v>11.9511060714722</v>
+        <v>11.9511070251465</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G19" t="n">
-        <v>11.8356056213379</v>
+        <v>11.8356037139893</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>17.5400009155273</v>
       </c>
       <c r="G20" t="n">
-        <v>11.9171352386475</v>
+        <v>11.9171361923218</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G21" t="n">
-        <v>11.9918727874756</v>
+        <v>11.991870880127</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>15.8299999237061</v>
       </c>
       <c r="G27" t="n">
-        <v>10.7553157806396</v>
+        <v>10.755316734314</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>15.8900003433228</v>
       </c>
       <c r="G28" t="n">
-        <v>10.7960815429688</v>
+        <v>10.7960805892944</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>16.4899997711182</v>
       </c>
       <c r="G29" t="n">
-        <v>11.2037372589111</v>
+        <v>11.2037363052368</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>16.0799999237061</v>
       </c>
       <c r="G30" t="n">
-        <v>10.9251728057861</v>
+        <v>10.9251718521118</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>16.5</v>
       </c>
       <c r="G32" t="n">
-        <v>11.2105312347412</v>
+        <v>11.2105321884155</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>16.9300003051758</v>
       </c>
       <c r="G35" t="n">
-        <v>11.502685546875</v>
+        <v>11.5026836395264</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G36" t="n">
-        <v>11.686131477356</v>
+        <v>11.6861324310303</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>17.6299991607666</v>
       </c>
       <c r="G37" t="n">
-        <v>11.9782819747925</v>
+        <v>11.9782829284668</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>17.4899997711182</v>
       </c>
       <c r="G39" t="n">
-        <v>11.8831634521484</v>
+        <v>11.8831624984741</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G40" t="n">
-        <v>11.8559885025024</v>
+        <v>11.8559865951538</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>18.2600002288818</v>
       </c>
       <c r="G43" t="n">
-        <v>12.4063196182251</v>
+        <v>12.4063215255737</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>17.9599990844727</v>
       </c>
       <c r="G45" t="n">
-        <v>12.2024936676025</v>
+        <v>12.2024927139282</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>18.1399993896484</v>
       </c>
       <c r="G46" t="n">
-        <v>12.3247909545898</v>
+        <v>12.3247919082642</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>17.8799991607666</v>
       </c>
       <c r="G47" t="n">
-        <v>12.1481399536133</v>
+        <v>12.148138999939</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>17.4799995422363</v>
       </c>
       <c r="G48" t="n">
-        <v>11.876368522644</v>
+        <v>11.8763704299927</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>17.4799995422363</v>
       </c>
       <c r="G49" t="n">
-        <v>11.876368522644</v>
+        <v>11.8763704299927</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>16.7600002288818</v>
       </c>
       <c r="G50" t="n">
-        <v>11.3871812820435</v>
+        <v>11.3871831893921</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G51" t="n">
-        <v>11.652156829834</v>
+        <v>11.6521596908569</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>17.5799999237061</v>
       </c>
       <c r="G52" t="n">
-        <v>11.9443111419678</v>
+        <v>11.9443120956421</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>17.7800006866455</v>
       </c>
       <c r="G53" t="n">
-        <v>12.0801982879639</v>
+        <v>12.0801973342896</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>17.6200008392334</v>
       </c>
       <c r="G54" t="n">
-        <v>11.9714889526367</v>
+        <v>11.971489906311</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>17.8600006103516</v>
       </c>
       <c r="G56" t="n">
-        <v>12.1345520019531</v>
+        <v>12.1345510482788</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>17.5799999237061</v>
       </c>
       <c r="G57" t="n">
-        <v>11.9443111419678</v>
+        <v>11.9443120956421</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G58" t="n">
-        <v>11.7404842376709</v>
+        <v>11.7404851913452</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>17.6200008392334</v>
       </c>
       <c r="G60" t="n">
-        <v>11.9714889526367</v>
+        <v>11.971489906311</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>17.5900001525879</v>
       </c>
       <c r="G62" t="n">
-        <v>11.9511060714722</v>
+        <v>11.9511070251465</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>18.25</v>
       </c>
       <c r="G64" t="n">
-        <v>12.399528503418</v>
+        <v>12.3995275497437</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>18.5</v>
       </c>
       <c r="G66" t="n">
-        <v>12.5693836212158</v>
+        <v>12.5693845748901</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G67" t="n">
-        <v>12.3315839767456</v>
+        <v>12.3315858840942</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>19.0200004577637</v>
       </c>
       <c r="G71" t="n">
-        <v>12.9226865768433</v>
+        <v>12.9226875305176</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>18.2600002288818</v>
       </c>
       <c r="G74" t="n">
-        <v>12.4063196182251</v>
+        <v>12.4063215255737</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>18.5200004577637</v>
       </c>
       <c r="G75" t="n">
-        <v>12.5829734802246</v>
+        <v>12.582971572876</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G76" t="n">
-        <v>12.3315839767456</v>
+        <v>12.3315858840942</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G77" t="n">
-        <v>12.3315839767456</v>
+        <v>12.3315858840942</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>18.0400009155273</v>
       </c>
       <c r="G78" t="n">
-        <v>12.2568502426147</v>
+        <v>12.2568464279175</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G79" t="n">
-        <v>12.1617279052734</v>
+        <v>12.1617269515991</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G80" t="n">
-        <v>12.0937852859497</v>
+        <v>12.0937843322754</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>17.75</v>
       </c>
       <c r="G81" t="n">
-        <v>12.0598134994507</v>
+        <v>12.059814453125</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>17.7700004577637</v>
       </c>
       <c r="G84" t="n">
-        <v>12.0734043121338</v>
+        <v>12.0734033584595</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>18.4300003051758</v>
       </c>
       <c r="G85" t="n">
-        <v>12.5218257904053</v>
+        <v>12.5218238830566</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>18.2299995422363</v>
       </c>
       <c r="G86" t="n">
-        <v>12.3859386444092</v>
+        <v>12.3859376907349</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>17.8899993896484</v>
       </c>
       <c r="G88" t="n">
-        <v>12.1549339294434</v>
+        <v>12.1549348831177</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>17.9099998474121</v>
       </c>
       <c r="G89" t="n">
-        <v>12.1685237884521</v>
+        <v>12.1685209274292</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>18.0300006866455</v>
       </c>
       <c r="G92" t="n">
-        <v>12.2500524520874</v>
+        <v>12.250054359436</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>17.5699996948242</v>
       </c>
       <c r="G93" t="n">
-        <v>11.937518119812</v>
+        <v>11.9375171661377</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>17.75</v>
       </c>
       <c r="G94" t="n">
-        <v>12.0598134994507</v>
+        <v>12.059814453125</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>17.8700008392334</v>
       </c>
       <c r="G95" t="n">
-        <v>12.1413450241089</v>
+        <v>12.1413459777832</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>17.5300006866455</v>
       </c>
       <c r="G98" t="n">
-        <v>11.9103403091431</v>
+        <v>11.9103393554688</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>17.6900005340576</v>
       </c>
       <c r="G99" t="n">
-        <v>12.0190477371216</v>
+        <v>12.0190496444702</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G100" t="n">
-        <v>12.280177116394</v>
+        <v>12.2801790237427</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>17.3899993896484</v>
       </c>
       <c r="G101" t="n">
-        <v>12.273120880127</v>
+        <v>12.2731218338013</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>17.7099990844727</v>
       </c>
       <c r="G102" t="n">
-        <v>12.4989624023438</v>
+        <v>12.4989633560181</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G103" t="n">
-        <v>12.4919080734253</v>
+        <v>12.491907119751</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>17.9400005340576</v>
       </c>
       <c r="G104" t="n">
-        <v>12.6612873077393</v>
+        <v>12.6612892150879</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>17.7800006866455</v>
       </c>
       <c r="G106" t="n">
-        <v>12.5483675003052</v>
+        <v>12.5483655929565</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>18</v>
       </c>
       <c r="G108" t="n">
-        <v>12.7036352157593</v>
+        <v>12.7036323547363</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>17.8600006103516</v>
       </c>
       <c r="G109" t="n">
-        <v>12.6048288345337</v>
+        <v>12.6048278808594</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>17.8600006103516</v>
       </c>
       <c r="G110" t="n">
-        <v>12.6048288345337</v>
+        <v>12.6048278808594</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>17.9400005340576</v>
       </c>
       <c r="G111" t="n">
-        <v>12.6612873077393</v>
+        <v>12.6612892150879</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>17.75</v>
       </c>
       <c r="G112" t="n">
-        <v>12.5271940231323</v>
+        <v>12.5271949768066</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>17.7399997711182</v>
       </c>
       <c r="G114" t="n">
-        <v>12.5201377868652</v>
+        <v>12.5201368331909</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G115" t="n">
-        <v>12.068452835083</v>
+        <v>12.0684518814087</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>17.2099990844727</v>
       </c>
       <c r="G116" t="n">
-        <v>12.1460828781128</v>
+        <v>12.1460847854614</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G117" t="n">
-        <v>11.8920125961304</v>
+        <v>11.8920116424561</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G118" t="n">
-        <v>11.6097097396851</v>
+        <v>11.6097106933594</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>16.6299991607666</v>
       </c>
       <c r="G119" t="n">
-        <v>11.7367448806763</v>
+        <v>11.7367458343506</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>17.1100006103516</v>
       </c>
       <c r="G120" t="n">
-        <v>12.0755100250244</v>
+        <v>12.0755090713501</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>17.1100006103516</v>
       </c>
       <c r="G121" t="n">
-        <v>12.0755100250244</v>
+        <v>12.0755090713501</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>17.0900001525879</v>
       </c>
       <c r="G122" t="n">
-        <v>12.0613946914673</v>
+        <v>12.061393737793</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>17.4699993133545</v>
       </c>
       <c r="G123" t="n">
-        <v>12.3295822143555</v>
+        <v>12.3295812606812</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G125" t="n">
-        <v>11.1086206436157</v>
+        <v>11.10862159729</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>17.0100002288818</v>
       </c>
       <c r="G127" t="n">
-        <v>12.0049333572388</v>
+        <v>12.0049343109131</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>17.0100002288818</v>
       </c>
       <c r="G128" t="n">
-        <v>12.0049333572388</v>
+        <v>12.0049343109131</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>17.9300003051758</v>
       </c>
       <c r="G129" t="n">
-        <v>12.6542310714722</v>
+        <v>12.6542320251465</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>18.0699996948242</v>
       </c>
       <c r="G130" t="n">
-        <v>12.7530374526978</v>
+        <v>12.7530384063721</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>17.9400005340576</v>
       </c>
       <c r="G131" t="n">
-        <v>12.6612873077393</v>
+        <v>12.6612892150879</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G132" t="n">
-        <v>12.3084106445312</v>
+        <v>12.3084096908569</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>17.8099994659424</v>
       </c>
       <c r="G134" t="n">
-        <v>12.569540977478</v>
+        <v>12.5695390701294</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>17.9300003051758</v>
       </c>
       <c r="G135" t="n">
-        <v>12.6542310714722</v>
+        <v>12.6542320251465</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>18.3799991607666</v>
       </c>
       <c r="G136" t="n">
-        <v>12.9718227386475</v>
+        <v>12.9718208312988</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>18</v>
       </c>
       <c r="G137" t="n">
-        <v>12.7036352157593</v>
+        <v>12.7036323547363</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>18.3400001525879</v>
       </c>
       <c r="G138" t="n">
-        <v>12.9435911178589</v>
+        <v>12.9435920715332</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>18.3299999237061</v>
       </c>
       <c r="G139" t="n">
-        <v>12.9365339279175</v>
+        <v>12.9365329742432</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>18.0200004577637</v>
       </c>
       <c r="G141" t="n">
-        <v>12.7177495956421</v>
+        <v>12.7177486419678</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>18.3799991607666</v>
       </c>
       <c r="G143" t="n">
-        <v>12.9718227386475</v>
+        <v>12.9718208312988</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>18.7199993133545</v>
       </c>
       <c r="G144" t="n">
-        <v>13.2117795944214</v>
+        <v>13.2117786407471</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>18.3099994659424</v>
       </c>
       <c r="G145" t="n">
-        <v>12.9224185943604</v>
+        <v>12.9224195480347</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G147" t="n">
-        <v>13.3035268783569</v>
+        <v>13.3035287857056</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>18.6700000762939</v>
       </c>
       <c r="G148" t="n">
-        <v>13.1764917373657</v>
+        <v>13.1764898300171</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>18.8099994659424</v>
       </c>
       <c r="G149" t="n">
-        <v>13.2752952575684</v>
+        <v>13.275297164917</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G150" t="n">
-        <v>13.3035268783569</v>
+        <v>13.3035287857056</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>18.3600006103516</v>
       </c>
       <c r="G151" t="n">
-        <v>12.957709312439</v>
+        <v>12.9577054977417</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>17.7800006866455</v>
       </c>
       <c r="G154" t="n">
-        <v>12.5483675003052</v>
+        <v>12.5483655929565</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>18.0400009155273</v>
       </c>
       <c r="G155" t="n">
-        <v>12.7318658828735</v>
+        <v>12.7318639755249</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>18.2199993133545</v>
       </c>
       <c r="G156" t="n">
-        <v>12.8588991165161</v>
+        <v>12.8589010238647</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>18.25</v>
       </c>
       <c r="G157" t="n">
-        <v>12.8800735473633</v>
+        <v>12.880072593689</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>18.1800003051758</v>
       </c>
       <c r="G158" t="n">
-        <v>12.8306703567505</v>
+        <v>12.8306713104248</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>17.8299999237061</v>
       </c>
       <c r="G159" t="n">
-        <v>12.5836553573608</v>
+        <v>12.5836563110352</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>17.9200000762939</v>
       </c>
       <c r="G160" t="n">
-        <v>12.6471729278564</v>
+        <v>12.6471719741821</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>17.75</v>
       </c>
       <c r="G162" t="n">
-        <v>12.5271940231323</v>
+        <v>12.5271949768066</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>17.75</v>
       </c>
       <c r="G163" t="n">
-        <v>12.5271940231323</v>
+        <v>12.5271949768066</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G164" t="n">
-        <v>12.280177116394</v>
+        <v>12.2801790237427</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G167" t="n">
-        <v>12.3154668807983</v>
+        <v>12.3154678344727</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>17.75</v>
       </c>
       <c r="G169" t="n">
-        <v>12.5271940231323</v>
+        <v>12.5271949768066</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>17.5599994659424</v>
       </c>
       <c r="G170" t="n">
-        <v>12.3930997848511</v>
+        <v>12.3931007385254</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>17.2700004577637</v>
       </c>
       <c r="G171" t="n">
-        <v>12.1884326934814</v>
+        <v>12.1884298324585</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>17.3899993896484</v>
       </c>
       <c r="G172" t="n">
-        <v>12.273120880127</v>
+        <v>12.2731218338013</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>17.6399993896484</v>
       </c>
       <c r="G173" t="n">
-        <v>12.4495601654053</v>
+        <v>12.449559211731</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>17.5100002288818</v>
       </c>
       <c r="G174" t="n">
-        <v>12.357813835144</v>
+        <v>12.3578128814697</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>17.6299991607666</v>
       </c>
       <c r="G175" t="n">
-        <v>12.4425029754639</v>
+        <v>12.4425020217896</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>17.9400005340576</v>
       </c>
       <c r="G176" t="n">
-        <v>12.6612873077393</v>
+        <v>12.6612892150879</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>17.8299999237061</v>
       </c>
       <c r="G177" t="n">
-        <v>12.5836553573608</v>
+        <v>12.5836563110352</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>17.3799991607666</v>
       </c>
       <c r="G179" t="n">
-        <v>12.2660636901855</v>
+        <v>12.2660646438599</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>17.25</v>
       </c>
       <c r="G180" t="n">
-        <v>12.1743144989014</v>
+        <v>12.1743154525757</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>17.1800003051758</v>
       </c>
       <c r="G181" t="n">
-        <v>12.1249132156372</v>
+        <v>12.1249141693115</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G182" t="n">
-        <v>12.3084106445312</v>
+        <v>12.3084096908569</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G183" t="n">
-        <v>12.3154668807983</v>
+        <v>12.3154678344727</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G184" t="n">
-        <v>12.280177116394</v>
+        <v>12.2801790237427</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>17.2900009155273</v>
       </c>
       <c r="G185" t="n">
-        <v>12.2025461196899</v>
+        <v>12.2025451660156</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>17.7399997711182</v>
       </c>
       <c r="G187" t="n">
-        <v>12.5201377868652</v>
+        <v>12.5201368331909</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>17.7399997711182</v>
       </c>
       <c r="G189" t="n">
-        <v>12.5201377868652</v>
+        <v>12.5201368331909</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>17.4699993133545</v>
       </c>
       <c r="G190" t="n">
-        <v>12.3295822143555</v>
+        <v>12.3295812606812</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>17.6200008392334</v>
       </c>
       <c r="G191" t="n">
-        <v>12.4354476928711</v>
+        <v>12.4354457855225</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G194" t="n">
-        <v>12.4566202163696</v>
+        <v>12.456618309021</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>17.75</v>
       </c>
       <c r="G195" t="n">
-        <v>12.5271940231323</v>
+        <v>12.5271949768066</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>17.8199996948242</v>
       </c>
       <c r="G196" t="n">
-        <v>12.5765991210938</v>
+        <v>12.5765972137451</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>17.6299991607666</v>
       </c>
       <c r="G198" t="n">
-        <v>12.4425029754639</v>
+        <v>12.4425020217896</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>17.3199996948242</v>
       </c>
       <c r="G200" t="n">
-        <v>12.2237167358398</v>
+        <v>12.2237186431885</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G201" t="n">
-        <v>12.1390285491943</v>
+        <v>12.139030456543</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G204" t="n">
-        <v>12.0331630706787</v>
+        <v>12.033164024353</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G206" t="n">
-        <v>12.068452835083</v>
+        <v>12.0684518814087</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>17.0400009155273</v>
       </c>
       <c r="G208" t="n">
-        <v>12.0261077880859</v>
+        <v>12.0261096954346</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>16.7399997711182</v>
       </c>
       <c r="G213" t="n">
-        <v>11.8143787384033</v>
+        <v>11.8143796920776</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>16.6299991607666</v>
       </c>
       <c r="G218" t="n">
-        <v>11.7367448806763</v>
+        <v>11.7367458343506</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G219" t="n">
-        <v>11.7579174041748</v>
+        <v>11.7579183578491</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G221" t="n">
-        <v>11.6097097396851</v>
+        <v>11.6097106933594</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>16.6299991607666</v>
       </c>
       <c r="G222" t="n">
-        <v>11.7367448806763</v>
+        <v>11.7367458343506</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>16.5599994659424</v>
       </c>
       <c r="G224" t="n">
-        <v>11.6873416900635</v>
+        <v>11.6873426437378</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>16</v>
       </c>
       <c r="G225" t="n">
-        <v>11.2921190261841</v>
+        <v>11.2921180725098</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>16.5100002288818</v>
       </c>
       <c r="G226" t="n">
-        <v>11.6520557403564</v>
+        <v>11.6520538330078</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G229" t="n">
-        <v>11.6732292175293</v>
+        <v>11.673228263855</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G231" t="n">
-        <v>11.7579174041748</v>
+        <v>11.7579183578491</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>16.5699996948242</v>
       </c>
       <c r="G233" t="n">
-        <v>11.6944007873535</v>
+        <v>11.6944017410278</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>16.3899993896484</v>
       </c>
       <c r="G234" t="n">
-        <v>11.5673627853394</v>
+        <v>11.567364692688</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G239" t="n">
-        <v>11.6097097396851</v>
+        <v>11.6097106933594</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>17</v>
       </c>
       <c r="G240" t="n">
-        <v>11.9978761672974</v>
+        <v>11.997875213623</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G241" t="n">
-        <v>12.1390285491943</v>
+        <v>12.139030456543</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>16.9300003051758</v>
       </c>
       <c r="G242" t="n">
-        <v>11.9484720230103</v>
+        <v>11.9484739303589</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>17.2099990844727</v>
       </c>
       <c r="G243" t="n">
-        <v>12.1460828781128</v>
+        <v>12.1460847854614</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>17</v>
       </c>
       <c r="G244" t="n">
-        <v>11.9978761672974</v>
+        <v>11.997875213623</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>17.3899993896484</v>
       </c>
       <c r="G247" t="n">
-        <v>12.273120880127</v>
+        <v>12.2731218338013</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G249" t="n">
-        <v>12.3154668807983</v>
+        <v>12.3154678344727</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>17.5400009155273</v>
       </c>
       <c r="G250" t="n">
-        <v>12.3789873123169</v>
+        <v>12.3789863586426</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>17.5100002288818</v>
       </c>
       <c r="G252" t="n">
-        <v>12.357813835144</v>
+        <v>12.3578128814697</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>17.6100006103516</v>
       </c>
       <c r="G255" t="n">
-        <v>12.4283885955811</v>
+        <v>12.4283876419067</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>17.3899993896484</v>
       </c>
       <c r="G258" t="n">
-        <v>12.273120880127</v>
+        <v>12.2731218338013</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>17.5400009155273</v>
       </c>
       <c r="G259" t="n">
-        <v>12.3789873123169</v>
+        <v>12.3789863586426</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>17.5900001525879</v>
       </c>
       <c r="G261" t="n">
-        <v>12.4142732620239</v>
+        <v>12.4142742156982</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>17.6700000762939</v>
       </c>
       <c r="G262" t="n">
-        <v>12.4707336425781</v>
+        <v>12.4707345962524</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G263" t="n">
-        <v>12.4566202163696</v>
+        <v>12.456618309021</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>17.3199996948242</v>
       </c>
       <c r="G266" t="n">
-        <v>12.2237167358398</v>
+        <v>12.2237186431885</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>17.75</v>
       </c>
       <c r="G269" t="n">
-        <v>12.5271940231323</v>
+        <v>12.5271949768066</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G270" t="n">
-        <v>12.6330575942993</v>
+        <v>12.6330585479736</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>18.3799991607666</v>
       </c>
       <c r="G272" t="n">
-        <v>12.9718227386475</v>
+        <v>12.9718208312988</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>18.5200004577637</v>
       </c>
       <c r="G273" t="n">
-        <v>13.070629119873</v>
+        <v>13.0706272125244</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>18.5900001525879</v>
       </c>
       <c r="G274" t="n">
-        <v>13.1200323104858</v>
+        <v>13.1200304031372</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>18.25</v>
       </c>
       <c r="G275" t="n">
-        <v>12.8800735473633</v>
+        <v>12.880072593689</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>17.9599990844727</v>
       </c>
       <c r="G277" t="n">
-        <v>12.6754026412964</v>
+        <v>12.6754035949707</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>18.0499992370605</v>
       </c>
       <c r="G280" t="n">
-        <v>12.7389211654663</v>
+        <v>12.738920211792</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>18.4699993133545</v>
       </c>
       <c r="G282" t="n">
-        <v>13.0353393554688</v>
+        <v>13.0353403091431</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G283" t="n">
-        <v>12.8447866439819</v>
+        <v>12.8447856903076</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>18.2199993133545</v>
       </c>
       <c r="G284" t="n">
-        <v>12.8588991165161</v>
+        <v>12.8589010238647</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>18.4400005340576</v>
       </c>
       <c r="G285" t="n">
-        <v>13.0141677856445</v>
+        <v>13.0141687393188</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>18.4099998474121</v>
       </c>
       <c r="G286" t="n">
-        <v>12.992995262146</v>
+        <v>12.9929943084717</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G287" t="n">
-        <v>12.8447866439819</v>
+        <v>12.8447856903076</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G288" t="n">
-        <v>12.8447866439819</v>
+        <v>12.8447856903076</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G289" t="n">
-        <v>12.9153594970703</v>
+        <v>12.9153614044189</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>18.4099998474121</v>
       </c>
       <c r="G292" t="n">
-        <v>12.992995262146</v>
+        <v>12.9929943084717</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G294" t="n">
-        <v>12.9153594970703</v>
+        <v>12.9153614044189</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>18.5100002288818</v>
       </c>
       <c r="G295" t="n">
-        <v>13.0635709762573</v>
+        <v>13.0635681152344</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>18.3899993896484</v>
       </c>
       <c r="G296" t="n">
-        <v>12.9788780212402</v>
+        <v>12.9788799285889</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>18.1200008392334</v>
       </c>
       <c r="G297" t="n">
-        <v>12.7883253097534</v>
+        <v>12.7883234024048</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>18.5599994659424</v>
       </c>
       <c r="G298" t="n">
-        <v>13.0988578796387</v>
+        <v>13.0988569259644</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>19.1499996185303</v>
       </c>
       <c r="G299" t="n">
-        <v>13.5152540206909</v>
+        <v>13.5152549743652</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>19.4500007629395</v>
       </c>
       <c r="G300" t="n">
-        <v>13.7269840240479</v>
+        <v>13.7269821166992</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>20</v>
       </c>
       <c r="G303" t="n">
-        <v>14.1151504516602</v>
+        <v>14.1151475906372</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G306" t="n">
-        <v>13.9739952087402</v>
+        <v>13.9739971160889</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>20.3099994659424</v>
       </c>
       <c r="G308" t="n">
-        <v>14.3339338302612</v>
+        <v>14.3339357376099</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>20.9899997711182</v>
       </c>
       <c r="G309" t="n">
-        <v>14.8138475418091</v>
+        <v>14.8138494491577</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>20.2199993133545</v>
       </c>
       <c r="G310" t="n">
-        <v>14.2704133987427</v>
+        <v>14.270414352417</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>20.25</v>
       </c>
       <c r="G311" t="n">
-        <v>14.2915878295898</v>
+        <v>14.2915868759155</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>20.4200000762939</v>
       </c>
       <c r="G312" t="n">
-        <v>14.4115686416626</v>
+        <v>14.4115676879883</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G316" t="n">
-        <v>14.7856197357178</v>
+        <v>14.7856178283691</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>21</v>
       </c>
       <c r="G317" t="n">
-        <v>14.8209066390991</v>
+        <v>14.8209037780762</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>20.75</v>
       </c>
       <c r="G318" t="n">
-        <v>14.6444692611694</v>
+        <v>14.6444664001465</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>20.2600002288818</v>
       </c>
       <c r="G320" t="n">
-        <v>14.2986459732056</v>
+        <v>14.2986469268799</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G322" t="n">
-        <v>14.3268728256226</v>
+        <v>14.3268747329712</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>20.7700004577637</v>
       </c>
       <c r="G324" t="n">
-        <v>14.6585826873779</v>
+        <v>14.6585855484009</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G325" t="n">
-        <v>14.5386037826538</v>
+        <v>14.5386028289795</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>20.8400001525879</v>
       </c>
       <c r="G327" t="n">
-        <v>14.7079839706421</v>
+        <v>14.7079849243164</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>21</v>
       </c>
       <c r="G329" t="n">
-        <v>14.8209066390991</v>
+        <v>14.8209037780762</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>21.0200004577637</v>
       </c>
       <c r="G330" t="n">
-        <v>14.8350219726562</v>
+        <v>14.8350191116333</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>20.8199996948242</v>
       </c>
       <c r="G331" t="n">
-        <v>14.6938695907593</v>
+        <v>14.693868637085</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>21.25</v>
       </c>
       <c r="G332" t="n">
-        <v>14.9973459243774</v>
+        <v>14.9973478317261</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>21.9400005340576</v>
       </c>
       <c r="G333" t="n">
-        <v>15.4843149185181</v>
+        <v>15.4843187332153</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>20.9699993133545</v>
       </c>
       <c r="G335" t="n">
-        <v>14.7997312545776</v>
+        <v>14.7997341156006</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>21.75</v>
       </c>
       <c r="G336" t="n">
-        <v>15.3502216339111</v>
+        <v>15.3502225875854</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>21.8099994659424</v>
       </c>
       <c r="G337" t="n">
-        <v>15.3925676345825</v>
+        <v>15.3925695419312</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>21.7199993133545</v>
       </c>
       <c r="G338" t="n">
-        <v>15.3290529251099</v>
+        <v>15.3290519714355</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>21.7299995422363</v>
       </c>
       <c r="G339" t="n">
-        <v>15.3361072540283</v>
+        <v>15.336109161377</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>22.2600002288818</v>
       </c>
       <c r="G342" t="n">
-        <v>15.7101621627808</v>
+        <v>15.7101583480835</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>22.2299995422363</v>
       </c>
       <c r="G345" t="n">
-        <v>15.6889886856079</v>
+        <v>15.6889848709106</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>22.8099994659424</v>
       </c>
       <c r="G346" t="n">
-        <v>16.0983276367188</v>
+        <v>16.098331451416</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>22.3700008392334</v>
       </c>
       <c r="G348" t="n">
-        <v>15.7877941131592</v>
+        <v>15.7877922058105</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G350" t="n">
-        <v>15.9854040145874</v>
+        <v>15.985405921936</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G351" t="n">
-        <v>16.1265544891357</v>
+        <v>16.1265602111816</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>22.0499992370605</v>
       </c>
       <c r="G354" t="n">
-        <v>15.5619525909424</v>
+        <v>15.5619506835938</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>21.5799999237061</v>
       </c>
       <c r="G355" t="n">
-        <v>15.7295980453491</v>
+        <v>15.7295970916748</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G357" t="n">
-        <v>16.1815147399902</v>
+        <v>16.1815128326416</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>22</v>
       </c>
       <c r="G358" t="n">
-        <v>16.0357360839844</v>
+        <v>16.0357322692871</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>21.7900009155273</v>
       </c>
       <c r="G361" t="n">
-        <v>15.8826665878296</v>
+        <v>15.8826684951782</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>22.0200004577637</v>
       </c>
       <c r="G363" t="n">
-        <v>16.050313949585</v>
+        <v>16.0503120422363</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>21.9099998474121</v>
       </c>
       <c r="G364" t="n">
-        <v>15.9701328277588</v>
+        <v>15.9701347351074</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G368" t="n">
-        <v>16.1815147399902</v>
+        <v>16.1815128326416</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G370" t="n">
-        <v>15.5983963012695</v>
+        <v>15.5983972549438</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>21.6200008392334</v>
       </c>
       <c r="G371" t="n">
-        <v>15.7587518692017</v>
+        <v>15.7587537765503</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>21.6599998474121</v>
       </c>
       <c r="G373" t="n">
-        <v>15.7879104614258</v>
+        <v>15.7879095077515</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>22.0400009155273</v>
       </c>
       <c r="G375" t="n">
-        <v>16.0648918151855</v>
+        <v>16.0648899078369</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>21.6399993896484</v>
       </c>
       <c r="G376" t="n">
-        <v>15.7733335494995</v>
+        <v>15.7733316421509</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>20.8099994659424</v>
       </c>
       <c r="G384" t="n">
-        <v>15.1683483123779</v>
+        <v>15.1683464050293</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>20.6100006103516</v>
       </c>
       <c r="G388" t="n">
-        <v>15.0225667953491</v>
+        <v>15.0225677490234</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>21</v>
       </c>
       <c r="G389" t="n">
-        <v>15.3068370819092</v>
+        <v>15.3068351745605</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>20.7900009155273</v>
       </c>
       <c r="G390" t="n">
-        <v>15.1537685394287</v>
+        <v>15.1537666320801</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>20.6900005340576</v>
       </c>
       <c r="G391" t="n">
-        <v>15.0808792114258</v>
+        <v>15.0808801651001</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>21</v>
       </c>
       <c r="G392" t="n">
-        <v>15.3068370819092</v>
+        <v>15.3068351745605</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>21.8500003814697</v>
       </c>
       <c r="G395" t="n">
-        <v>15.926399230957</v>
+        <v>15.9264011383057</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>22</v>
       </c>
       <c r="G397" t="n">
-        <v>16.0357360839844</v>
+        <v>16.0357322692871</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G398" t="n">
-        <v>16.2544040679932</v>
+        <v>16.2544021606445</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>22.0599994659424</v>
       </c>
       <c r="G399" t="n">
-        <v>16.0794696807861</v>
+        <v>16.0794677734375</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>22.3600006103516</v>
       </c>
       <c r="G400" t="n">
-        <v>16.2981395721436</v>
+        <v>16.2981376647949</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>22.3600006103516</v>
       </c>
       <c r="G401" t="n">
-        <v>16.2981395721436</v>
+        <v>16.2981376647949</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>22.3700008392334</v>
       </c>
       <c r="G402" t="n">
-        <v>16.3054275512695</v>
+        <v>16.3054237365723</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>22.5</v>
       </c>
       <c r="G403" t="n">
-        <v>16.4001846313477</v>
+        <v>16.400182723999</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>21.6200008392334</v>
       </c>
       <c r="G405" t="n">
-        <v>15.7587518692017</v>
+        <v>15.7587537765503</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>21.5799999237061</v>
       </c>
       <c r="G406" t="n">
-        <v>15.7295980453491</v>
+        <v>15.7295970916748</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G408" t="n">
-        <v>16.2908477783203</v>
+        <v>16.2908496856689</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G410" t="n">
-        <v>15.7441740036011</v>
+        <v>15.7441778182983</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G412" t="n">
-        <v>15.7441740036011</v>
+        <v>15.7441778182983</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>21.4099998474121</v>
       </c>
       <c r="G413" t="n">
-        <v>15.6056871414185</v>
+        <v>15.6056823730469</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>21.3199996948242</v>
       </c>
       <c r="G414" t="n">
-        <v>15.5400867462158</v>
+        <v>15.5400829315186</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G415" t="n">
-        <v>15.8170642852783</v>
+        <v>15.817066192627</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G416" t="n">
-        <v>15.7441740036011</v>
+        <v>15.7441778182983</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>21.3600006103516</v>
       </c>
       <c r="G417" t="n">
-        <v>15.5692405700684</v>
+        <v>15.5692386627197</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>21.1900005340576</v>
       </c>
       <c r="G418" t="n">
-        <v>15.4453296661377</v>
+        <v>15.4453277587891</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>21.2099990844727</v>
       </c>
       <c r="G419" t="n">
-        <v>15.459903717041</v>
+        <v>15.4599056243896</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>21.3600006103516</v>
       </c>
       <c r="G420" t="n">
-        <v>15.5692405700684</v>
+        <v>15.5692386627197</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>21.0499992370605</v>
       </c>
       <c r="G421" t="n">
-        <v>15.3432836532593</v>
+        <v>15.3432817459106</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>20.7700004577637</v>
       </c>
       <c r="G423" t="n">
-        <v>15.1391916275024</v>
+        <v>15.1391944885254</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>20.6499996185303</v>
       </c>
       <c r="G424" t="n">
-        <v>15.0517244338989</v>
+        <v>15.0517225265503</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>21.2299995422363</v>
       </c>
       <c r="G428" t="n">
-        <v>15.4744815826416</v>
+        <v>15.4744844436646</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G429" t="n">
-        <v>15.5983963012695</v>
+        <v>15.5983972549438</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>21.4599990844727</v>
       </c>
       <c r="G431" t="n">
-        <v>15.642128944397</v>
+        <v>15.6421308517456</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>22.0499992370605</v>
       </c>
       <c r="G435" t="n">
-        <v>16.0721797943115</v>
+        <v>16.0721778869629</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>22.3299999237061</v>
       </c>
       <c r="G437" t="n">
-        <v>16.2762699127197</v>
+        <v>16.2762718200684</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>21.9200000762939</v>
       </c>
       <c r="G438" t="n">
-        <v>15.9774208068848</v>
+        <v>15.9774227142334</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>22</v>
       </c>
       <c r="G439" t="n">
-        <v>16.0357360839844</v>
+        <v>16.0357322692871</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>22.0400009155273</v>
       </c>
       <c r="G440" t="n">
-        <v>16.0648918151855</v>
+        <v>16.0648899078369</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>22.0799999237061</v>
       </c>
       <c r="G441" t="n">
-        <v>16.0940456390381</v>
+        <v>16.0940475463867</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>22.0799999237061</v>
       </c>
       <c r="G442" t="n">
-        <v>16.0940456390381</v>
+        <v>16.0940475463867</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>22.0699996948242</v>
       </c>
       <c r="G443" t="n">
-        <v>16.0867576599121</v>
+        <v>16.0867595672607</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>22.0900001525879</v>
       </c>
       <c r="G444" t="n">
-        <v>16.1013355255127</v>
+        <v>16.1013336181641</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G445" t="n">
-        <v>16.1815147399902</v>
+        <v>16.1815128326416</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>22.3400001525879</v>
       </c>
       <c r="G446" t="n">
-        <v>16.2835597991943</v>
+        <v>16.283561706543</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>22.3700008392334</v>
       </c>
       <c r="G447" t="n">
-        <v>16.3054275512695</v>
+        <v>16.3054237365723</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G448" t="n">
-        <v>16.2544040679932</v>
+        <v>16.2544021606445</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>22.3799991607666</v>
       </c>
       <c r="G449" t="n">
-        <v>16.3127136230469</v>
+        <v>16.3127155303955</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G451" t="n">
-        <v>16.3272933959961</v>
+        <v>16.3272914886475</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>22.7099990844727</v>
       </c>
       <c r="G452" t="n">
-        <v>16.5532512664795</v>
+        <v>16.5532474517822</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>22.7299995422363</v>
       </c>
       <c r="G456" t="n">
-        <v>16.5678291320801</v>
+        <v>16.5678272247314</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>22.6900005340576</v>
       </c>
       <c r="G457" t="n">
-        <v>16.5386734008789</v>
+        <v>16.5386753082275</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>23.4200000762939</v>
       </c>
       <c r="G459" t="n">
-        <v>17.0707664489746</v>
+        <v>17.0707683563232</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G462" t="n">
-        <v>16.2908477783203</v>
+        <v>16.2908496856689</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>22.3899993896484</v>
       </c>
       <c r="G465" t="n">
-        <v>16.3200035095215</v>
+        <v>16.3200016021729</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G467" t="n">
-        <v>16.3637390136719</v>
+        <v>16.3637371063232</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>22.0900001525879</v>
       </c>
       <c r="G471" t="n">
-        <v>16.1013355255127</v>
+        <v>16.1013336181641</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>22</v>
       </c>
       <c r="G472" t="n">
-        <v>16.0357360839844</v>
+        <v>16.0357322692871</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>21.8400001525879</v>
       </c>
       <c r="G474" t="n">
-        <v>15.9191102981567</v>
+        <v>15.9191083908081</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>21.6399993896484</v>
       </c>
       <c r="G475" t="n">
-        <v>15.7733335494995</v>
+        <v>15.7733316421509</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>21.4899997711182</v>
       </c>
       <c r="G476" t="n">
-        <v>15.6639966964722</v>
+        <v>15.6639947891235</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G478" t="n">
-        <v>15.4161720275879</v>
+        <v>15.4161691665649</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>20.75</v>
       </c>
       <c r="G479" t="n">
-        <v>15.1246156692505</v>
+        <v>15.1246137619019</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>20.4699993133545</v>
       </c>
       <c r="G480" t="n">
-        <v>14.9205236434937</v>
+        <v>14.9205207824707</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>21.3199996948242</v>
       </c>
       <c r="G482" t="n">
-        <v>15.5400867462158</v>
+        <v>15.5400829315186</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G483" t="n">
-        <v>15.270393371582</v>
+        <v>15.2703924179077</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>21.5599994659424</v>
       </c>
       <c r="G486" t="n">
-        <v>15.7150192260742</v>
+        <v>15.7150211334229</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G487" t="n">
-        <v>15.5983963012695</v>
+        <v>15.5983972549438</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>21.4099998474121</v>
       </c>
       <c r="G489" t="n">
-        <v>15.6056871414185</v>
+        <v>15.6056823730469</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>21.8199996948242</v>
       </c>
       <c r="G490" t="n">
-        <v>15.9045324325562</v>
+        <v>15.9045343399048</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>21.5799999237061</v>
       </c>
       <c r="G491" t="n">
-        <v>15.7295980453491</v>
+        <v>15.7295970916748</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>21.7099990844727</v>
       </c>
       <c r="G492" t="n">
-        <v>15.8243522644043</v>
+        <v>15.8243541717529</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>21.9400005340576</v>
       </c>
       <c r="G495" t="n">
-        <v>15.9919967651367</v>
+        <v>15.9920015335083</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>21.7399997711182</v>
       </c>
       <c r="G496" t="n">
-        <v>15.8462200164795</v>
+        <v>15.8462219238281</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>21.8899993896484</v>
       </c>
       <c r="G497" t="n">
-        <v>15.9555568695068</v>
+        <v>15.9555530548096</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>21.6599998474121</v>
       </c>
       <c r="G498" t="n">
-        <v>15.7879104614258</v>
+        <v>15.7879095077515</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G502" t="n">
-        <v>15.4161720275879</v>
+        <v>15.4161691665649</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>21.2399997711182</v>
       </c>
       <c r="G503" t="n">
-        <v>15.4817705154419</v>
+        <v>15.4817724227905</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>21</v>
       </c>
       <c r="G504" t="n">
-        <v>15.3068370819092</v>
+        <v>15.3068351745605</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>20.7600002288818</v>
       </c>
       <c r="G505" t="n">
-        <v>15.1318998336792</v>
+        <v>15.1319036483765</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>21.2900009155273</v>
       </c>
       <c r="G506" t="n">
-        <v>15.5182180404663</v>
+        <v>15.5182199478149</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>21.3600006103516</v>
       </c>
       <c r="G507" t="n">
-        <v>15.5692405700684</v>
+        <v>15.5692386627197</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>21.6599998474121</v>
       </c>
       <c r="G509" t="n">
-        <v>15.7879104614258</v>
+        <v>15.7879095077515</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G513" t="n">
-        <v>15.7441740036011</v>
+        <v>15.7441778182983</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>21.9200000762939</v>
       </c>
       <c r="G515" t="n">
-        <v>15.9774208068848</v>
+        <v>15.9774227142334</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>21.9200000762939</v>
       </c>
       <c r="G516" t="n">
-        <v>15.9774208068848</v>
+        <v>15.9774227142334</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>21.7399997711182</v>
       </c>
       <c r="G517" t="n">
-        <v>15.8462200164795</v>
+        <v>15.8462219238281</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>21.3600006103516</v>
       </c>
       <c r="G519" t="n">
-        <v>15.5692405700684</v>
+        <v>15.5692386627197</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>21.7399997711182</v>
       </c>
       <c r="G520" t="n">
-        <v>15.8462200164795</v>
+        <v>15.8462219238281</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>22.0200004577637</v>
       </c>
       <c r="G521" t="n">
-        <v>16.050313949585</v>
+        <v>16.0503120422363</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G522" t="n">
-        <v>16.1815147399902</v>
+        <v>16.1815128326416</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>22.3400001525879</v>
       </c>
       <c r="G523" t="n">
-        <v>16.2835597991943</v>
+        <v>16.283561706543</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>22.4799995422363</v>
       </c>
       <c r="G525" t="n">
-        <v>16.3856048583984</v>
+        <v>16.3856067657471</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>22.8199996948242</v>
       </c>
       <c r="G530" t="n">
-        <v>16.633430480957</v>
+        <v>16.6334285736084</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>22.6399993896484</v>
       </c>
       <c r="G534" t="n">
-        <v>16.5022277832031</v>
+        <v>16.5022296905518</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>22.0599994659424</v>
       </c>
       <c r="G535" t="n">
-        <v>16.0794696807861</v>
+        <v>16.0794677734375</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>21.6599998474121</v>
       </c>
       <c r="G536" t="n">
-        <v>15.7879104614258</v>
+        <v>15.7879095077515</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>21.3400001525879</v>
       </c>
       <c r="G537" t="n">
-        <v>15.5546627044678</v>
+        <v>15.5546607971191</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>21.9599990844727</v>
       </c>
       <c r="G538" t="n">
-        <v>16.0065803527832</v>
+        <v>16.0065784454346</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>21</v>
       </c>
       <c r="G540" t="n">
-        <v>15.3068370819092</v>
+        <v>15.3068351745605</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>20.7600002288818</v>
       </c>
       <c r="G541" t="n">
-        <v>15.1318998336792</v>
+        <v>15.1319036483765</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>21</v>
       </c>
       <c r="G542" t="n">
-        <v>15.3068370819092</v>
+        <v>15.3068351745605</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>21.0799999237061</v>
       </c>
       <c r="G543" t="n">
-        <v>15.3651475906372</v>
+        <v>15.3651514053345</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>21</v>
       </c>
       <c r="G544" t="n">
-        <v>15.3068370819092</v>
+        <v>15.3068351745605</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>21.3400001525879</v>
       </c>
       <c r="G545" t="n">
-        <v>15.5546627044678</v>
+        <v>15.5546607971191</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G546" t="n">
-        <v>15.5983963012695</v>
+        <v>15.5983972549438</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>21.4599990844727</v>
       </c>
       <c r="G549" t="n">
-        <v>15.642128944397</v>
+        <v>15.6421308517456</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>21.5799999237061</v>
       </c>
       <c r="G550" t="n">
-        <v>15.7295980453491</v>
+        <v>15.7295970916748</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>22.0200004577637</v>
       </c>
       <c r="G552" t="n">
-        <v>16.050313949585</v>
+        <v>16.0503120422363</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>21.8600006103516</v>
       </c>
       <c r="G553" t="n">
-        <v>15.933687210083</v>
+        <v>15.9336891174316</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>21</v>
       </c>
       <c r="G556" t="n">
-        <v>15.3068370819092</v>
+        <v>15.3068351745605</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G558" t="n">
-        <v>15.3797254562378</v>
+        <v>15.3797273635864</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>22.3600006103516</v>
       </c>
       <c r="G560" t="n">
-        <v>16.2981395721436</v>
+        <v>16.2981376647949</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>22.5400009155273</v>
       </c>
       <c r="G561" t="n">
-        <v>16.4293403625488</v>
+        <v>16.4293384552002</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G562" t="n">
-        <v>16.3272933959961</v>
+        <v>16.3272914886475</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>22.5</v>
       </c>
       <c r="G563" t="n">
-        <v>16.4001846313477</v>
+        <v>16.400182723999</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>23.8600006103516</v>
       </c>
       <c r="G564" t="n">
-        <v>17.3914852142334</v>
+        <v>17.3914813995361</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>23.7800006866455</v>
       </c>
       <c r="G565" t="n">
-        <v>17.3331718444824</v>
+        <v>17.3331699371338</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>24.4200000762939</v>
       </c>
       <c r="G566" t="n">
-        <v>17.7996654510498</v>
+        <v>17.7996673583984</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>24.7600002288818</v>
       </c>
       <c r="G567" t="n">
-        <v>18.0474891662598</v>
+        <v>18.0474910736084</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>24.1800003051758</v>
       </c>
       <c r="G570" t="n">
-        <v>17.6247310638428</v>
+        <v>17.6247291564941</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>24.1599998474121</v>
       </c>
       <c r="G571" t="n">
-        <v>17.6101531982422</v>
+        <v>17.6101512908936</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>24.1599998474121</v>
       </c>
       <c r="G572" t="n">
-        <v>17.6101531982422</v>
+        <v>17.6101512908936</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>24.1399993896484</v>
       </c>
       <c r="G574" t="n">
-        <v>17.595573425293</v>
+        <v>17.5955715179443</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G576" t="n">
-        <v>18.1495361328125</v>
+        <v>18.1495342254639</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>25.0200004577637</v>
       </c>
       <c r="G578" t="n">
-        <v>18.237003326416</v>
+        <v>18.2370014190674</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G580" t="n">
-        <v>18.4410953521729</v>
+        <v>18.4410934448242</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>24.7600002288818</v>
       </c>
       <c r="G581" t="n">
-        <v>18.0474891662598</v>
+        <v>18.0474910736084</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>25</v>
       </c>
       <c r="G582" t="n">
-        <v>18.2224273681641</v>
+        <v>18.2224254608154</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G584" t="n">
-        <v>18.0766468048096</v>
+        <v>18.0766448974609</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G586" t="n">
-        <v>18.1495361328125</v>
+        <v>18.1495342254639</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>24.7800006866455</v>
       </c>
       <c r="G587" t="n">
-        <v>18.0620670318604</v>
+        <v>18.062068939209</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>24.9400005340576</v>
       </c>
       <c r="G588" t="n">
-        <v>18.1786918640137</v>
+        <v>18.1786937713623</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>24.8799991607666</v>
       </c>
       <c r="G589" t="n">
-        <v>18.1349544525146</v>
+        <v>18.1349582672119</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>24.8400001525879</v>
       </c>
       <c r="G590" t="n">
-        <v>18.1057987213135</v>
+        <v>18.1058006286621</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>24.8799991607666</v>
       </c>
       <c r="G591" t="n">
-        <v>18.1349544525146</v>
+        <v>18.1349582672119</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>24.9200000762939</v>
       </c>
       <c r="G592" t="n">
-        <v>18.1641139984131</v>
+        <v>18.1641159057617</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>24.8799991607666</v>
       </c>
       <c r="G593" t="n">
-        <v>18.1349544525146</v>
+        <v>18.1349582672119</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>25.0200004577637</v>
       </c>
       <c r="G594" t="n">
-        <v>18.237003326416</v>
+        <v>18.2370014190674</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>25.3400001525879</v>
       </c>
       <c r="G597" t="n">
-        <v>18.4702529907227</v>
+        <v>18.470251083374</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G598" t="n">
-        <v>18.3682041168213</v>
+        <v>18.3682060241699</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>25.2399997711182</v>
       </c>
       <c r="G599" t="n">
-        <v>18.3973598480225</v>
+        <v>18.3973617553711</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>25.1599998474121</v>
       </c>
       <c r="G600" t="n">
-        <v>18.3390502929688</v>
+        <v>18.3390483856201</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>25.1599998474121</v>
       </c>
       <c r="G601" t="n">
-        <v>18.3390502929688</v>
+        <v>18.3390483856201</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>24.7600002288818</v>
       </c>
       <c r="G604" t="n">
-        <v>18.0474891662598</v>
+        <v>18.0474910736084</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>24.1399993896484</v>
       </c>
       <c r="G605" t="n">
-        <v>17.595573425293</v>
+        <v>17.5955715179443</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>24.1399993896484</v>
       </c>
       <c r="G606" t="n">
-        <v>17.595573425293</v>
+        <v>17.5955715179443</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>23.4599990844727</v>
       </c>
       <c r="G607" t="n">
-        <v>17.0999240875244</v>
+        <v>17.0999221801758</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>23.7399997711182</v>
       </c>
       <c r="G608" t="n">
-        <v>17.3040142059326</v>
+        <v>17.3040180206299</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>23.4200000762939</v>
       </c>
       <c r="G609" t="n">
-        <v>17.0707664489746</v>
+        <v>17.0707683563232</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>23.4200000762939</v>
       </c>
       <c r="G610" t="n">
-        <v>17.0707664489746</v>
+        <v>17.0707683563232</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>23.3199996948242</v>
       </c>
       <c r="G612" t="n">
-        <v>16.9978771209717</v>
+        <v>16.9978790283203</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>23.2399997711182</v>
       </c>
       <c r="G620" t="n">
-        <v>17.4947147369385</v>
+        <v>17.4947166442871</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>22.7399997711182</v>
       </c>
       <c r="G622" t="n">
-        <v>17.1183261871338</v>
+        <v>17.1183242797852</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G624" t="n">
-        <v>17.6151599884033</v>
+        <v>17.615161895752</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G625" t="n">
-        <v>17.6151599884033</v>
+        <v>17.615161895752</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>23.1200008392334</v>
       </c>
       <c r="G628" t="n">
-        <v>17.4043807983398</v>
+        <v>17.4043827056885</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>22.1800003051758</v>
       </c>
       <c r="G634" t="n">
-        <v>16.6967639923096</v>
+        <v>16.6967658996582</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>23.9799995422363</v>
       </c>
       <c r="G646" t="n">
-        <v>18.051778793335</v>
+        <v>18.0517768859863</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>24</v>
       </c>
       <c r="G647" t="n">
-        <v>18.0668334960938</v>
+        <v>18.0668315887451</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>23.1399993896484</v>
       </c>
       <c r="G656" t="n">
-        <v>17.4194393157959</v>
+        <v>17.4194374084473</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>24.1000003814697</v>
       </c>
       <c r="G663" t="n">
-        <v>18.1421089172363</v>
+        <v>18.142110824585</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>24.1000003814697</v>
       </c>
       <c r="G664" t="n">
-        <v>18.1421089172363</v>
+        <v>18.142110824585</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>24.4200000762939</v>
       </c>
       <c r="G666" t="n">
-        <v>18.3830013275146</v>
+        <v>18.3830032348633</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>24</v>
       </c>
       <c r="G668" t="n">
-        <v>18.0668334960938</v>
+        <v>18.0668315887451</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G671" t="n">
-        <v>17.9162769317627</v>
+        <v>17.9162750244141</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>23.9400005340576</v>
       </c>
       <c r="G672" t="n">
-        <v>18.0216655731201</v>
+        <v>18.0216674804688</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>23.8400001525879</v>
       </c>
       <c r="G673" t="n">
-        <v>17.9463901519775</v>
+        <v>17.9463882446289</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>24.2800006866455</v>
       </c>
       <c r="G683" t="n">
-        <v>18.2776126861572</v>
+        <v>18.2776145935059</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>25.3600006103516</v>
       </c>
       <c r="G696" t="n">
-        <v>19.0906219482422</v>
+        <v>19.0906238555908</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>25.6399993896484</v>
       </c>
       <c r="G698" t="n">
-        <v>19.3014030456543</v>
+        <v>19.3014011383057</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>23.5599994659424</v>
       </c>
       <c r="G706" t="n">
-        <v>17.7356052398682</v>
+        <v>17.7356071472168</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>23.4599990844727</v>
       </c>
       <c r="G707" t="n">
-        <v>17.6603298187256</v>
+        <v>17.660327911377</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>21.8400001525879</v>
       </c>
       <c r="G718" t="n">
-        <v>16.4408168792725</v>
+        <v>16.4408149719238</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>21.4599990844727</v>
       </c>
       <c r="G719" t="n">
-        <v>16.1547584533691</v>
+        <v>16.1547603607178</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>21.4599990844727</v>
       </c>
       <c r="G726" t="n">
-        <v>16.1547584533691</v>
+        <v>16.1547603607178</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>21.0799999237061</v>
       </c>
       <c r="G728" t="n">
-        <v>15.8687000274658</v>
+        <v>15.8687019348145</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>21.4599990844727</v>
       </c>
       <c r="G731" t="n">
-        <v>16.1547584533691</v>
+        <v>16.1547603607178</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>20.4799995422363</v>
       </c>
       <c r="G735" t="n">
-        <v>15.4170331954956</v>
+        <v>15.4170322418213</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>19.3799991607666</v>
       </c>
       <c r="G742" t="n">
-        <v>14.5889682769775</v>
+        <v>14.5889663696289</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>19.8400001525879</v>
       </c>
       <c r="G745" t="n">
-        <v>14.9352502822876</v>
+        <v>14.935248374939</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>19.7099990844727</v>
       </c>
       <c r="G746" t="n">
-        <v>14.8373861312866</v>
+        <v>14.8373870849609</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>20.6399993896484</v>
       </c>
       <c r="G751" t="n">
-        <v>15.5374774932861</v>
+        <v>15.5374755859375</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>20.8199996948242</v>
       </c>
       <c r="G752" t="n">
-        <v>15.6729784011841</v>
+        <v>15.6729764938354</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>21.5</v>
       </c>
       <c r="G754" t="n">
-        <v>16.1848697662354</v>
+        <v>16.1848678588867</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>21.5</v>
       </c>
       <c r="G759" t="n">
-        <v>16.1848697662354</v>
+        <v>16.1848678588867</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>20.9200000762939</v>
       </c>
       <c r="G765" t="n">
-        <v>15.7482557296753</v>
+        <v>15.7482576370239</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>21.4599990844727</v>
       </c>
       <c r="G768" t="n">
-        <v>16.1547584533691</v>
+        <v>16.1547603607178</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>21.1399993896484</v>
       </c>
       <c r="G773" t="n">
-        <v>15.9138679504395</v>
+        <v>15.9138660430908</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>21.1800003051758</v>
       </c>
       <c r="G775" t="n">
-        <v>15.94398021698</v>
+        <v>15.9439783096313</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>21.1200008392334</v>
       </c>
       <c r="G776" t="n">
-        <v>15.898814201355</v>
+        <v>15.8988161087036</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>21.1200008392334</v>
       </c>
       <c r="G781" t="n">
-        <v>15.898814201355</v>
+        <v>15.8988161087036</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>20.6399993896484</v>
       </c>
       <c r="G782" t="n">
-        <v>15.5374774932861</v>
+        <v>15.5374755859375</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>20.8199996948242</v>
       </c>
       <c r="G783" t="n">
-        <v>15.6729784011841</v>
+        <v>15.6729764938354</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>20.8199996948242</v>
       </c>
       <c r="G784" t="n">
-        <v>15.6729784011841</v>
+        <v>15.6729764938354</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>21.0799999237061</v>
       </c>
       <c r="G788" t="n">
-        <v>15.8687000274658</v>
+        <v>15.8687019348145</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>20.4799995422363</v>
       </c>
       <c r="G795" t="n">
-        <v>15.4170331954956</v>
+        <v>15.4170322418213</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>20.9200000762939</v>
       </c>
       <c r="G797" t="n">
-        <v>15.7482557296753</v>
+        <v>15.7482576370239</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>20.3199996948242</v>
       </c>
       <c r="G799" t="n">
-        <v>15.2965841293335</v>
+        <v>15.2965822219849</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>19.9300003051758</v>
       </c>
       <c r="G800" t="n">
-        <v>15.0030002593994</v>
+        <v>15.0029983520508</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>21.1800003051758</v>
       </c>
       <c r="G802" t="n">
-        <v>15.94398021698</v>
+        <v>15.9439783096313</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>21.1399993896484</v>
       </c>
       <c r="G803" t="n">
-        <v>15.9138679504395</v>
+        <v>15.9138660430908</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>20.6399993896484</v>
       </c>
       <c r="G809" t="n">
-        <v>15.5374774932861</v>
+        <v>15.5374755859375</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>20.6399993896484</v>
       </c>
       <c r="G815" t="n">
-        <v>15.5374774932861</v>
+        <v>15.5374755859375</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>20.7600002288818</v>
       </c>
       <c r="G817" t="n">
-        <v>15.6278085708618</v>
+        <v>15.6278104782104</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>20.7600002288818</v>
       </c>
       <c r="G819" t="n">
-        <v>15.6278085708618</v>
+        <v>15.6278104782104</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>20.3199996948242</v>
       </c>
       <c r="G825" t="n">
-        <v>15.2965841293335</v>
+        <v>15.2965822219849</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>20.8500003814697</v>
       </c>
       <c r="G843" t="n">
-        <v>15.6955614089966</v>
+        <v>15.6955633163452</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>21.25</v>
       </c>
       <c r="G854" t="n">
-        <v>15.9966773986816</v>
+        <v>15.996675491333</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G855" t="n">
-        <v>15.7708406448364</v>
+        <v>15.7708387374878</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>21.25</v>
       </c>
       <c r="G862" t="n">
-        <v>15.9966773986816</v>
+        <v>15.996675491333</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>20.25</v>
       </c>
       <c r="G867" t="n">
-        <v>15.8348550796509</v>
+        <v>15.8348531723022</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>20.25</v>
       </c>
       <c r="G868" t="n">
-        <v>15.8348550796509</v>
+        <v>15.8348531723022</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G876" t="n">
-        <v>16.3822345733643</v>
+        <v>16.3822326660156</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G884" t="n">
-        <v>15.6784610748291</v>
+        <v>15.6784620285034</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G888" t="n">
-        <v>15.6784610748291</v>
+        <v>15.6784620285034</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G900" t="n">
-        <v>16.3822345733643</v>
+        <v>16.3822326660156</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G904" t="n">
-        <v>15.4829683303833</v>
+        <v>15.4829702377319</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G908" t="n">
-        <v>15.4829683303833</v>
+        <v>15.4829702377319</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>19.4400005340576</v>
       </c>
       <c r="G910" t="n">
-        <v>15.2014617919922</v>
+        <v>15.2014636993408</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>19.1200008392334</v>
       </c>
       <c r="G913" t="n">
-        <v>14.9512319564819</v>
+        <v>14.9512329101562</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>18.9599990844727</v>
       </c>
       <c r="G914" t="n">
-        <v>14.8261156082153</v>
+        <v>14.826117515564</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>18.9599990844727</v>
       </c>
       <c r="G915" t="n">
-        <v>14.8261156082153</v>
+        <v>14.826117515564</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>19.3799991607666</v>
       </c>
       <c r="G917" t="n">
-        <v>15.1545438766479</v>
+        <v>15.1545419692993</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G921" t="n">
-        <v>14.3100175857544</v>
+        <v>14.3100185394287</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>18.5200004577637</v>
       </c>
       <c r="G922" t="n">
-        <v>14.4820518493652</v>
+        <v>14.4820499420166</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>18.6399993896484</v>
       </c>
       <c r="G925" t="n">
-        <v>14.5758857727051</v>
+        <v>14.5758876800537</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>18.6200008392334</v>
       </c>
       <c r="G926" t="n">
-        <v>14.5602493286133</v>
+        <v>14.5602512359619</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>19.6399993896484</v>
       </c>
       <c r="G930" t="n">
-        <v>15.357852935791</v>
+        <v>15.3578548431396</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>20</v>
       </c>
       <c r="G952" t="n">
-        <v>15.639365196228</v>
+        <v>15.6393632888794</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25303,7 +25303,7 @@
         <v>19.3799991607666</v>
       </c>
       <c r="G959" t="n">
-        <v>15.1545438766479</v>
+        <v>15.1545419692993</v>
       </c>
       <c r="H959" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>20.25</v>
       </c>
       <c r="G962" t="n">
-        <v>15.8348550796509</v>
+        <v>15.8348531723022</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>19.3799991607666</v>
       </c>
       <c r="G965" t="n">
-        <v>15.1545438766479</v>
+        <v>15.1545419692993</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>19.1200008392334</v>
       </c>
       <c r="G967" t="n">
-        <v>14.9512319564819</v>
+        <v>14.9512329101562</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G969" t="n">
-        <v>14.7791986465454</v>
+        <v>14.7791976928711</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G970" t="n">
-        <v>14.7010011672974</v>
+        <v>14.7010021209717</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>18.6599998474121</v>
       </c>
       <c r="G971" t="n">
-        <v>14.5915279388428</v>
+        <v>14.5915260314941</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G977" t="n">
-        <v>14.7010011672974</v>
+        <v>14.7010021209717</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>19.6399993896484</v>
       </c>
       <c r="G983" t="n">
-        <v>15.357852935791</v>
+        <v>15.3578548431396</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>19.1200008392334</v>
       </c>
       <c r="G991" t="n">
-        <v>14.9512319564819</v>
+        <v>14.9512329101562</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>19.4400005340576</v>
       </c>
       <c r="G993" t="n">
-        <v>15.2014617919922</v>
+        <v>15.2014636993408</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26213,7 +26213,7 @@
         <v>20.25</v>
       </c>
       <c r="G994" t="n">
-        <v>15.8348550796509</v>
+        <v>15.8348531723022</v>
       </c>
       <c r="H994" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>20.25</v>
       </c>
       <c r="G998" t="n">
-        <v>15.8348550796509</v>
+        <v>15.8348531723022</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>20</v>
       </c>
       <c r="G1031" t="n">
-        <v>15.639365196228</v>
+        <v>15.6393632888794</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>20.25</v>
       </c>
       <c r="G1032" t="n">
-        <v>15.8348550796509</v>
+        <v>15.8348531723022</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>19.3799991607666</v>
       </c>
       <c r="G1038" t="n">
-        <v>15.1545438766479</v>
+        <v>15.1545419692993</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>19.5200004577637</v>
       </c>
       <c r="G1039" t="n">
-        <v>15.2640190124512</v>
+        <v>15.2640209197998</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G1040" t="n">
-        <v>15.4829683303833</v>
+        <v>15.4829702377319</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>20</v>
       </c>
       <c r="G1041" t="n">
-        <v>15.639365196228</v>
+        <v>15.6393632888794</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>20</v>
       </c>
       <c r="G1046" t="n">
-        <v>15.639365196228</v>
+        <v>15.6393632888794</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>20</v>
       </c>
       <c r="G1047" t="n">
-        <v>15.639365196228</v>
+        <v>15.6393632888794</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>20</v>
       </c>
       <c r="G1048" t="n">
-        <v>15.639365196228</v>
+        <v>15.6393632888794</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G1049" t="n">
-        <v>15.4829683303833</v>
+        <v>15.4829702377319</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1056" t="n">
-        <v>13.371657371521</v>
+        <v>13.3716564178467</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>16.4400005340576</v>
       </c>
       <c r="G1058" t="n">
-        <v>12.8555564880371</v>
+        <v>12.8555574417114</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1059" t="n">
-        <v>12.6678857803345</v>
+        <v>12.6678867340088</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1062" t="n">
-        <v>12.6678857803345</v>
+        <v>12.6678867340088</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>14.1800003051758</v>
       </c>
       <c r="G1063" t="n">
-        <v>11.0883083343506</v>
+        <v>11.0883092880249</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G1066" t="n">
-        <v>10.4001760482788</v>
+        <v>10.4001770019531</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G1067" t="n">
-        <v>10.8224401473999</v>
+        <v>10.8224391937256</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>12</v>
       </c>
       <c r="G1070" t="n">
-        <v>9.38361930847168</v>
+        <v>9.38361835479736</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>15.5</v>
       </c>
       <c r="G1074" t="n">
-        <v>12.1205072402954</v>
+        <v>12.1205081939697</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28345,7 +28345,7 @@
         <v>14.8199996948242</v>
       </c>
       <c r="G1076" t="n">
-        <v>11.5887689590454</v>
+        <v>11.5887680053711</v>
       </c>
       <c r="H1076" t="s">
         <v>8</v>
@@ -28449,7 +28449,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G1080" t="n">
-        <v>9.61820793151855</v>
+        <v>9.61820888519287</v>
       </c>
       <c r="H1080" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>12.6800003051758</v>
       </c>
       <c r="G1083" t="n">
-        <v>9.91535758972168</v>
+        <v>9.915358543396</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28709,7 +28709,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1090" t="n">
-        <v>10.0873899459839</v>
+        <v>10.0873889923096</v>
       </c>
       <c r="H1090" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G1092" t="n">
-        <v>9.49309349060059</v>
+        <v>9.4930944442749</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G1094" t="n">
-        <v>9.4305362701416</v>
+        <v>9.43053722381592</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>11.0200004577637</v>
       </c>
       <c r="G1103" t="n">
-        <v>8.61729049682617</v>
+        <v>8.61728954315186</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29125,7 +29125,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G1106" t="n">
-        <v>9.55565071105957</v>
+        <v>9.55565166473389</v>
       </c>
       <c r="H1106" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G1107" t="n">
-        <v>9.61820793151855</v>
+        <v>9.61820888519287</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G1108" t="n">
-        <v>9.14902687072754</v>
+        <v>9.14902782440186</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29255,7 +29255,7 @@
         <v>12</v>
       </c>
       <c r="G1111" t="n">
-        <v>9.38361930847168</v>
+        <v>9.38361835479736</v>
       </c>
       <c r="H1111" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G1113" t="n">
-        <v>9.4305362701416</v>
+        <v>9.43053722381592</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29463,7 +29463,7 @@
         <v>13.1400003433228</v>
       </c>
       <c r="G1119" t="n">
-        <v>10.2750625610352</v>
+        <v>10.2750616073608</v>
       </c>
       <c r="H1119" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>13.1199998855591</v>
       </c>
       <c r="G1122" t="n">
-        <v>10.2594213485718</v>
+        <v>10.2594223022461</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29567,7 +29567,7 @@
         <v>13.1199998855591</v>
       </c>
       <c r="G1123" t="n">
-        <v>10.2594213485718</v>
+        <v>10.2594223022461</v>
       </c>
       <c r="H1123" t="s">
         <v>8</v>
@@ -29723,7 +29723,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1129" t="n">
-        <v>10.3219795227051</v>
+        <v>10.3219804763794</v>
       </c>
       <c r="H1129" t="s">
         <v>8</v>
@@ -29957,7 +29957,7 @@
         <v>13.6199998855591</v>
       </c>
       <c r="G1138" t="n">
-        <v>10.6504068374634</v>
+        <v>10.6504077911377</v>
       </c>
       <c r="H1138" t="s">
         <v>8</v>
@@ -30009,7 +30009,7 @@
         <v>13.2799997329712</v>
       </c>
       <c r="G1140" t="n">
-        <v>10.3845367431641</v>
+        <v>10.3845376968384</v>
       </c>
       <c r="H1140" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>13.0600004196167</v>
       </c>
       <c r="G1142" t="n">
-        <v>10.2125062942505</v>
+        <v>10.2125053405762</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30113,7 +30113,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1144" t="n">
-        <v>10.0873899459839</v>
+        <v>10.0873889923096</v>
       </c>
       <c r="H1144" t="s">
         <v>8</v>
@@ -30451,7 +30451,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1157" t="n">
-        <v>10.0873899459839</v>
+        <v>10.0873889923096</v>
       </c>
       <c r="H1157" t="s">
         <v>8</v>
@@ -30503,7 +30503,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G1159" t="n">
-        <v>9.94663524627686</v>
+        <v>9.94663619995117</v>
       </c>
       <c r="H1159" t="s">
         <v>8</v>
@@ -30685,7 +30685,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G1166" t="n">
-        <v>9.88407897949219</v>
+        <v>9.8840799331665</v>
       </c>
       <c r="H1166" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G1182" t="n">
-        <v>9.99355316162109</v>
+        <v>9.99355220794678</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31127,7 +31127,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1183" t="n">
-        <v>10.3219795227051</v>
+        <v>10.3219804763794</v>
       </c>
       <c r="H1183" t="s">
         <v>8</v>
@@ -31231,7 +31231,7 @@
         <v>13.1400003433228</v>
       </c>
       <c r="G1187" t="n">
-        <v>10.2750625610352</v>
+        <v>10.2750616073608</v>
       </c>
       <c r="H1187" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>13.7600002288818</v>
       </c>
       <c r="G1195" t="n">
-        <v>10.7598829269409</v>
+        <v>10.7598819732666</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31543,7 +31543,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G1199" t="n">
-        <v>10.5878486633301</v>
+        <v>10.5878496170044</v>
       </c>
       <c r="H1199" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G1203" t="n">
-        <v>10.5878486633301</v>
+        <v>10.5878496170044</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31855,7 +31855,7 @@
         <v>14.7200002670288</v>
       </c>
       <c r="G1211" t="n">
-        <v>11.5105724334717</v>
+        <v>11.5105714797974</v>
       </c>
       <c r="H1211" t="s">
         <v>8</v>
@@ -31881,7 +31881,7 @@
         <v>14.4399995803833</v>
       </c>
       <c r="G1212" t="n">
-        <v>11.2916202545166</v>
+        <v>11.2916212081909</v>
       </c>
       <c r="H1212" t="s">
         <v>8</v>
@@ -31907,7 +31907,7 @@
         <v>14.539999961853</v>
       </c>
       <c r="G1213" t="n">
-        <v>11.3698177337646</v>
+        <v>11.369818687439</v>
       </c>
       <c r="H1213" t="s">
         <v>8</v>
@@ -32011,7 +32011,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G1217" t="n">
-        <v>10.4783744812012</v>
+        <v>10.4783735275269</v>
       </c>
       <c r="H1217" t="s">
         <v>8</v>
@@ -32037,7 +32037,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G1218" t="n">
-        <v>10.0248327255249</v>
+        <v>10.0248317718506</v>
       </c>
       <c r="H1218" t="s">
         <v>8</v>
@@ -32089,7 +32089,7 @@
         <v>13.2799997329712</v>
       </c>
       <c r="G1220" t="n">
-        <v>10.3845367431641</v>
+        <v>10.3845376968384</v>
       </c>
       <c r="H1220" t="s">
         <v>8</v>
@@ -32141,7 +32141,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G1222" t="n">
-        <v>10.0248327255249</v>
+        <v>10.0248317718506</v>
       </c>
       <c r="H1222" t="s">
         <v>8</v>
@@ -32245,7 +32245,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G1226" t="n">
-        <v>9.68076515197754</v>
+        <v>9.68076610565186</v>
       </c>
       <c r="H1226" t="s">
         <v>8</v>
@@ -32271,7 +32271,7 @@
         <v>11.5200004577637</v>
       </c>
       <c r="G1227" t="n">
-        <v>9.00827312469482</v>
+        <v>9.00827407836914</v>
       </c>
       <c r="H1227" t="s">
         <v>8</v>
@@ -32401,7 +32401,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G1232" t="n">
-        <v>9.14902687072754</v>
+        <v>9.14902782440186</v>
       </c>
       <c r="H1232" t="s">
         <v>8</v>
@@ -32635,7 +32635,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G1241" t="n">
-        <v>12.5584096908569</v>
+        <v>12.5584087371826</v>
       </c>
       <c r="H1241" t="s">
         <v>8</v>
@@ -32765,7 +32765,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G1246" t="n">
-        <v>12.167426109314</v>
+        <v>12.1674251556396</v>
       </c>
       <c r="H1246" t="s">
         <v>8</v>
@@ -32791,7 +32791,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1247" t="n">
-        <v>12.3550987243652</v>
+        <v>12.3550977706909</v>
       </c>
       <c r="H1247" t="s">
         <v>8</v>
@@ -32895,7 +32895,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G1251" t="n">
-        <v>12.167426109314</v>
+        <v>12.1674251556396</v>
       </c>
       <c r="H1251" t="s">
         <v>8</v>
@@ -32947,7 +32947,7 @@
         <v>15.7799997329712</v>
       </c>
       <c r="G1253" t="n">
-        <v>12.3394575119019</v>
+        <v>12.3394584655762</v>
       </c>
       <c r="H1253" t="s">
         <v>8</v>
@@ -32973,7 +32973,7 @@
         <v>15.7200002670288</v>
       </c>
       <c r="G1254" t="n">
-        <v>12.2925405502319</v>
+        <v>12.2925395965576</v>
       </c>
       <c r="H1254" t="s">
         <v>8</v>
@@ -33129,7 +33129,7 @@
         <v>15.039999961853</v>
       </c>
       <c r="G1260" t="n">
-        <v>11.7608013153076</v>
+        <v>11.7608022689819</v>
       </c>
       <c r="H1260" t="s">
         <v>8</v>
@@ -33181,7 +33181,7 @@
         <v>15.5</v>
       </c>
       <c r="G1262" t="n">
-        <v>12.1205072402954</v>
+        <v>12.1205081939697</v>
       </c>
       <c r="H1262" t="s">
         <v>8</v>
@@ -33285,7 +33285,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1266" t="n">
-        <v>12.3550987243652</v>
+        <v>12.3550977706909</v>
       </c>
       <c r="H1266" t="s">
         <v>8</v>
@@ -33337,7 +33337,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1268" t="n">
-        <v>12.6678857803345</v>
+        <v>12.6678867340088</v>
       </c>
       <c r="H1268" t="s">
         <v>8</v>
@@ -33363,7 +33363,7 @@
         <v>16.8600006103516</v>
       </c>
       <c r="G1269" t="n">
-        <v>13.1839828491211</v>
+        <v>13.1839838027954</v>
       </c>
       <c r="H1269" t="s">
         <v>8</v>
@@ -33389,7 +33389,7 @@
         <v>16.8600006103516</v>
       </c>
       <c r="G1270" t="n">
-        <v>13.1839828491211</v>
+        <v>13.1839838027954</v>
       </c>
       <c r="H1270" t="s">
         <v>8</v>
@@ -33415,7 +33415,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1271" t="n">
-        <v>13.371657371521</v>
+        <v>13.3716564178467</v>
       </c>
       <c r="H1271" t="s">
         <v>8</v>
@@ -33441,7 +33441,7 @@
         <v>17.3199996948242</v>
       </c>
       <c r="G1272" t="n">
-        <v>13.5436878204346</v>
+        <v>13.5436887741089</v>
       </c>
       <c r="H1272" t="s">
         <v>8</v>
@@ -33493,7 +33493,7 @@
         <v>17.7199993133545</v>
       </c>
       <c r="G1274" t="n">
-        <v>13.8564767837524</v>
+        <v>13.8564758300781</v>
       </c>
       <c r="H1274" t="s">
         <v>8</v>
@@ -33519,7 +33519,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1275" t="n">
-        <v>13.9190340042114</v>
+        <v>13.9190330505371</v>
       </c>
       <c r="H1275" t="s">
         <v>8</v>
@@ -33597,7 +33597,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1278" t="n">
-        <v>13.6062450408936</v>
+        <v>13.6062469482422</v>
       </c>
       <c r="H1278" t="s">
         <v>8</v>
@@ -33623,7 +33623,7 @@
         <v>17.8199996948242</v>
       </c>
       <c r="G1279" t="n">
-        <v>13.9346742630005</v>
+        <v>13.9346733093262</v>
       </c>
       <c r="H1279" t="s">
         <v>8</v>
@@ -33753,7 +33753,7 @@
         <v>17.1599998474121</v>
       </c>
       <c r="G1284" t="n">
-        <v>13.4185733795166</v>
+        <v>13.4185743331909</v>
       </c>
       <c r="H1284" t="s">
         <v>8</v>
@@ -33857,7 +33857,7 @@
         <v>16.9400005340576</v>
       </c>
       <c r="G1288" t="n">
-        <v>13.246542930603</v>
+        <v>13.2465419769287</v>
       </c>
       <c r="H1288" t="s">
         <v>8</v>
@@ -33935,7 +33935,7 @@
         <v>17.2199993133545</v>
       </c>
       <c r="G1291" t="n">
-        <v>13.4654912948608</v>
+        <v>13.4654922485352</v>
       </c>
       <c r="H1291" t="s">
         <v>8</v>
@@ -33961,7 +33961,7 @@
         <v>17.3199996948242</v>
       </c>
       <c r="G1292" t="n">
-        <v>13.5436878204346</v>
+        <v>13.5436887741089</v>
       </c>
       <c r="H1292" t="s">
         <v>8</v>
@@ -34013,7 +34013,7 @@
         <v>18</v>
       </c>
       <c r="G1294" t="n">
-        <v>14.0754289627075</v>
+        <v>14.0754270553589</v>
       </c>
       <c r="H1294" t="s">
         <v>8</v>
@@ -34091,7 +34091,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1297" t="n">
-        <v>14.7791986465454</v>
+        <v>14.7791976928711</v>
       </c>
       <c r="H1297" t="s">
         <v>8</v>
@@ -34117,7 +34117,7 @@
         <v>19.2800006866455</v>
       </c>
       <c r="G1298" t="n">
-        <v>15.0763454437256</v>
+        <v>15.0763473510742</v>
       </c>
       <c r="H1298" t="s">
         <v>8</v>
@@ -34221,7 +34221,7 @@
         <v>18.6399993896484</v>
       </c>
       <c r="G1302" t="n">
-        <v>14.5758857727051</v>
+        <v>14.5758876800537</v>
       </c>
       <c r="H1302" t="s">
         <v>8</v>
@@ -34299,7 +34299,7 @@
         <v>18.6599998474121</v>
       </c>
       <c r="G1305" t="n">
-        <v>14.5915279388428</v>
+        <v>14.5915260314941</v>
       </c>
       <c r="H1305" t="s">
         <v>8</v>
@@ -34637,7 +34637,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G1318" t="n">
-        <v>15.4829683303833</v>
+        <v>15.4829702377319</v>
       </c>
       <c r="H1318" t="s">
         <v>8</v>
@@ -34715,7 +34715,7 @@
         <v>19.3799991607666</v>
       </c>
       <c r="G1321" t="n">
-        <v>15.1545438766479</v>
+        <v>15.1545419692993</v>
       </c>
       <c r="H1321" t="s">
         <v>8</v>
@@ -34767,7 +34767,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1323" t="n">
-        <v>14.1536235809326</v>
+        <v>14.1536254882812</v>
       </c>
       <c r="H1323" t="s">
         <v>8</v>
@@ -34819,7 +34819,7 @@
         <v>18.3600006103516</v>
       </c>
       <c r="G1325" t="n">
-        <v>14.3569383621216</v>
+        <v>14.3569374084473</v>
       </c>
       <c r="H1325" t="s">
         <v>8</v>
@@ -34871,7 +34871,7 @@
         <v>18.2600002288818</v>
       </c>
       <c r="G1327" t="n">
-        <v>14.2787380218506</v>
+        <v>14.2787399291992</v>
       </c>
       <c r="H1327" t="s">
         <v>8</v>
@@ -34923,7 +34923,7 @@
         <v>18.5200004577637</v>
       </c>
       <c r="G1329" t="n">
-        <v>14.4820518493652</v>
+        <v>14.4820499420166</v>
       </c>
       <c r="H1329" t="s">
         <v>8</v>
@@ -34949,7 +34949,7 @@
         <v>18.6800003051758</v>
       </c>
       <c r="G1330" t="n">
-        <v>14.6071662902832</v>
+        <v>14.6071643829346</v>
       </c>
       <c r="H1330" t="s">
         <v>8</v>
@@ -35001,7 +35001,7 @@
         <v>18.8400001525879</v>
       </c>
       <c r="G1332" t="n">
-        <v>14.7322816848755</v>
+        <v>14.7322797775269</v>
       </c>
       <c r="H1332" t="s">
         <v>8</v>
@@ -35053,7 +35053,7 @@
         <v>18.6200008392334</v>
       </c>
       <c r="G1334" t="n">
-        <v>14.5602493286133</v>
+        <v>14.5602512359619</v>
       </c>
       <c r="H1334" t="s">
         <v>8</v>
@@ -35131,7 +35131,7 @@
         <v>18.3899993896484</v>
       </c>
       <c r="G1337" t="n">
-        <v>14.3803939819336</v>
+        <v>14.3803958892822</v>
       </c>
       <c r="H1337" t="s">
         <v>8</v>
@@ -35157,7 +35157,7 @@
         <v>18.3600006103516</v>
       </c>
       <c r="G1338" t="n">
-        <v>14.3569383621216</v>
+        <v>14.3569374084473</v>
       </c>
       <c r="H1338" t="s">
         <v>8</v>
@@ -35261,7 +35261,7 @@
         <v>18.7800006866455</v>
       </c>
       <c r="G1342" t="n">
-        <v>14.6853618621826</v>
+        <v>14.6853637695312</v>
       </c>
       <c r="H1342" t="s">
         <v>8</v>
@@ -35339,7 +35339,7 @@
         <v>18.6200008392334</v>
       </c>
       <c r="G1345" t="n">
-        <v>14.5602493286133</v>
+        <v>14.5602512359619</v>
       </c>
       <c r="H1345" t="s">
         <v>8</v>
@@ -35417,7 +35417,7 @@
         <v>18.9699993133545</v>
       </c>
       <c r="G1348" t="n">
-        <v>14.8339347839355</v>
+        <v>14.8339366912842</v>
       </c>
       <c r="H1348" t="s">
         <v>8</v>
@@ -35573,7 +35573,7 @@
         <v>19.1200008392334</v>
       </c>
       <c r="G1354" t="n">
-        <v>14.9512319564819</v>
+        <v>14.9512329101562</v>
       </c>
       <c r="H1354" t="s">
         <v>8</v>
@@ -35625,7 +35625,7 @@
         <v>19.7700004577637</v>
       </c>
       <c r="G1356" t="n">
-        <v>15.459511756897</v>
+        <v>15.4595098495483</v>
       </c>
       <c r="H1356" t="s">
         <v>8</v>
@@ -35911,7 +35911,7 @@
         <v>20</v>
       </c>
       <c r="G1367" t="n">
-        <v>15.639365196228</v>
+        <v>15.6393632888794</v>
       </c>
       <c r="H1367" t="s">
         <v>8</v>
@@ -36249,7 +36249,7 @@
         <v>20.7600002288818</v>
       </c>
       <c r="G1380" t="n">
-        <v>16.2336578369141</v>
+        <v>16.2336597442627</v>
       </c>
       <c r="H1380" t="s">
         <v>8</v>
@@ -36509,7 +36509,7 @@
         <v>20.2199993133545</v>
       </c>
       <c r="G1390" t="n">
-        <v>15.8113946914673</v>
+        <v>15.8113965988159</v>
       </c>
       <c r="H1390" t="s">
         <v>8</v>
@@ -36535,7 +36535,7 @@
         <v>20.3199996948242</v>
       </c>
       <c r="G1391" t="n">
-        <v>15.8895931243896</v>
+        <v>15.889591217041</v>
       </c>
       <c r="H1391" t="s">
         <v>8</v>
@@ -36899,7 +36899,7 @@
         <v>20.9200000762939</v>
       </c>
       <c r="G1405" t="n">
-        <v>16.3587741851807</v>
+        <v>16.3587760925293</v>
       </c>
       <c r="H1405" t="s">
         <v>8</v>
@@ -36951,7 +36951,7 @@
         <v>20.8199996948242</v>
       </c>
       <c r="G1407" t="n">
-        <v>16.2805767059326</v>
+        <v>16.280574798584</v>
       </c>
       <c r="H1407" t="s">
         <v>8</v>
@@ -37029,7 +37029,7 @@
         <v>19.1200008392334</v>
       </c>
       <c r="G1410" t="n">
-        <v>14.9512319564819</v>
+        <v>14.9512329101562</v>
       </c>
       <c r="H1410" t="s">
         <v>8</v>
@@ -37081,7 +37081,7 @@
         <v>19.5400009155273</v>
       </c>
       <c r="G1412" t="n">
-        <v>15.2796592712402</v>
+        <v>15.2796583175659</v>
       </c>
       <c r="H1412" t="s">
         <v>8</v>
@@ -37107,7 +37107,7 @@
         <v>19.5699996948242</v>
       </c>
       <c r="G1413" t="n">
-        <v>15.3031187057495</v>
+        <v>15.3031167984009</v>
       </c>
       <c r="H1413" t="s">
         <v>8</v>
@@ -37341,7 +37341,7 @@
         <v>21.9400005340576</v>
       </c>
       <c r="G1422" t="n">
-        <v>17.156379699707</v>
+        <v>17.1563816070557</v>
       </c>
       <c r="H1422" t="s">
         <v>8</v>
@@ -37393,7 +37393,7 @@
         <v>21.2399997711182</v>
       </c>
       <c r="G1424" t="n">
-        <v>16.6090030670166</v>
+        <v>16.6090049743652</v>
       </c>
       <c r="H1424" t="s">
         <v>8</v>
@@ -37419,7 +37419,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G1425" t="n">
-        <v>17.0469074249268</v>
+        <v>17.0469055175781</v>
       </c>
       <c r="H1425" t="s">
         <v>8</v>
@@ -37523,7 +37523,7 @@
         <v>21.2399997711182</v>
       </c>
       <c r="G1429" t="n">
-        <v>16.6090030670166</v>
+        <v>16.6090049743652</v>
       </c>
       <c r="H1429" t="s">
         <v>8</v>
@@ -37549,7 +37549,7 @@
         <v>20.9799995422363</v>
       </c>
       <c r="G1430" t="n">
-        <v>16.4056930541992</v>
+        <v>16.4056911468506</v>
       </c>
       <c r="H1430" t="s">
         <v>8</v>
@@ -37627,7 +37627,7 @@
         <v>20.2199993133545</v>
       </c>
       <c r="G1433" t="n">
-        <v>15.8113946914673</v>
+        <v>15.8113965988159</v>
       </c>
       <c r="H1433" t="s">
         <v>8</v>
@@ -37757,7 +37757,7 @@
         <v>20.3199996948242</v>
       </c>
       <c r="G1438" t="n">
-        <v>15.8895931243896</v>
+        <v>15.889591217041</v>
       </c>
       <c r="H1438" t="s">
         <v>8</v>
@@ -37783,7 +37783,7 @@
         <v>20.3199996948242</v>
       </c>
       <c r="G1439" t="n">
-        <v>15.8895931243896</v>
+        <v>15.889591217041</v>
       </c>
       <c r="H1439" t="s">
         <v>8</v>
@@ -37965,7 +37965,7 @@
         <v>20</v>
       </c>
       <c r="G1446" t="n">
-        <v>15.639365196228</v>
+        <v>15.6393632888794</v>
       </c>
       <c r="H1446" t="s">
         <v>8</v>
@@ -38095,7 +38095,7 @@
         <v>19.3500003814697</v>
       </c>
       <c r="G1451" t="n">
-        <v>15.131085395813</v>
+        <v>15.1310873031616</v>
       </c>
       <c r="H1451" t="s">
         <v>8</v>
@@ -38225,7 +38225,7 @@
         <v>19.3500003814697</v>
       </c>
       <c r="G1456" t="n">
-        <v>15.131085395813</v>
+        <v>15.1310873031616</v>
       </c>
       <c r="H1456" t="s">
         <v>8</v>
@@ -38277,7 +38277,7 @@
         <v>19.6399993896484</v>
       </c>
       <c r="G1458" t="n">
-        <v>15.357852935791</v>
+        <v>15.3578548431396</v>
       </c>
       <c r="H1458" t="s">
         <v>8</v>
@@ -38355,7 +38355,7 @@
         <v>19.4400005340576</v>
       </c>
       <c r="G1461" t="n">
-        <v>15.2014617919922</v>
+        <v>15.2014636993408</v>
       </c>
       <c r="H1461" t="s">
         <v>8</v>
@@ -38381,7 +38381,7 @@
         <v>21.1399993896484</v>
       </c>
       <c r="G1462" t="n">
-        <v>16.5308074951172</v>
+        <v>16.5308055877686</v>
       </c>
       <c r="H1462" t="s">
         <v>8</v>
@@ -38407,7 +38407,7 @@
         <v>20.5799999237061</v>
       </c>
       <c r="G1463" t="n">
-        <v>16.0929050445557</v>
+        <v>16.0929069519043</v>
       </c>
       <c r="H1463" t="s">
         <v>8</v>
@@ -38433,7 +38433,7 @@
         <v>20.7800006866455</v>
       </c>
       <c r="G1464" t="n">
-        <v>16.2493000030518</v>
+        <v>16.2492980957031</v>
       </c>
       <c r="H1464" t="s">
         <v>8</v>
@@ -38459,7 +38459,7 @@
         <v>21.3199996948242</v>
       </c>
       <c r="G1465" t="n">
-        <v>16.6715641021729</v>
+        <v>16.6715621948242</v>
       </c>
       <c r="H1465" t="s">
         <v>8</v>
@@ -38485,7 +38485,7 @@
         <v>21.0799999237061</v>
       </c>
       <c r="G1466" t="n">
-        <v>16.4838886260986</v>
+        <v>16.4838905334473</v>
       </c>
       <c r="H1466" t="s">
         <v>8</v>
@@ -38667,7 +38667,7 @@
         <v>20.9200000762939</v>
       </c>
       <c r="G1473" t="n">
-        <v>16.3587741851807</v>
+        <v>16.3587760925293</v>
       </c>
       <c r="H1473" t="s">
         <v>8</v>
@@ -38693,7 +38693,7 @@
         <v>20.4799995422363</v>
       </c>
       <c r="G1474" t="n">
-        <v>16.287202835083</v>
+        <v>16.2872009277344</v>
       </c>
       <c r="H1474" t="s">
         <v>8</v>
@@ -38797,7 +38797,7 @@
         <v>20.6399993896484</v>
       </c>
       <c r="G1478" t="n">
-        <v>16.4144458770752</v>
+        <v>16.4144439697266</v>
       </c>
       <c r="H1478" t="s">
         <v>8</v>
@@ -39213,7 +39213,7 @@
         <v>20</v>
       </c>
       <c r="G1494" t="n">
-        <v>15.9054708480835</v>
+        <v>15.9054689407349</v>
       </c>
       <c r="H1494" t="s">
         <v>8</v>
@@ -39421,7 +39421,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1502" t="n">
-        <v>14.9511394500732</v>
+        <v>14.9511413574219</v>
       </c>
       <c r="H1502" t="s">
         <v>8</v>
@@ -39629,7 +39629,7 @@
         <v>19.0200004577637</v>
       </c>
       <c r="G1510" t="n">
-        <v>15.1261024475098</v>
+        <v>15.1261005401611</v>
       </c>
       <c r="H1510" t="s">
         <v>8</v>
@@ -39681,7 +39681,7 @@
         <v>18.8400001525879</v>
       </c>
       <c r="G1512" t="n">
-        <v>14.9829530715942</v>
+        <v>14.9829511642456</v>
       </c>
       <c r="H1512" t="s">
         <v>8</v>
@@ -39733,7 +39733,7 @@
         <v>18.8899993896484</v>
       </c>
       <c r="G1514" t="n">
-        <v>15.0227136611938</v>
+        <v>15.0227146148682</v>
       </c>
       <c r="H1514" t="s">
         <v>8</v>
@@ -39811,7 +39811,7 @@
         <v>18.3899993896484</v>
       </c>
       <c r="G1517" t="n">
-        <v>14.6250772476196</v>
+        <v>14.6250791549683</v>
       </c>
       <c r="H1517" t="s">
         <v>8</v>
@@ -39837,7 +39837,7 @@
         <v>18.3600006103516</v>
       </c>
       <c r="G1518" t="n">
-        <v>14.6012229919434</v>
+        <v>14.601222038269</v>
       </c>
       <c r="H1518" t="s">
         <v>8</v>
@@ -39863,7 +39863,7 @@
         <v>18</v>
       </c>
       <c r="G1519" t="n">
-        <v>14.314923286438</v>
+        <v>14.3149213790894</v>
       </c>
       <c r="H1519" t="s">
         <v>8</v>
@@ -39915,7 +39915,7 @@
         <v>18</v>
       </c>
       <c r="G1521" t="n">
-        <v>14.314923286438</v>
+        <v>14.3149213790894</v>
       </c>
       <c r="H1521" t="s">
         <v>8</v>
@@ -39967,7 +39967,7 @@
         <v>18.8400001525879</v>
       </c>
       <c r="G1523" t="n">
-        <v>14.9829530715942</v>
+        <v>14.9829511642456</v>
       </c>
       <c r="H1523" t="s">
         <v>8</v>
@@ -39993,7 +39993,7 @@
         <v>18.8899993896484</v>
       </c>
       <c r="G1524" t="n">
-        <v>15.0227136611938</v>
+        <v>15.0227146148682</v>
       </c>
       <c r="H1524" t="s">
         <v>8</v>
@@ -40019,7 +40019,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1525" t="n">
-        <v>15.0306692123413</v>
+        <v>15.030668258667</v>
       </c>
       <c r="H1525" t="s">
         <v>8</v>
@@ -40045,7 +40045,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1526" t="n">
-        <v>15.0306692123413</v>
+        <v>15.030668258667</v>
       </c>
       <c r="H1526" t="s">
         <v>8</v>
@@ -40201,7 +40201,7 @@
         <v>18.4799995422363</v>
       </c>
       <c r="G1532" t="n">
-        <v>14.6966533660889</v>
+        <v>14.6966514587402</v>
       </c>
       <c r="H1532" t="s">
         <v>8</v>
@@ -40253,7 +40253,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1534" t="n">
-        <v>15.0306692123413</v>
+        <v>15.030668258667</v>
       </c>
       <c r="H1534" t="s">
         <v>8</v>
@@ -40435,7 +40435,7 @@
         <v>18.4200000762939</v>
       </c>
       <c r="G1541" t="n">
-        <v>14.6489362716675</v>
+        <v>14.6489381790161</v>
       </c>
       <c r="H1541" t="s">
         <v>8</v>
@@ -40461,7 +40461,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1542" t="n">
-        <v>14.1558675765991</v>
+        <v>14.1558666229248</v>
       </c>
       <c r="H1542" t="s">
         <v>8</v>
@@ -40539,7 +40539,7 @@
         <v>18.75</v>
       </c>
       <c r="G1545" t="n">
-        <v>14.9113798141479</v>
+        <v>14.9113779067993</v>
       </c>
       <c r="H1545" t="s">
         <v>8</v>
@@ -40591,7 +40591,7 @@
         <v>18.8299999237061</v>
       </c>
       <c r="G1547" t="n">
-        <v>14.9750003814697</v>
+        <v>14.9749984741211</v>
       </c>
       <c r="H1547" t="s">
         <v>8</v>
@@ -40643,7 +40643,7 @@
         <v>18.8099994659424</v>
       </c>
       <c r="G1549" t="n">
-        <v>14.9590921401978</v>
+        <v>14.9590940475464</v>
       </c>
       <c r="H1549" t="s">
         <v>8</v>
@@ -40669,7 +40669,7 @@
         <v>18.3199996948242</v>
       </c>
       <c r="G1550" t="n">
-        <v>14.5694093704224</v>
+        <v>14.569408416748</v>
       </c>
       <c r="H1550" t="s">
         <v>8</v>
@@ -40721,7 +40721,7 @@
         <v>17.75</v>
       </c>
       <c r="G1552" t="n">
-        <v>14.1161041259766</v>
+        <v>14.1161050796509</v>
       </c>
       <c r="H1552" t="s">
         <v>8</v>
@@ -40747,7 +40747,7 @@
         <v>17.8099994659424</v>
       </c>
       <c r="G1553" t="n">
-        <v>14.1638212203979</v>
+        <v>14.1638202667236</v>
       </c>
       <c r="H1553" t="s">
         <v>8</v>
@@ -40773,7 +40773,7 @@
         <v>17.75</v>
       </c>
       <c r="G1554" t="n">
-        <v>14.1161041259766</v>
+        <v>14.1161050796509</v>
       </c>
       <c r="H1554" t="s">
         <v>8</v>
@@ -40825,7 +40825,7 @@
         <v>18</v>
       </c>
       <c r="G1556" t="n">
-        <v>14.314923286438</v>
+        <v>14.3149213790894</v>
       </c>
       <c r="H1556" t="s">
         <v>8</v>
@@ -40877,7 +40877,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1558" t="n">
-        <v>14.553503036499</v>
+        <v>14.5535049438477</v>
       </c>
       <c r="H1558" t="s">
         <v>8</v>
@@ -40903,7 +40903,7 @@
         <v>18.8400001525879</v>
       </c>
       <c r="G1559" t="n">
-        <v>14.9829530715942</v>
+        <v>14.9829511642456</v>
       </c>
       <c r="H1559" t="s">
         <v>8</v>
@@ -40981,7 +40981,7 @@
         <v>17.9699993133545</v>
       </c>
       <c r="G1562" t="n">
-        <v>14.2910642623901</v>
+        <v>14.2910623550415</v>
       </c>
       <c r="H1562" t="s">
         <v>8</v>
@@ -41007,7 +41007,7 @@
         <v>17.5</v>
       </c>
       <c r="G1563" t="n">
-        <v>13.9172859191895</v>
+        <v>13.9172849655151</v>
       </c>
       <c r="H1563" t="s">
         <v>8</v>
@@ -41319,7 +41319,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G1575" t="n">
-        <v>12.3744554519653</v>
+        <v>12.374454498291</v>
       </c>
       <c r="H1575" t="s">
         <v>8</v>
@@ -41345,7 +41345,7 @@
         <v>16.0200004577637</v>
       </c>
       <c r="G1576" t="n">
-        <v>12.7402811050415</v>
+        <v>12.7402820587158</v>
       </c>
       <c r="H1576" t="s">
         <v>8</v>
@@ -41553,7 +41553,7 @@
         <v>15.1300001144409</v>
       </c>
       <c r="G1584" t="n">
-        <v>12.0324878692627</v>
+        <v>12.0324869155884</v>
       </c>
       <c r="H1584" t="s">
         <v>8</v>
@@ -41605,7 +41605,7 @@
         <v>14.7200002670288</v>
       </c>
       <c r="G1586" t="n">
-        <v>11.7064256668091</v>
+        <v>11.7064247131348</v>
       </c>
       <c r="H1586" t="s">
         <v>8</v>
@@ -41657,7 +41657,7 @@
         <v>15.039999961853</v>
       </c>
       <c r="G1588" t="n">
-        <v>11.9609127044678</v>
+        <v>11.9609136581421</v>
       </c>
       <c r="H1588" t="s">
         <v>8</v>
@@ -41735,7 +41735,7 @@
         <v>15.039999961853</v>
       </c>
       <c r="G1591" t="n">
-        <v>11.9609127044678</v>
+        <v>11.9609136581421</v>
       </c>
       <c r="H1591" t="s">
         <v>8</v>
@@ -41891,7 +41891,7 @@
         <v>14.6400003433228</v>
       </c>
       <c r="G1597" t="n">
-        <v>11.642804145813</v>
+        <v>11.6428031921387</v>
       </c>
       <c r="H1597" t="s">
         <v>8</v>
@@ -42021,7 +42021,7 @@
         <v>16.0200004577637</v>
       </c>
       <c r="G1602" t="n">
-        <v>12.7402811050415</v>
+        <v>12.7402820587158</v>
       </c>
       <c r="H1602" t="s">
         <v>8</v>
@@ -42047,7 +42047,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G1603" t="n">
-        <v>12.628942489624</v>
+        <v>12.6289415359497</v>
       </c>
       <c r="H1603" t="s">
         <v>8</v>
@@ -42073,7 +42073,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G1604" t="n">
-        <v>12.6766576766968</v>
+        <v>12.6766586303711</v>
       </c>
       <c r="H1604" t="s">
         <v>8</v>
@@ -42125,7 +42125,7 @@
         <v>15.7799997329712</v>
       </c>
       <c r="G1606" t="n">
-        <v>12.5494146347046</v>
+        <v>12.5494155883789</v>
       </c>
       <c r="H1606" t="s">
         <v>8</v>
@@ -42593,7 +42593,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G1624" t="n">
-        <v>11.0065851211548</v>
+        <v>11.0065841674805</v>
       </c>
       <c r="H1624" t="s">
         <v>8</v>
@@ -42645,7 +42645,7 @@
         <v>13.1400003433228</v>
       </c>
       <c r="G1626" t="n">
-        <v>10.8172426223755</v>
+        <v>10.8172416687012</v>
       </c>
       <c r="H1626" t="s">
         <v>8</v>
@@ -42697,7 +42697,7 @@
         <v>13.6199998855591</v>
       </c>
       <c r="G1628" t="n">
-        <v>11.2123918533325</v>
+        <v>11.2123928070068</v>
       </c>
       <c r="H1628" t="s">
         <v>8</v>
@@ -42801,7 +42801,7 @@
         <v>13.7600002288818</v>
       </c>
       <c r="G1632" t="n">
-        <v>11.3276443481445</v>
+        <v>11.3276433944702</v>
       </c>
       <c r="H1632" t="s">
         <v>8</v>
@@ -42983,7 +42983,7 @@
         <v>13.2799997329712</v>
       </c>
       <c r="G1639" t="n">
-        <v>10.9324932098389</v>
+        <v>10.9324941635132</v>
       </c>
       <c r="H1639" t="s">
         <v>8</v>
@@ -43035,7 +43035,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G1641" t="n">
-        <v>10.5538082122803</v>
+        <v>10.553807258606</v>
       </c>
       <c r="H1641" t="s">
         <v>8</v>
@@ -43217,7 +43217,7 @@
         <v>13.1400003433228</v>
       </c>
       <c r="G1648" t="n">
-        <v>10.8172426223755</v>
+        <v>10.8172416687012</v>
       </c>
       <c r="H1648" t="s">
         <v>8</v>
@@ -43321,7 +43321,7 @@
         <v>13.460000038147</v>
       </c>
       <c r="G1652" t="n">
-        <v>11.0806741714478</v>
+        <v>11.0806751251221</v>
       </c>
       <c r="H1652" t="s">
         <v>8</v>
@@ -43373,7 +43373,7 @@
         <v>13.1400003433228</v>
       </c>
       <c r="G1654" t="n">
-        <v>10.8172426223755</v>
+        <v>10.8172416687012</v>
       </c>
       <c r="H1654" t="s">
         <v>8</v>
@@ -43399,7 +43399,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1655" t="n">
-        <v>10.6196660995483</v>
+        <v>10.619665145874</v>
       </c>
       <c r="H1655" t="s">
         <v>8</v>
@@ -43425,7 +43425,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G1656" t="n">
-        <v>10.1915864944458</v>
+        <v>10.1915874481201</v>
       </c>
       <c r="H1656" t="s">
         <v>8</v>
@@ -43555,7 +43555,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G1661" t="n">
-        <v>10.5538082122803</v>
+        <v>10.553807258606</v>
       </c>
       <c r="H1661" t="s">
         <v>8</v>
@@ -43581,7 +43581,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G1662" t="n">
-        <v>10.4056262969971</v>
+        <v>10.4056272506714</v>
       </c>
       <c r="H1662" t="s">
         <v>8</v>
@@ -43659,7 +43659,7 @@
         <v>12.9799995422363</v>
       </c>
       <c r="G1665" t="n">
-        <v>10.6855249404907</v>
+        <v>10.6855239868164</v>
       </c>
       <c r="H1665" t="s">
         <v>8</v>
@@ -43685,7 +43685,7 @@
         <v>13.2799997329712</v>
       </c>
       <c r="G1666" t="n">
-        <v>10.9324932098389</v>
+        <v>10.9324941635132</v>
       </c>
       <c r="H1666" t="s">
         <v>8</v>
@@ -43867,7 +43867,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G1673" t="n">
-        <v>10.9489574432373</v>
+        <v>10.9489583969116</v>
       </c>
       <c r="H1673" t="s">
         <v>8</v>
@@ -43971,7 +43971,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G1677" t="n">
-        <v>11.1465330123901</v>
+        <v>11.1465339660645</v>
       </c>
       <c r="H1677" t="s">
         <v>8</v>
@@ -44205,7 +44205,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G1686" t="n">
-        <v>10.5538082122803</v>
+        <v>10.553807258606</v>
       </c>
       <c r="H1686" t="s">
         <v>8</v>
@@ -44231,7 +44231,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G1687" t="n">
-        <v>10.4714851379395</v>
+        <v>10.4714860916138</v>
       </c>
       <c r="H1687" t="s">
         <v>8</v>
@@ -44335,7 +44335,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G1691" t="n">
-        <v>10.059868812561</v>
+        <v>10.0598697662354</v>
       </c>
       <c r="H1691" t="s">
         <v>8</v>
@@ -44387,7 +44387,7 @@
         <v>11.7799997329712</v>
       </c>
       <c r="G1693" t="n">
-        <v>9.69764804840088</v>
+        <v>9.6976490020752</v>
       </c>
       <c r="H1693" t="s">
         <v>8</v>
@@ -44413,7 +44413,7 @@
         <v>11.7799997329712</v>
       </c>
       <c r="G1694" t="n">
-        <v>9.69764804840088</v>
+        <v>9.6976490020752</v>
       </c>
       <c r="H1694" t="s">
         <v>8</v>
@@ -44491,7 +44491,7 @@
         <v>11.5200004577637</v>
       </c>
       <c r="G1697" t="n">
-        <v>9.48360919952393</v>
+        <v>9.48361015319824</v>
       </c>
       <c r="H1697" t="s">
         <v>8</v>
@@ -44517,7 +44517,7 @@
         <v>11.6199998855591</v>
       </c>
       <c r="G1698" t="n">
-        <v>9.56593132019043</v>
+        <v>9.56593227386475</v>
       </c>
       <c r="H1698" t="s">
         <v>8</v>
@@ -44647,7 +44647,7 @@
         <v>11.4399995803833</v>
       </c>
       <c r="G1703" t="n">
-        <v>9.41774940490723</v>
+        <v>9.41775035858154</v>
       </c>
       <c r="H1703" t="s">
         <v>8</v>
@@ -44699,7 +44699,7 @@
         <v>11.5200004577637</v>
       </c>
       <c r="G1705" t="n">
-        <v>9.48360919952393</v>
+        <v>9.48361015319824</v>
       </c>
       <c r="H1705" t="s">
         <v>8</v>
@@ -44777,7 +44777,7 @@
         <v>10.6400003433228</v>
       </c>
       <c r="G1708" t="n">
-        <v>8.7591667175293</v>
+        <v>8.75916767120361</v>
       </c>
       <c r="H1708" t="s">
         <v>8</v>
@@ -44803,7 +44803,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1709" t="n">
-        <v>8.97320747375488</v>
+        <v>8.97320652008057</v>
       </c>
       <c r="H1709" t="s">
         <v>8</v>
@@ -44829,7 +44829,7 @@
         <v>10.5600004196167</v>
       </c>
       <c r="G1710" t="n">
-        <v>8.69330883026123</v>
+        <v>8.69330978393555</v>
       </c>
       <c r="H1710" t="s">
         <v>8</v>
@@ -44881,7 +44881,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G1712" t="n">
-        <v>8.54512596130371</v>
+        <v>8.54512691497803</v>
       </c>
       <c r="H1712" t="s">
         <v>8</v>
@@ -44985,7 +44985,7 @@
         <v>9.72000026702881</v>
       </c>
       <c r="G1716" t="n">
-        <v>8.00179481506348</v>
+        <v>8.00179576873779</v>
       </c>
       <c r="H1716" t="s">
         <v>8</v>
@@ -45063,7 +45063,7 @@
         <v>9.6899995803833</v>
       </c>
       <c r="G1719" t="n">
-        <v>7.97709798812866</v>
+        <v>7.97709703445435</v>
       </c>
       <c r="H1719" t="s">
         <v>8</v>
@@ -45167,7 +45167,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G1723" t="n">
-        <v>7.87007761001587</v>
+        <v>7.87007856369019</v>
       </c>
       <c r="H1723" t="s">
         <v>8</v>
@@ -45349,7 +45349,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G1730" t="n">
-        <v>8.4957332611084</v>
+        <v>8.49573230743408</v>
       </c>
       <c r="H1730" t="s">
         <v>8</v>
@@ -45427,7 +45427,7 @@
         <v>10</v>
       </c>
       <c r="G1733" t="n">
-        <v>8.23230075836182</v>
+        <v>8.2322998046875</v>
       </c>
       <c r="H1733" t="s">
         <v>8</v>
@@ -45583,7 +45583,7 @@
         <v>10.6599998474121</v>
       </c>
       <c r="G1739" t="n">
-        <v>8.77563190460205</v>
+        <v>8.77563095092773</v>
       </c>
       <c r="H1739" t="s">
         <v>8</v>
@@ -45609,7 +45609,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G1740" t="n">
-        <v>8.74270153045654</v>
+        <v>8.74270248413086</v>
       </c>
       <c r="H1740" t="s">
         <v>8</v>
@@ -45635,7 +45635,7 @@
         <v>10.5600004196167</v>
       </c>
       <c r="G1741" t="n">
-        <v>8.69330883026123</v>
+        <v>8.69330978393555</v>
       </c>
       <c r="H1741" t="s">
         <v>8</v>
@@ -45661,7 +45661,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G1742" t="n">
-        <v>8.4957332611084</v>
+        <v>8.49573230743408</v>
       </c>
       <c r="H1742" t="s">
         <v>8</v>
@@ -45739,7 +45739,7 @@
         <v>10.9399995803833</v>
       </c>
       <c r="G1745" t="n">
-        <v>9.00613594055176</v>
+        <v>9.00613498687744</v>
       </c>
       <c r="H1745" t="s">
         <v>8</v>
@@ -45765,7 +45765,7 @@
         <v>11.0200004577637</v>
       </c>
       <c r="G1746" t="n">
-        <v>9.07199478149414</v>
+        <v>9.07199382781982</v>
       </c>
       <c r="H1746" t="s">
         <v>8</v>
@@ -45791,7 +45791,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G1747" t="n">
-        <v>9.35189151763916</v>
+        <v>9.35189247131348</v>
       </c>
       <c r="H1747" t="s">
         <v>8</v>
@@ -45817,7 +45817,7 @@
         <v>11.6199998855591</v>
       </c>
       <c r="G1748" t="n">
-        <v>9.56593132019043</v>
+        <v>9.56593227386475</v>
       </c>
       <c r="H1748" t="s">
         <v>8</v>
@@ -45973,7 +45973,7 @@
         <v>11.0200004577637</v>
       </c>
       <c r="G1754" t="n">
-        <v>9.07199478149414</v>
+        <v>9.07199382781982</v>
       </c>
       <c r="H1754" t="s">
         <v>8</v>
@@ -46077,7 +46077,7 @@
         <v>11.4399995803833</v>
       </c>
       <c r="G1758" t="n">
-        <v>9.41774940490723</v>
+        <v>9.41775035858154</v>
       </c>
       <c r="H1758" t="s">
         <v>8</v>
@@ -46103,7 +46103,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G1759" t="n">
-        <v>9.13785266876221</v>
+        <v>9.13785171508789</v>
       </c>
       <c r="H1759" t="s">
         <v>8</v>
@@ -46181,7 +46181,7 @@
         <v>11.4399995803833</v>
       </c>
       <c r="G1762" t="n">
-        <v>9.41774940490723</v>
+        <v>9.41775035858154</v>
       </c>
       <c r="H1762" t="s">
         <v>8</v>
@@ -46311,7 +46311,7 @@
         <v>11.5600004196167</v>
       </c>
       <c r="G1767" t="n">
-        <v>9.5165376663208</v>
+        <v>9.51653861999512</v>
       </c>
       <c r="H1767" t="s">
         <v>8</v>
@@ -46363,7 +46363,7 @@
         <v>11.4399995803833</v>
       </c>
       <c r="G1769" t="n">
-        <v>9.41774940490723</v>
+        <v>9.41775035858154</v>
       </c>
       <c r="H1769" t="s">
         <v>8</v>
@@ -46415,7 +46415,7 @@
         <v>11.6199998855591</v>
       </c>
       <c r="G1771" t="n">
-        <v>9.56593132019043</v>
+        <v>9.56593227386475</v>
       </c>
       <c r="H1771" t="s">
         <v>8</v>
@@ -46519,7 +46519,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G1775" t="n">
-        <v>9.13785266876221</v>
+        <v>9.13785171508789</v>
       </c>
       <c r="H1775" t="s">
         <v>8</v>
@@ -46857,7 +46857,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G1788" t="n">
-        <v>10.1257276535034</v>
+        <v>10.1257286071777</v>
       </c>
       <c r="H1788" t="s">
         <v>8</v>
@@ -47273,7 +47273,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G1804" t="n">
-        <v>9.9281530380249</v>
+        <v>9.92815399169922</v>
       </c>
       <c r="H1804" t="s">
         <v>8</v>
@@ -47377,7 +47377,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G1808" t="n">
-        <v>9.99401092529297</v>
+        <v>9.99401187896729</v>
       </c>
       <c r="H1808" t="s">
         <v>8</v>
@@ -47533,7 +47533,7 @@
         <v>12</v>
       </c>
       <c r="G1814" t="n">
-        <v>9.87875938415527</v>
+        <v>9.87875843048096</v>
       </c>
       <c r="H1814" t="s">
         <v>8</v>
@@ -47585,7 +47585,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G1816" t="n">
-        <v>9.63179016113281</v>
+        <v>9.63179111480713</v>
       </c>
       <c r="H1816" t="s">
         <v>8</v>
@@ -47611,7 +47611,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G1817" t="n">
-        <v>9.35189151763916</v>
+        <v>9.35189247131348</v>
       </c>
       <c r="H1817" t="s">
         <v>8</v>
@@ -48313,7 +48313,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G1844" t="n">
-        <v>10.5538082122803</v>
+        <v>10.553807258606</v>
       </c>
       <c r="H1844" t="s">
         <v>8</v>
@@ -48339,7 +48339,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1845" t="n">
-        <v>10.8666343688965</v>
+        <v>10.8666353225708</v>
       </c>
       <c r="H1845" t="s">
         <v>8</v>
@@ -48365,7 +48365,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1846" t="n">
-        <v>10.8666343688965</v>
+        <v>10.8666353225708</v>
       </c>
       <c r="H1846" t="s">
         <v>8</v>
@@ -48443,7 +48443,7 @@
         <v>13.6199998855591</v>
       </c>
       <c r="G1849" t="n">
-        <v>11.2123918533325</v>
+        <v>11.2123928070068</v>
       </c>
       <c r="H1849" t="s">
         <v>8</v>
@@ -48469,7 +48469,7 @@
         <v>13.460000038147</v>
       </c>
       <c r="G1850" t="n">
-        <v>11.0806741714478</v>
+        <v>11.0806751251221</v>
       </c>
       <c r="H1850" t="s">
         <v>8</v>
@@ -48521,7 +48521,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G1852" t="n">
-        <v>11.1465330123901</v>
+        <v>11.1465339660645</v>
       </c>
       <c r="H1852" t="s">
         <v>8</v>
@@ -48547,7 +48547,7 @@
         <v>13.6800003051758</v>
       </c>
       <c r="G1853" t="n">
-        <v>11.2617864608765</v>
+        <v>11.2617855072021</v>
       </c>
       <c r="H1853" t="s">
         <v>8</v>
@@ -48573,7 +48573,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G1854" t="n">
-        <v>11.1465330123901</v>
+        <v>11.1465339660645</v>
       </c>
       <c r="H1854" t="s">
         <v>8</v>
@@ -49067,7 +49067,7 @@
         <v>13.6199998855591</v>
       </c>
       <c r="G1873" t="n">
-        <v>11.2123918533325</v>
+        <v>11.2123928070068</v>
       </c>
       <c r="H1873" t="s">
         <v>8</v>
@@ -49093,7 +49093,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G1874" t="n">
-        <v>11.1465330123901</v>
+        <v>11.1465339660645</v>
       </c>
       <c r="H1874" t="s">
         <v>8</v>
@@ -49119,7 +49119,7 @@
         <v>15.4200000762939</v>
       </c>
       <c r="G1875" t="n">
-        <v>12.694206237793</v>
+        <v>12.6942071914673</v>
       </c>
       <c r="H1875" t="s">
         <v>8</v>
@@ -49197,7 +49197,7 @@
         <v>14.7399997711182</v>
       </c>
       <c r="G1878" t="n">
-        <v>12.13440990448</v>
+        <v>12.1344089508057</v>
       </c>
       <c r="H1878" t="s">
         <v>8</v>
@@ -49249,7 +49249,7 @@
         <v>14.4399995803833</v>
       </c>
       <c r="G1880" t="n">
-        <v>12.2078104019165</v>
+        <v>12.2078113555908</v>
       </c>
       <c r="H1880" t="s">
         <v>8</v>
@@ -49327,7 +49327,7 @@
         <v>14.539999961853</v>
       </c>
       <c r="G1883" t="n">
-        <v>12.2923526763916</v>
+        <v>12.2923536300659</v>
       </c>
       <c r="H1883" t="s">
         <v>8</v>
@@ -49379,7 +49379,7 @@
         <v>14.539999961853</v>
       </c>
       <c r="G1885" t="n">
-        <v>12.2923526763916</v>
+        <v>12.2923536300659</v>
       </c>
       <c r="H1885" t="s">
         <v>8</v>
@@ -49457,7 +49457,7 @@
         <v>14.6400003433228</v>
       </c>
       <c r="G1888" t="n">
-        <v>12.3768949508667</v>
+        <v>12.3768939971924</v>
       </c>
       <c r="H1888" t="s">
         <v>8</v>
@@ -49587,7 +49587,7 @@
         <v>15.039999961853</v>
       </c>
       <c r="G1893" t="n">
-        <v>12.7150602340698</v>
+        <v>12.7150611877441</v>
       </c>
       <c r="H1893" t="s">
         <v>8</v>
@@ -49717,7 +49717,7 @@
         <v>14.7200002670288</v>
       </c>
       <c r="G1898" t="n">
-        <v>12.4445285797119</v>
+        <v>12.4445276260376</v>
       </c>
       <c r="H1898" t="s">
         <v>8</v>
@@ -49795,7 +49795,7 @@
         <v>14.7200002670288</v>
       </c>
       <c r="G1901" t="n">
-        <v>12.4445285797119</v>
+        <v>12.4445276260376</v>
       </c>
       <c r="H1901" t="s">
         <v>8</v>
@@ -50081,7 +50081,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G1912" t="n">
-        <v>11.7005615234375</v>
+        <v>11.7005605697632</v>
       </c>
       <c r="H1912" t="s">
         <v>8</v>
@@ -50159,7 +50159,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G1915" t="n">
-        <v>11.7005615234375</v>
+        <v>11.7005605697632</v>
       </c>
       <c r="H1915" t="s">
         <v>8</v>
@@ -50393,7 +50393,7 @@
         <v>13.6800003051758</v>
       </c>
       <c r="G1924" t="n">
-        <v>11.5652952194214</v>
+        <v>11.5652942657471</v>
       </c>
       <c r="H1924" t="s">
         <v>8</v>
@@ -50575,7 +50575,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G1931" t="n">
-        <v>11.7005615234375</v>
+        <v>11.7005605697632</v>
       </c>
       <c r="H1931" t="s">
         <v>8</v>
@@ -50627,7 +50627,7 @@
         <v>13.6199998855591</v>
       </c>
       <c r="G1933" t="n">
-        <v>11.5145692825317</v>
+        <v>11.5145702362061</v>
       </c>
       <c r="H1933" t="s">
         <v>8</v>
@@ -50731,7 +50731,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1937" t="n">
-        <v>10.9058704376221</v>
+        <v>10.9058694839478</v>
       </c>
       <c r="H1937" t="s">
         <v>8</v>
@@ -50757,7 +50757,7 @@
         <v>12.9799995422363</v>
       </c>
       <c r="G1938" t="n">
-        <v>10.973503112793</v>
+        <v>10.9735021591187</v>
       </c>
       <c r="H1938" t="s">
         <v>8</v>
@@ -50861,7 +50861,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G1942" t="n">
-        <v>10.8044204711914</v>
+        <v>10.8044195175171</v>
       </c>
       <c r="H1942" t="s">
         <v>8</v>
@@ -50991,7 +50991,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G1947" t="n">
-        <v>10.6860618591309</v>
+        <v>10.6860628128052</v>
       </c>
       <c r="H1947" t="s">
         <v>8</v>
@@ -51043,7 +51043,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G1949" t="n">
-        <v>10.8382368087769</v>
+        <v>10.8382358551025</v>
       </c>
       <c r="H1949" t="s">
         <v>8</v>
@@ -51173,7 +51173,7 @@
         <v>13.1400003433228</v>
       </c>
       <c r="G1954" t="n">
-        <v>11.1087713241577</v>
+        <v>11.1087703704834</v>
       </c>
       <c r="H1954" t="s">
         <v>8</v>
@@ -51199,7 +51199,7 @@
         <v>13.2799997329712</v>
       </c>
       <c r="G1955" t="n">
-        <v>11.2271270751953</v>
+        <v>11.2271280288696</v>
       </c>
       <c r="H1955" t="s">
         <v>8</v>
@@ -51225,7 +51225,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G1956" t="n">
-        <v>11.2440366744995</v>
+        <v>11.2440376281738</v>
       </c>
       <c r="H1956" t="s">
         <v>8</v>
@@ -51251,7 +51251,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G1957" t="n">
-        <v>11.3285789489746</v>
+        <v>11.3285779953003</v>
       </c>
       <c r="H1957" t="s">
         <v>8</v>
@@ -51667,7 +51667,7 @@
         <v>12</v>
       </c>
       <c r="G1973" t="n">
-        <v>10.1449956893921</v>
+        <v>10.1449947357178</v>
       </c>
       <c r="H1973" t="s">
         <v>8</v>
@@ -51797,7 +51797,7 @@
         <v>11.5600004196167</v>
       </c>
       <c r="G1978" t="n">
-        <v>9.77301216125488</v>
+        <v>9.7730131149292</v>
       </c>
       <c r="H1978" t="s">
         <v>8</v>
@@ -52005,7 +52005,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G1986" t="n">
-        <v>9.13049602508545</v>
+        <v>9.13049697875977</v>
       </c>
       <c r="H1986" t="s">
         <v>8</v>
@@ -52057,7 +52057,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1988" t="n">
-        <v>9.21503829956055</v>
+        <v>9.21503734588623</v>
       </c>
       <c r="H1988" t="s">
         <v>8</v>
@@ -52109,7 +52109,7 @@
         <v>10.9200000762939</v>
       </c>
       <c r="G1990" t="n">
-        <v>9.23194599151611</v>
+        <v>9.2319450378418</v>
       </c>
       <c r="H1990" t="s">
         <v>8</v>
@@ -52291,7 +52291,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G1997" t="n">
-        <v>9.603928565979</v>
+        <v>9.60392951965332</v>
       </c>
       <c r="H1997" t="s">
         <v>8</v>
@@ -52499,7 +52499,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G2005" t="n">
-        <v>10.1957197189331</v>
+        <v>10.1957206726074</v>
       </c>
       <c r="H2005" t="s">
         <v>8</v>
@@ -52707,7 +52707,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G2013" t="n">
-        <v>9.603928565979</v>
+        <v>9.60392951965332</v>
       </c>
       <c r="H2013" t="s">
         <v>8</v>
@@ -52811,7 +52811,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G2017" t="n">
-        <v>9.13049602508545</v>
+        <v>9.13049697875977</v>
       </c>
       <c r="H2017" t="s">
         <v>8</v>
@@ -52863,7 +52863,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G2019" t="n">
-        <v>9.38412189483643</v>
+        <v>9.38412094116211</v>
       </c>
       <c r="H2019" t="s">
         <v>8</v>
@@ -52967,7 +52967,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G2023" t="n">
-        <v>9.38412189483643</v>
+        <v>9.38412094116211</v>
       </c>
       <c r="H2023" t="s">
         <v>8</v>
@@ -53071,7 +53071,7 @@
         <v>11.4399995803833</v>
       </c>
       <c r="G2027" t="n">
-        <v>9.6715612411499</v>
+        <v>9.67156219482422</v>
       </c>
       <c r="H2027" t="s">
         <v>8</v>
@@ -53201,7 +53201,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G2032" t="n">
-        <v>9.603928565979</v>
+        <v>9.60392951965332</v>
       </c>
       <c r="H2032" t="s">
         <v>8</v>
@@ -53461,7 +53461,7 @@
         <v>11.5200004577637</v>
       </c>
       <c r="G2042" t="n">
-        <v>9.73919582366943</v>
+        <v>9.73919677734375</v>
       </c>
       <c r="H2042" t="s">
         <v>8</v>
@@ -53513,7 +53513,7 @@
         <v>11.5600004196167</v>
       </c>
       <c r="G2044" t="n">
-        <v>9.77301216125488</v>
+        <v>9.7730131149292</v>
       </c>
       <c r="H2044" t="s">
         <v>8</v>
@@ -53721,7 +53721,7 @@
         <v>11.0200004577637</v>
       </c>
       <c r="G2052" t="n">
-        <v>9.31648826599121</v>
+        <v>9.31648731231689</v>
       </c>
       <c r="H2052" t="s">
         <v>8</v>
@@ -54475,7 +54475,7 @@
         <v>11.4399995803833</v>
       </c>
       <c r="G2081" t="n">
-        <v>9.6715612411499</v>
+        <v>9.67156219482422</v>
       </c>
       <c r="H2081" t="s">
         <v>8</v>
@@ -54631,7 +54631,7 @@
         <v>10.539999961853</v>
       </c>
       <c r="G2087" t="n">
-        <v>8.91068744659424</v>
+        <v>8.91068840026855</v>
       </c>
       <c r="H2087" t="s">
         <v>8</v>
@@ -54657,7 +54657,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G2088" t="n">
-        <v>9.21503829956055</v>
+        <v>9.21503734588623</v>
       </c>
       <c r="H2088" t="s">
         <v>8</v>
@@ -54709,7 +54709,7 @@
         <v>11.8199996948242</v>
       </c>
       <c r="G2090" t="n">
-        <v>9.99282073974609</v>
+        <v>9.99281978607178</v>
       </c>
       <c r="H2090" t="s">
         <v>8</v>
@@ -54891,7 +54891,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G2097" t="n">
-        <v>9.89136981964111</v>
+        <v>9.89137077331543</v>
       </c>
       <c r="H2097" t="s">
         <v>8</v>
@@ -54917,7 +54917,7 @@
         <v>11.7799997329712</v>
       </c>
       <c r="G2098" t="n">
-        <v>9.95900344848633</v>
+        <v>9.95900440216064</v>
       </c>
       <c r="H2098" t="s">
         <v>8</v>
@@ -54943,7 +54943,7 @@
         <v>11.7799997329712</v>
       </c>
       <c r="G2099" t="n">
-        <v>9.95900344848633</v>
+        <v>9.95900440216064</v>
       </c>
       <c r="H2099" t="s">
         <v>8</v>
@@ -55021,7 +55021,7 @@
         <v>11.5600004196167</v>
       </c>
       <c r="G2102" t="n">
-        <v>9.77301216125488</v>
+        <v>9.7730131149292</v>
       </c>
       <c r="H2102" t="s">
         <v>8</v>
@@ -55073,7 +55073,7 @@
         <v>11.4399995803833</v>
       </c>
       <c r="G2104" t="n">
-        <v>9.6715612411499</v>
+        <v>9.67156219482422</v>
       </c>
       <c r="H2104" t="s">
         <v>8</v>
@@ -55177,7 +55177,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G2108" t="n">
-        <v>9.603928565979</v>
+        <v>9.60392951965332</v>
       </c>
       <c r="H2108" t="s">
         <v>8</v>
@@ -55255,7 +55255,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G2111" t="n">
-        <v>9.38412189483643</v>
+        <v>9.38412094116211</v>
       </c>
       <c r="H2111" t="s">
         <v>8</v>
@@ -55333,7 +55333,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G2114" t="n">
-        <v>10.060453414917</v>
+        <v>10.0604524612427</v>
       </c>
       <c r="H2114" t="s">
         <v>8</v>
@@ -55385,7 +55385,7 @@
         <v>11.8199996948242</v>
       </c>
       <c r="G2116" t="n">
-        <v>9.99282073974609</v>
+        <v>9.99281978607178</v>
       </c>
       <c r="H2116" t="s">
         <v>8</v>
@@ -55411,7 +55411,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G2117" t="n">
-        <v>10.060453414917</v>
+        <v>10.0604524612427</v>
       </c>
       <c r="H2117" t="s">
         <v>8</v>
@@ -55437,7 +55437,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G2118" t="n">
-        <v>10.2802619934082</v>
+        <v>10.2802610397339</v>
       </c>
       <c r="H2118" t="s">
         <v>8</v>
@@ -55463,7 +55463,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G2119" t="n">
-        <v>10.2802619934082</v>
+        <v>10.2802610397339</v>
       </c>
       <c r="H2119" t="s">
         <v>8</v>
@@ -55489,7 +55489,7 @@
         <v>12.0799999237061</v>
       </c>
       <c r="G2120" t="n">
-        <v>10.2126293182373</v>
+        <v>10.212628364563</v>
       </c>
       <c r="H2120" t="s">
         <v>8</v>
@@ -55515,7 +55515,7 @@
         <v>12</v>
       </c>
       <c r="G2121" t="n">
-        <v>10.1449956893921</v>
+        <v>10.1449947357178</v>
       </c>
       <c r="H2121" t="s">
         <v>8</v>
@@ -55593,7 +55593,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G2124" t="n">
-        <v>10.1957197189331</v>
+        <v>10.1957206726074</v>
       </c>
       <c r="H2124" t="s">
         <v>8</v>
@@ -55671,7 +55671,7 @@
         <v>12.0799999237061</v>
       </c>
       <c r="G2127" t="n">
-        <v>10.2126293182373</v>
+        <v>10.212628364563</v>
       </c>
       <c r="H2127" t="s">
         <v>8</v>
@@ -55749,7 +55749,7 @@
         <v>11.9200000762939</v>
       </c>
       <c r="G2130" t="n">
-        <v>10.0773630142212</v>
+        <v>10.0773620605469</v>
       </c>
       <c r="H2130" t="s">
         <v>8</v>
@@ -71248,6 +71248,32 @@
         <v>5.59000015258789</v>
       </c>
       <c r="H2726" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2727">
+      <c r="A2727" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B2727" t="n">
+        <v>248696</v>
+      </c>
+      <c r="C2727" t="n">
+        <v>5.59999990463257</v>
+      </c>
+      <c r="D2727" t="n">
+        <v>5.51999998092651</v>
+      </c>
+      <c r="E2727" t="n">
+        <v>5.59999990463257</v>
+      </c>
+      <c r="F2727" t="n">
+        <v>5.55999994277954</v>
+      </c>
+      <c r="G2727" t="n">
+        <v>5.55999994277954</v>
+      </c>
+      <c r="H2727" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/MARR.MI.xlsx
+++ b/data/MARR.MI.xlsx
@@ -63270,8 +63270,31 @@
       <c r="E2735" t="n">
         <v>5.21000003814697</v>
       </c>
-      <c r="F2735"/>
+      <c r="F2735" t="n">
+        <v>5.19000005722046</v>
+      </c>
       <c r="G2735" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2736">
+      <c r="A2736" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2736" t="n">
+        <v>147373</v>
+      </c>
+      <c r="C2736" t="n">
+        <v>5.38000011444092</v>
+      </c>
+      <c r="D2736" t="n">
+        <v>5.21999979019165</v>
+      </c>
+      <c r="E2736" t="n">
+        <v>5.21999979019165</v>
+      </c>
+      <c r="F2736"/>
+      <c r="G2736" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/MARR.MI.xlsx
+++ b/data/MARR.MI.xlsx
@@ -63293,8 +63293,31 @@
       <c r="E2736" t="n">
         <v>5.21999979019165</v>
       </c>
-      <c r="F2736"/>
+      <c r="F2736" t="n">
+        <v>5.36999988555908</v>
+      </c>
       <c r="G2736" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2737">
+      <c r="A2737" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2737" t="n">
+        <v>160250</v>
+      </c>
+      <c r="C2737" t="n">
+        <v>5.42999982833862</v>
+      </c>
+      <c r="D2737" t="n">
+        <v>5.23000001907349</v>
+      </c>
+      <c r="E2737" t="n">
+        <v>5.42999982833862</v>
+      </c>
+      <c r="F2737"/>
+      <c r="G2737" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/MARR.MI.xlsx
+++ b/data/MARR.MI.xlsx
@@ -63311,13 +63311,36 @@
         <v>5.42999982833862</v>
       </c>
       <c r="D2737" t="n">
-        <v>5.23000001907349</v>
+        <v>5.19999980926514</v>
       </c>
       <c r="E2737" t="n">
         <v>5.42999982833862</v>
       </c>
-      <c r="F2737"/>
+      <c r="F2737" t="n">
+        <v>5.19999980926514</v>
+      </c>
       <c r="G2737" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2738">
+      <c r="A2738" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2738" t="n">
+        <v>190307</v>
+      </c>
+      <c r="C2738" t="n">
+        <v>5.26000022888184</v>
+      </c>
+      <c r="D2738" t="n">
+        <v>5.17999982833862</v>
+      </c>
+      <c r="E2738" t="n">
+        <v>5.21000003814697</v>
+      </c>
+      <c r="F2738"/>
+      <c r="G2738" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/MARR.MI.xlsx
+++ b/data/MARR.MI.xlsx
@@ -63339,8 +63339,31 @@
       <c r="E2738" t="n">
         <v>5.21000003814697</v>
       </c>
-      <c r="F2738"/>
+      <c r="F2738" t="n">
+        <v>5.23000001907349</v>
+      </c>
       <c r="G2738" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2739">
+      <c r="A2739" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B2739" t="n">
+        <v>155418</v>
+      </c>
+      <c r="C2739" t="n">
+        <v>5.3899998664856</v>
+      </c>
+      <c r="D2739" t="n">
+        <v>5.26999998092651</v>
+      </c>
+      <c r="E2739" t="n">
+        <v>5.26999998092651</v>
+      </c>
+      <c r="F2739"/>
+      <c r="G2739" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/MARR.MI.xlsx
+++ b/data/MARR.MI.xlsx
@@ -63369,6 +63369,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2740">
+      <c r="A2740" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2740" t="n">
+        <v>116352</v>
+      </c>
+      <c r="C2740" t="n">
+        <v>5.30000019073486</v>
+      </c>
+      <c r="D2740" t="n">
+        <v>5.17999982833862</v>
+      </c>
+      <c r="E2740" t="n">
+        <v>5.30000019073486</v>
+      </c>
+      <c r="F2740" t="n">
+        <v>5.17999982833862</v>
+      </c>
+      <c r="G2740" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
